--- a/results/block2_results/area/Normal_1/branches/dataframes/dataset_LCA_B01_Normal_1.xlsx
+++ b/results/block2_results/area/Normal_1/branches/dataframes/dataset_LCA_B01_Normal_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J823"/>
+  <dimension ref="A1:K823"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Segment_ID</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Area</t>
         </is>
       </c>
@@ -515,6 +520,9 @@
         </is>
       </c>
       <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
         <v>24.44938674448072</v>
       </c>
     </row>
@@ -553,6 +561,9 @@
         </is>
       </c>
       <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
         <v>23.09469567725773</v>
       </c>
     </row>
@@ -591,6 +602,9 @@
         </is>
       </c>
       <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
         <v>23.09469567725773</v>
       </c>
     </row>
@@ -629,6 +643,9 @@
         </is>
       </c>
       <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
         <v>23.09469567725773</v>
       </c>
     </row>
@@ -667,6 +684,9 @@
         </is>
       </c>
       <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
         <v>16.22537890841612</v>
       </c>
     </row>
@@ -705,6 +725,9 @@
         </is>
       </c>
       <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
         <v>15.92519383307983</v>
       </c>
     </row>
@@ -743,6 +766,9 @@
         </is>
       </c>
       <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
         <v>15.55123726155539</v>
       </c>
     </row>
@@ -781,6 +807,9 @@
         </is>
       </c>
       <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
         <v>15.50392193361757</v>
       </c>
     </row>
@@ -819,6 +848,9 @@
         </is>
       </c>
       <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
         <v>15.43409332138252</v>
       </c>
     </row>
@@ -857,6 +889,9 @@
         </is>
       </c>
       <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
         <v>15.43409332138252</v>
       </c>
     </row>
@@ -895,6 +930,9 @@
         </is>
       </c>
       <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
         <v>14.91383648998964</v>
       </c>
     </row>
@@ -933,6 +971,9 @@
         </is>
       </c>
       <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" t="n">
         <v>14.91383648998964</v>
       </c>
     </row>
@@ -971,6 +1012,9 @@
         </is>
       </c>
       <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
         <v>13.96252814601202</v>
       </c>
     </row>
@@ -1009,6 +1053,9 @@
         </is>
       </c>
       <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
         <v>12.8845474029381</v>
       </c>
     </row>
@@ -1047,6 +1094,9 @@
         </is>
       </c>
       <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
         <v>12.56557511094277</v>
       </c>
     </row>
@@ -1085,6 +1135,9 @@
         </is>
       </c>
       <c r="J17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" t="n">
         <v>12.56557511094277</v>
       </c>
     </row>
@@ -1123,6 +1176,9 @@
         </is>
       </c>
       <c r="J18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" t="n">
         <v>12.42650727241244</v>
       </c>
     </row>
@@ -1161,6 +1217,9 @@
         </is>
       </c>
       <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
         <v>12.61222121789064</v>
       </c>
     </row>
@@ -1199,6 +1258,9 @@
         </is>
       </c>
       <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
         <v>12.6149723565889</v>
       </c>
     </row>
@@ -1237,6 +1299,9 @@
         </is>
       </c>
       <c r="J21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" t="n">
         <v>12.6149723565889</v>
       </c>
     </row>
@@ -1275,6 +1340,9 @@
         </is>
       </c>
       <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
         <v>12.88726856229838</v>
       </c>
     </row>
@@ -1313,6 +1381,9 @@
         </is>
       </c>
       <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
         <v>13.08268414389388</v>
       </c>
     </row>
@@ -1351,6 +1422,9 @@
         </is>
       </c>
       <c r="J24" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" t="n">
         <v>13.11655963642752</v>
       </c>
     </row>
@@ -1389,6 +1463,9 @@
         </is>
       </c>
       <c r="J25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
         <v>13.06477406907523</v>
       </c>
     </row>
@@ -1427,6 +1504,9 @@
         </is>
       </c>
       <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
         <v>13.00822550737505</v>
       </c>
     </row>
@@ -1465,6 +1545,9 @@
         </is>
       </c>
       <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
         <v>13.00822550737505</v>
       </c>
     </row>
@@ -1503,6 +1586,9 @@
         </is>
       </c>
       <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
         <v>12.82946633796654</v>
       </c>
     </row>
@@ -1541,6 +1627,9 @@
         </is>
       </c>
       <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
         <v>12.72199060197538</v>
       </c>
     </row>
@@ -1579,6 +1668,9 @@
         </is>
       </c>
       <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
         <v>12.76786570293602</v>
       </c>
     </row>
@@ -1617,6 +1709,9 @@
         </is>
       </c>
       <c r="J31" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" t="n">
         <v>12.94918332241907</v>
       </c>
     </row>
@@ -1655,6 +1750,9 @@
         </is>
       </c>
       <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
         <v>13.29202663846189</v>
       </c>
     </row>
@@ -1693,6 +1791,9 @@
         </is>
       </c>
       <c r="J33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" t="n">
         <v>13.29202663846189</v>
       </c>
     </row>
@@ -1731,6 +1832,9 @@
         </is>
       </c>
       <c r="J34" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" t="n">
         <v>13.74461230569916</v>
       </c>
     </row>
@@ -1769,6 +1873,9 @@
         </is>
       </c>
       <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
         <v>14.01711486461985</v>
       </c>
     </row>
@@ -1807,6 +1914,9 @@
         </is>
       </c>
       <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
         <v>14.02341868198291</v>
       </c>
     </row>
@@ -1845,6 +1955,9 @@
         </is>
       </c>
       <c r="J37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" t="n">
         <v>14.4136984000467</v>
       </c>
     </row>
@@ -1883,6 +1996,9 @@
         </is>
       </c>
       <c r="J38" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" t="n">
         <v>14.4136984000467</v>
       </c>
     </row>
@@ -1921,6 +2037,9 @@
         </is>
       </c>
       <c r="J39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K39" t="n">
         <v>14.4136984000467</v>
       </c>
     </row>
@@ -1959,6 +2078,9 @@
         </is>
       </c>
       <c r="J40" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" t="n">
         <v>14.37286417316269</v>
       </c>
     </row>
@@ -1997,6 +2119,9 @@
         </is>
       </c>
       <c r="J41" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" t="n">
         <v>14.36056284287022</v>
       </c>
     </row>
@@ -2035,6 +2160,9 @@
         </is>
       </c>
       <c r="J42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" t="n">
         <v>14.32918239439808</v>
       </c>
     </row>
@@ -2073,6 +2201,9 @@
         </is>
       </c>
       <c r="J43" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" t="n">
         <v>14.33140447444988</v>
       </c>
     </row>
@@ -2111,6 +2242,9 @@
         </is>
       </c>
       <c r="J44" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" t="n">
         <v>14.33266758623184</v>
       </c>
     </row>
@@ -2149,6 +2283,9 @@
         </is>
       </c>
       <c r="J45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" t="n">
         <v>14.47432312940295</v>
       </c>
     </row>
@@ -2187,6 +2324,9 @@
         </is>
       </c>
       <c r="J46" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" t="n">
         <v>14.69408070284003</v>
       </c>
     </row>
@@ -2225,6 +2365,9 @@
         </is>
       </c>
       <c r="J47" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" t="n">
         <v>14.90097207929845</v>
       </c>
     </row>
@@ -2263,6 +2406,9 @@
         </is>
       </c>
       <c r="J48" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" t="n">
         <v>14.90097207929845</v>
       </c>
     </row>
@@ -2301,6 +2447,9 @@
         </is>
       </c>
       <c r="J49" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" t="n">
         <v>15.39058793177672</v>
       </c>
     </row>
@@ -2339,6 +2488,9 @@
         </is>
       </c>
       <c r="J50" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" t="n">
         <v>15.55279586015389</v>
       </c>
     </row>
@@ -2377,6 +2529,9 @@
         </is>
       </c>
       <c r="J51" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" t="n">
         <v>16.46410452789935</v>
       </c>
     </row>
@@ -2415,6 +2570,9 @@
         </is>
       </c>
       <c r="J52" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" t="n">
         <v>17.37544874440357</v>
       </c>
     </row>
@@ -2453,6 +2611,9 @@
         </is>
       </c>
       <c r="J53" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" t="n">
         <v>18.99504856873714</v>
       </c>
     </row>
@@ -2491,6 +2652,9 @@
         </is>
       </c>
       <c r="J54" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" t="n">
         <v>19.35440687995326</v>
       </c>
     </row>
@@ -2529,6 +2693,9 @@
         </is>
       </c>
       <c r="J55" t="n">
+        <v>11</v>
+      </c>
+      <c r="K55" t="n">
         <v>20.85858809627996</v>
       </c>
     </row>
@@ -2567,6 +2734,9 @@
         </is>
       </c>
       <c r="J56" t="n">
+        <v>11</v>
+      </c>
+      <c r="K56" t="n">
         <v>20.89169658899361</v>
       </c>
     </row>
@@ -2605,6 +2775,9 @@
         </is>
       </c>
       <c r="J57" t="n">
+        <v>11</v>
+      </c>
+      <c r="K57" t="n">
         <v>21.75595998124422</v>
       </c>
     </row>
@@ -2643,6 +2816,9 @@
         </is>
       </c>
       <c r="J58" t="n">
+        <v>11</v>
+      </c>
+      <c r="K58" t="n">
         <v>22.23426731578168</v>
       </c>
     </row>
@@ -2681,6 +2857,9 @@
         </is>
       </c>
       <c r="J59" t="n">
+        <v>11</v>
+      </c>
+      <c r="K59" t="n">
         <v>21.95138014089535</v>
       </c>
     </row>
@@ -2719,6 +2898,9 @@
         </is>
       </c>
       <c r="J60" t="n">
+        <v>11</v>
+      </c>
+      <c r="K60" t="n">
         <v>24.63649424087505</v>
       </c>
     </row>
@@ -2757,6 +2939,9 @@
         </is>
       </c>
       <c r="J61" t="n">
+        <v>11</v>
+      </c>
+      <c r="K61" t="n">
         <v>25.18536911583633</v>
       </c>
     </row>
@@ -2795,6 +2980,9 @@
         </is>
       </c>
       <c r="J62" t="n">
+        <v>11</v>
+      </c>
+      <c r="K62" t="n">
         <v>27.31329478260586</v>
       </c>
     </row>
@@ -2833,6 +3021,9 @@
         </is>
       </c>
       <c r="J63" t="n">
+        <v>11</v>
+      </c>
+      <c r="K63" t="n">
         <v>27.18205504873007</v>
       </c>
     </row>
@@ -2871,6 +3062,9 @@
         </is>
       </c>
       <c r="J64" t="n">
+        <v>11</v>
+      </c>
+      <c r="K64" t="n">
         <v>26.71182468007363</v>
       </c>
     </row>
@@ -2909,6 +3103,9 @@
         </is>
       </c>
       <c r="J65" t="n">
+        <v>11</v>
+      </c>
+      <c r="K65" t="n">
         <v>26.61477337250786</v>
       </c>
     </row>
@@ -2947,6 +3144,9 @@
         </is>
       </c>
       <c r="J66" t="n">
+        <v>11</v>
+      </c>
+      <c r="K66" t="n">
         <v>9.819882390104297</v>
       </c>
     </row>
@@ -2985,6 +3185,9 @@
         </is>
       </c>
       <c r="J67" t="n">
+        <v>11</v>
+      </c>
+      <c r="K67" t="n">
         <v>9.819882390104297</v>
       </c>
     </row>
@@ -3023,6 +3226,9 @@
         </is>
       </c>
       <c r="J68" t="n">
+        <v>11</v>
+      </c>
+      <c r="K68" t="n">
         <v>9.745667235392832</v>
       </c>
     </row>
@@ -3061,6 +3267,9 @@
         </is>
       </c>
       <c r="J69" t="n">
+        <v>11</v>
+      </c>
+      <c r="K69" t="n">
         <v>9.745667235392832</v>
       </c>
     </row>
@@ -3099,6 +3308,9 @@
         </is>
       </c>
       <c r="J70" t="n">
+        <v>11</v>
+      </c>
+      <c r="K70" t="n">
         <v>9.75609596068019</v>
       </c>
     </row>
@@ -3137,6 +3349,9 @@
         </is>
       </c>
       <c r="J71" t="n">
+        <v>11</v>
+      </c>
+      <c r="K71" t="n">
         <v>9.75609596068019</v>
       </c>
     </row>
@@ -3175,6 +3390,9 @@
         </is>
       </c>
       <c r="J72" t="n">
+        <v>11</v>
+      </c>
+      <c r="K72" t="n">
         <v>9.981290382682612</v>
       </c>
     </row>
@@ -3213,6 +3431,9 @@
         </is>
       </c>
       <c r="J73" t="n">
+        <v>11</v>
+      </c>
+      <c r="K73" t="n">
         <v>9.981290382682612</v>
       </c>
     </row>
@@ -3251,6 +3472,9 @@
         </is>
       </c>
       <c r="J74" t="n">
+        <v>11</v>
+      </c>
+      <c r="K74" t="n">
         <v>12.09167051507188</v>
       </c>
     </row>
@@ -3289,6 +3513,9 @@
         </is>
       </c>
       <c r="J75" t="n">
+        <v>11</v>
+      </c>
+      <c r="K75" t="n">
         <v>12.31620569749018</v>
       </c>
     </row>
@@ -3327,6 +3554,9 @@
         </is>
       </c>
       <c r="J76" t="n">
+        <v>11</v>
+      </c>
+      <c r="K76" t="n">
         <v>12.66141284150133</v>
       </c>
     </row>
@@ -3365,6 +3595,9 @@
         </is>
       </c>
       <c r="J77" t="n">
+        <v>11</v>
+      </c>
+      <c r="K77" t="n">
         <v>13.00449390422686</v>
       </c>
     </row>
@@ -3403,6 +3636,9 @@
         </is>
       </c>
       <c r="J78" t="n">
+        <v>11</v>
+      </c>
+      <c r="K78" t="n">
         <v>9.12738816852228</v>
       </c>
     </row>
@@ -3441,6 +3677,9 @@
         </is>
       </c>
       <c r="J79" t="n">
+        <v>11</v>
+      </c>
+      <c r="K79" t="n">
         <v>8.68658704571123</v>
       </c>
     </row>
@@ -3479,6 +3718,9 @@
         </is>
       </c>
       <c r="J80" t="n">
+        <v>11</v>
+      </c>
+      <c r="K80" t="n">
         <v>8.681894726582</v>
       </c>
     </row>
@@ -3517,6 +3759,9 @@
         </is>
       </c>
       <c r="J81" t="n">
+        <v>11</v>
+      </c>
+      <c r="K81" t="n">
         <v>8.693004759293984</v>
       </c>
     </row>
@@ -3555,6 +3800,9 @@
         </is>
       </c>
       <c r="J82" t="n">
+        <v>11</v>
+      </c>
+      <c r="K82" t="n">
         <v>8.725149125649589</v>
       </c>
     </row>
@@ -3593,6 +3841,9 @@
         </is>
       </c>
       <c r="J83" t="n">
+        <v>11</v>
+      </c>
+      <c r="K83" t="n">
         <v>8.767374629969833</v>
       </c>
     </row>
@@ -3631,6 +3882,9 @@
         </is>
       </c>
       <c r="J84" t="n">
+        <v>11</v>
+      </c>
+      <c r="K84" t="n">
         <v>8.810038227616156</v>
       </c>
     </row>
@@ -3669,6 +3923,9 @@
         </is>
       </c>
       <c r="J85" t="n">
+        <v>11</v>
+      </c>
+      <c r="K85" t="n">
         <v>8.810038227616156</v>
       </c>
     </row>
@@ -3707,6 +3964,9 @@
         </is>
       </c>
       <c r="J86" t="n">
+        <v>11</v>
+      </c>
+      <c r="K86" t="n">
         <v>8.979920966893374</v>
       </c>
     </row>
@@ -3745,6 +4005,9 @@
         </is>
       </c>
       <c r="J87" t="n">
+        <v>11</v>
+      </c>
+      <c r="K87" t="n">
         <v>9.189485465294592</v>
       </c>
     </row>
@@ -3783,6 +4046,9 @@
         </is>
       </c>
       <c r="J88" t="n">
+        <v>11</v>
+      </c>
+      <c r="K88" t="n">
         <v>9.20061339885968</v>
       </c>
     </row>
@@ -3821,6 +4087,9 @@
         </is>
       </c>
       <c r="J89" t="n">
+        <v>11</v>
+      </c>
+      <c r="K89" t="n">
         <v>9.385776211530537</v>
       </c>
     </row>
@@ -3859,6 +4128,9 @@
         </is>
       </c>
       <c r="J90" t="n">
+        <v>11</v>
+      </c>
+      <c r="K90" t="n">
         <v>9.385776211530537</v>
       </c>
     </row>
@@ -3897,6 +4169,9 @@
         </is>
       </c>
       <c r="J91" t="n">
+        <v>11</v>
+      </c>
+      <c r="K91" t="n">
         <v>9.594901878548837</v>
       </c>
     </row>
@@ -3935,6 +4210,9 @@
         </is>
       </c>
       <c r="J92" t="n">
+        <v>11</v>
+      </c>
+      <c r="K92" t="n">
         <v>9.711631620980414</v>
       </c>
     </row>
@@ -3973,6 +4251,9 @@
         </is>
       </c>
       <c r="J93" t="n">
+        <v>11</v>
+      </c>
+      <c r="K93" t="n">
         <v>9.812453513515775</v>
       </c>
     </row>
@@ -4011,6 +4292,9 @@
         </is>
       </c>
       <c r="J94" t="n">
+        <v>11</v>
+      </c>
+      <c r="K94" t="n">
         <v>9.974311185902952</v>
       </c>
     </row>
@@ -4049,6 +4333,9 @@
         </is>
       </c>
       <c r="J95" t="n">
+        <v>11</v>
+      </c>
+      <c r="K95" t="n">
         <v>10.02205133288883</v>
       </c>
     </row>
@@ -4087,6 +4374,9 @@
         </is>
       </c>
       <c r="J96" t="n">
+        <v>11</v>
+      </c>
+      <c r="K96" t="n">
         <v>10.28025187896138</v>
       </c>
     </row>
@@ -4125,6 +4415,9 @@
         </is>
       </c>
       <c r="J97" t="n">
+        <v>11</v>
+      </c>
+      <c r="K97" t="n">
         <v>10.38618001855317</v>
       </c>
     </row>
@@ -4163,6 +4456,9 @@
         </is>
       </c>
       <c r="J98" t="n">
+        <v>11</v>
+      </c>
+      <c r="K98" t="n">
         <v>10.44776992585482</v>
       </c>
     </row>
@@ -4201,6 +4497,9 @@
         </is>
       </c>
       <c r="J99" t="n">
+        <v>11</v>
+      </c>
+      <c r="K99" t="n">
         <v>10.55026105538567</v>
       </c>
     </row>
@@ -4239,6 +4538,9 @@
         </is>
       </c>
       <c r="J100" t="n">
+        <v>11</v>
+      </c>
+      <c r="K100" t="n">
         <v>10.55640596549939</v>
       </c>
     </row>
@@ -4277,6 +4579,9 @@
         </is>
       </c>
       <c r="J101" t="n">
+        <v>11</v>
+      </c>
+      <c r="K101" t="n">
         <v>10.52219052114853</v>
       </c>
     </row>
@@ -4315,6 +4620,9 @@
         </is>
       </c>
       <c r="J102" t="n">
+        <v>11</v>
+      </c>
+      <c r="K102" t="n">
         <v>10.4808184702455</v>
       </c>
     </row>
@@ -4353,6 +4661,9 @@
         </is>
       </c>
       <c r="J103" t="n">
+        <v>11</v>
+      </c>
+      <c r="K103" t="n">
         <v>10.45075109019776</v>
       </c>
     </row>
@@ -4391,6 +4702,9 @@
         </is>
       </c>
       <c r="J104" t="n">
+        <v>11</v>
+      </c>
+      <c r="K104" t="n">
         <v>10.42180488538178</v>
       </c>
     </row>
@@ -4429,6 +4743,9 @@
         </is>
       </c>
       <c r="J105" t="n">
+        <v>11</v>
+      </c>
+      <c r="K105" t="n">
         <v>10.41806567842505</v>
       </c>
     </row>
@@ -4467,6 +4784,9 @@
         </is>
       </c>
       <c r="J106" t="n">
+        <v>11</v>
+      </c>
+      <c r="K106" t="n">
         <v>10.3885771773526</v>
       </c>
     </row>
@@ -4505,6 +4825,9 @@
         </is>
       </c>
       <c r="J107" t="n">
+        <v>11</v>
+      </c>
+      <c r="K107" t="n">
         <v>10.45060969889723</v>
       </c>
     </row>
@@ -4543,6 +4866,9 @@
         </is>
       </c>
       <c r="J108" t="n">
+        <v>11</v>
+      </c>
+      <c r="K108" t="n">
         <v>10.50364497429563</v>
       </c>
     </row>
@@ -4581,6 +4907,9 @@
         </is>
       </c>
       <c r="J109" t="n">
+        <v>11</v>
+      </c>
+      <c r="K109" t="n">
         <v>10.81779559383239</v>
       </c>
     </row>
@@ -4619,6 +4948,9 @@
         </is>
       </c>
       <c r="J110" t="n">
+        <v>11</v>
+      </c>
+      <c r="K110" t="n">
         <v>10.9357231825844</v>
       </c>
     </row>
@@ -4657,6 +4989,9 @@
         </is>
       </c>
       <c r="J111" t="n">
+        <v>11</v>
+      </c>
+      <c r="K111" t="n">
         <v>11.55281843846564</v>
       </c>
     </row>
@@ -4695,6 +5030,9 @@
         </is>
       </c>
       <c r="J112" t="n">
+        <v>11</v>
+      </c>
+      <c r="K112" t="n">
         <v>13.24905110056308</v>
       </c>
     </row>
@@ -4733,6 +5071,9 @@
         </is>
       </c>
       <c r="J113" t="n">
+        <v>11</v>
+      </c>
+      <c r="K113" t="n">
         <v>13.24905110056308</v>
       </c>
     </row>
@@ -4771,6 +5112,9 @@
         </is>
       </c>
       <c r="J114" t="n">
+        <v>11</v>
+      </c>
+      <c r="K114" t="n">
         <v>13.96546733948439</v>
       </c>
     </row>
@@ -4809,6 +5153,9 @@
         </is>
       </c>
       <c r="J115" t="n">
+        <v>11</v>
+      </c>
+      <c r="K115" t="n">
         <v>14.09499060277884</v>
       </c>
     </row>
@@ -4847,6 +5194,9 @@
         </is>
       </c>
       <c r="J116" t="n">
+        <v>11</v>
+      </c>
+      <c r="K116" t="n">
         <v>14.10231971947695</v>
       </c>
     </row>
@@ -4885,6 +5235,9 @@
         </is>
       </c>
       <c r="J117" t="n">
+        <v>11</v>
+      </c>
+      <c r="K117" t="n">
         <v>13.32115312121745</v>
       </c>
     </row>
@@ -4923,6 +5276,9 @@
         </is>
       </c>
       <c r="J118" t="n">
+        <v>11</v>
+      </c>
+      <c r="K118" t="n">
         <v>12.18673597949732</v>
       </c>
     </row>
@@ -4961,6 +5317,9 @@
         </is>
       </c>
       <c r="J119" t="n">
+        <v>11</v>
+      </c>
+      <c r="K119" t="n">
         <v>11.61520007469289</v>
       </c>
     </row>
@@ -4999,6 +5358,9 @@
         </is>
       </c>
       <c r="J120" t="n">
+        <v>11</v>
+      </c>
+      <c r="K120" t="n">
         <v>10.7717653162068</v>
       </c>
     </row>
@@ -5037,6 +5399,9 @@
         </is>
       </c>
       <c r="J121" t="n">
+        <v>11</v>
+      </c>
+      <c r="K121" t="n">
         <v>10.62118096941062</v>
       </c>
     </row>
@@ -5075,6 +5440,9 @@
         </is>
       </c>
       <c r="J122" t="n">
+        <v>11</v>
+      </c>
+      <c r="K122" t="n">
         <v>10.62118096941062</v>
       </c>
     </row>
@@ -5113,6 +5481,9 @@
         </is>
       </c>
       <c r="J123" t="n">
+        <v>11</v>
+      </c>
+      <c r="K123" t="n">
         <v>10.45511537631013</v>
       </c>
     </row>
@@ -5151,6 +5522,9 @@
         </is>
       </c>
       <c r="J124" t="n">
+        <v>11</v>
+      </c>
+      <c r="K124" t="n">
         <v>10.44611547119964</v>
       </c>
     </row>
@@ -5189,6 +5563,9 @@
         </is>
       </c>
       <c r="J125" t="n">
+        <v>11</v>
+      </c>
+      <c r="K125" t="n">
         <v>10.40516927885814</v>
       </c>
     </row>
@@ -5227,6 +5604,9 @@
         </is>
       </c>
       <c r="J126" t="n">
+        <v>11</v>
+      </c>
+      <c r="K126" t="n">
         <v>10.15234578612369</v>
       </c>
     </row>
@@ -5265,6 +5645,9 @@
         </is>
       </c>
       <c r="J127" t="n">
+        <v>11</v>
+      </c>
+      <c r="K127" t="n">
         <v>10.12854983494127</v>
       </c>
     </row>
@@ -5303,6 +5686,9 @@
         </is>
       </c>
       <c r="J128" t="n">
+        <v>11</v>
+      </c>
+      <c r="K128" t="n">
         <v>10.13429438631349</v>
       </c>
     </row>
@@ -5341,6 +5727,9 @@
         </is>
       </c>
       <c r="J129" t="n">
+        <v>11</v>
+      </c>
+      <c r="K129" t="n">
         <v>10.16702268282531</v>
       </c>
     </row>
@@ -5379,6 +5768,9 @@
         </is>
       </c>
       <c r="J130" t="n">
+        <v>11</v>
+      </c>
+      <c r="K130" t="n">
         <v>10.19850456500321</v>
       </c>
     </row>
@@ -5417,6 +5809,9 @@
         </is>
       </c>
       <c r="J131" t="n">
+        <v>11</v>
+      </c>
+      <c r="K131" t="n">
         <v>10.15988699682155</v>
       </c>
     </row>
@@ -5455,6 +5850,9 @@
         </is>
       </c>
       <c r="J132" t="n">
+        <v>11</v>
+      </c>
+      <c r="K132" t="n">
         <v>10.15045600603868</v>
       </c>
     </row>
@@ -5493,6 +5891,9 @@
         </is>
       </c>
       <c r="J133" t="n">
+        <v>11</v>
+      </c>
+      <c r="K133" t="n">
         <v>10.15045600603868</v>
       </c>
     </row>
@@ -5531,6 +5932,9 @@
         </is>
       </c>
       <c r="J134" t="n">
+        <v>11</v>
+      </c>
+      <c r="K134" t="n">
         <v>9.889113576235221</v>
       </c>
     </row>
@@ -5569,6 +5973,9 @@
         </is>
       </c>
       <c r="J135" t="n">
+        <v>11</v>
+      </c>
+      <c r="K135" t="n">
         <v>9.889113576235221</v>
       </c>
     </row>
@@ -5607,6 +6014,9 @@
         </is>
       </c>
       <c r="J136" t="n">
+        <v>11</v>
+      </c>
+      <c r="K136" t="n">
         <v>9.503480022823256</v>
       </c>
     </row>
@@ -5645,6 +6055,9 @@
         </is>
       </c>
       <c r="J137" t="n">
+        <v>11</v>
+      </c>
+      <c r="K137" t="n">
         <v>9.503480022823256</v>
       </c>
     </row>
@@ -5683,6 +6096,9 @@
         </is>
       </c>
       <c r="J138" t="n">
+        <v>11</v>
+      </c>
+      <c r="K138" t="n">
         <v>9.273302827189962</v>
       </c>
     </row>
@@ -5721,6 +6137,9 @@
         </is>
       </c>
       <c r="J139" t="n">
+        <v>11</v>
+      </c>
+      <c r="K139" t="n">
         <v>9.323353732391949</v>
       </c>
     </row>
@@ -5759,6 +6178,9 @@
         </is>
       </c>
       <c r="J140" t="n">
+        <v>11</v>
+      </c>
+      <c r="K140" t="n">
         <v>9.538199059605576</v>
       </c>
     </row>
@@ -5797,6 +6219,9 @@
         </is>
       </c>
       <c r="J141" t="n">
+        <v>11</v>
+      </c>
+      <c r="K141" t="n">
         <v>9.595159351550077</v>
       </c>
     </row>
@@ -5835,6 +6260,9 @@
         </is>
       </c>
       <c r="J142" t="n">
+        <v>11</v>
+      </c>
+      <c r="K142" t="n">
         <v>9.640228187381412</v>
       </c>
     </row>
@@ -5873,6 +6301,9 @@
         </is>
       </c>
       <c r="J143" t="n">
+        <v>11</v>
+      </c>
+      <c r="K143" t="n">
         <v>9.67585678642285</v>
       </c>
     </row>
@@ -5911,6 +6342,9 @@
         </is>
       </c>
       <c r="J144" t="n">
+        <v>11</v>
+      </c>
+      <c r="K144" t="n">
         <v>9.67585678642285</v>
       </c>
     </row>
@@ -5949,6 +6383,9 @@
         </is>
       </c>
       <c r="J145" t="n">
+        <v>11</v>
+      </c>
+      <c r="K145" t="n">
         <v>9.644544295013892</v>
       </c>
     </row>
@@ -5987,6 +6424,9 @@
         </is>
       </c>
       <c r="J146" t="n">
+        <v>11</v>
+      </c>
+      <c r="K146" t="n">
         <v>9.575393468358264</v>
       </c>
     </row>
@@ -6025,6 +6465,9 @@
         </is>
       </c>
       <c r="J147" t="n">
+        <v>11</v>
+      </c>
+      <c r="K147" t="n">
         <v>9.509165247009472</v>
       </c>
     </row>
@@ -6063,6 +6506,9 @@
         </is>
       </c>
       <c r="J148" t="n">
+        <v>11</v>
+      </c>
+      <c r="K148" t="n">
         <v>9.186890150588898</v>
       </c>
     </row>
@@ -6101,6 +6547,9 @@
         </is>
       </c>
       <c r="J149" t="n">
+        <v>11</v>
+      </c>
+      <c r="K149" t="n">
         <v>8.892310645809815</v>
       </c>
     </row>
@@ -6139,6 +6588,9 @@
         </is>
       </c>
       <c r="J150" t="n">
+        <v>11</v>
+      </c>
+      <c r="K150" t="n">
         <v>8.798285875284799</v>
       </c>
     </row>
@@ -6177,6 +6629,9 @@
         </is>
       </c>
       <c r="J151" t="n">
+        <v>11</v>
+      </c>
+      <c r="K151" t="n">
         <v>8.875333945274798</v>
       </c>
     </row>
@@ -6215,6 +6670,9 @@
         </is>
       </c>
       <c r="J152" t="n">
+        <v>11</v>
+      </c>
+      <c r="K152" t="n">
         <v>8.916837319105506</v>
       </c>
     </row>
@@ -6253,6 +6711,9 @@
         </is>
       </c>
       <c r="J153" t="n">
+        <v>11</v>
+      </c>
+      <c r="K153" t="n">
         <v>9.076727962887233</v>
       </c>
     </row>
@@ -6291,6 +6752,9 @@
         </is>
       </c>
       <c r="J154" t="n">
+        <v>11</v>
+      </c>
+      <c r="K154" t="n">
         <v>9.266264516167034</v>
       </c>
     </row>
@@ -6329,6 +6793,9 @@
         </is>
       </c>
       <c r="J155" t="n">
+        <v>11</v>
+      </c>
+      <c r="K155" t="n">
         <v>9.383051777516972</v>
       </c>
     </row>
@@ -6367,6 +6834,9 @@
         </is>
       </c>
       <c r="J156" t="n">
+        <v>11</v>
+      </c>
+      <c r="K156" t="n">
         <v>9.383051777516972</v>
       </c>
     </row>
@@ -6405,6 +6875,9 @@
         </is>
       </c>
       <c r="J157" t="n">
+        <v>11</v>
+      </c>
+      <c r="K157" t="n">
         <v>9.460674517214896</v>
       </c>
     </row>
@@ -6443,6 +6916,9 @@
         </is>
       </c>
       <c r="J158" t="n">
+        <v>11</v>
+      </c>
+      <c r="K158" t="n">
         <v>9.460674517214896</v>
       </c>
     </row>
@@ -6481,6 +6957,9 @@
         </is>
       </c>
       <c r="J159" t="n">
+        <v>11</v>
+      </c>
+      <c r="K159" t="n">
         <v>9.459995832832561</v>
       </c>
     </row>
@@ -6519,6 +6998,9 @@
         </is>
       </c>
       <c r="J160" t="n">
+        <v>11</v>
+      </c>
+      <c r="K160" t="n">
         <v>9.459995832832561</v>
       </c>
     </row>
@@ -6557,6 +7039,9 @@
         </is>
       </c>
       <c r="J161" t="n">
+        <v>11</v>
+      </c>
+      <c r="K161" t="n">
         <v>9.442058385983874</v>
       </c>
     </row>
@@ -6595,6 +7080,9 @@
         </is>
       </c>
       <c r="J162" t="n">
+        <v>11</v>
+      </c>
+      <c r="K162" t="n">
         <v>9.445691342095797</v>
       </c>
     </row>
@@ -6633,6 +7121,9 @@
         </is>
       </c>
       <c r="J163" t="n">
+        <v>11</v>
+      </c>
+      <c r="K163" t="n">
         <v>9.44635359893042</v>
       </c>
     </row>
@@ -6671,6 +7162,9 @@
         </is>
       </c>
       <c r="J164" t="n">
+        <v>11</v>
+      </c>
+      <c r="K164" t="n">
         <v>9.358002915936485</v>
       </c>
     </row>
@@ -6709,6 +7203,9 @@
         </is>
       </c>
       <c r="J165" t="n">
+        <v>11</v>
+      </c>
+      <c r="K165" t="n">
         <v>9.358002915936485</v>
       </c>
     </row>
@@ -6747,6 +7244,9 @@
         </is>
       </c>
       <c r="J166" t="n">
+        <v>11</v>
+      </c>
+      <c r="K166" t="n">
         <v>9.273348983270356</v>
       </c>
     </row>
@@ -6785,6 +7285,9 @@
         </is>
       </c>
       <c r="J167" t="n">
+        <v>11</v>
+      </c>
+      <c r="K167" t="n">
         <v>9.273348983270356</v>
       </c>
     </row>
@@ -6823,6 +7326,9 @@
         </is>
       </c>
       <c r="J168" t="n">
+        <v>11</v>
+      </c>
+      <c r="K168" t="n">
         <v>9.202805814248382</v>
       </c>
     </row>
@@ -6861,6 +7367,9 @@
         </is>
       </c>
       <c r="J169" t="n">
+        <v>11</v>
+      </c>
+      <c r="K169" t="n">
         <v>9.202805814248382</v>
       </c>
     </row>
@@ -6899,6 +7408,9 @@
         </is>
       </c>
       <c r="J170" t="n">
+        <v>11</v>
+      </c>
+      <c r="K170" t="n">
         <v>9.202805814248382</v>
       </c>
     </row>
@@ -6937,6 +7449,9 @@
         </is>
       </c>
       <c r="J171" t="n">
+        <v>11</v>
+      </c>
+      <c r="K171" t="n">
         <v>9.202805814248382</v>
       </c>
     </row>
@@ -6975,6 +7490,9 @@
         </is>
       </c>
       <c r="J172" t="n">
+        <v>11</v>
+      </c>
+      <c r="K172" t="n">
         <v>9.325700165492846</v>
       </c>
     </row>
@@ -7013,6 +7531,9 @@
         </is>
       </c>
       <c r="J173" t="n">
+        <v>11</v>
+      </c>
+      <c r="K173" t="n">
         <v>9.439273478382294</v>
       </c>
     </row>
@@ -7051,6 +7572,9 @@
         </is>
       </c>
       <c r="J174" t="n">
+        <v>13</v>
+      </c>
+      <c r="K174" t="n">
         <v>9.578592148482896</v>
       </c>
     </row>
@@ -7089,6 +7613,9 @@
         </is>
       </c>
       <c r="J175" t="n">
+        <v>13</v>
+      </c>
+      <c r="K175" t="n">
         <v>9.807680959686632</v>
       </c>
     </row>
@@ -7127,6 +7654,9 @@
         </is>
       </c>
       <c r="J176" t="n">
+        <v>13</v>
+      </c>
+      <c r="K176" t="n">
         <v>9.807680959686632</v>
       </c>
     </row>
@@ -7165,6 +7695,9 @@
         </is>
       </c>
       <c r="J177" t="n">
+        <v>13</v>
+      </c>
+      <c r="K177" t="n">
         <v>10.78022689352067</v>
       </c>
     </row>
@@ -7203,6 +7736,9 @@
         </is>
       </c>
       <c r="J178" t="n">
+        <v>13</v>
+      </c>
+      <c r="K178" t="n">
         <v>10.78022689352067</v>
       </c>
     </row>
@@ -7241,6 +7777,9 @@
         </is>
       </c>
       <c r="J179" t="n">
+        <v>13</v>
+      </c>
+      <c r="K179" t="n">
         <v>10.97632303694578</v>
       </c>
     </row>
@@ -7279,6 +7818,9 @@
         </is>
       </c>
       <c r="J180" t="n">
+        <v>13</v>
+      </c>
+      <c r="K180" t="n">
         <v>10.89437294526549</v>
       </c>
     </row>
@@ -7317,6 +7859,9 @@
         </is>
       </c>
       <c r="J181" t="n">
+        <v>13</v>
+      </c>
+      <c r="K181" t="n">
         <v>10.89437294526549</v>
       </c>
     </row>
@@ -7355,6 +7900,9 @@
         </is>
       </c>
       <c r="J182" t="n">
+        <v>13</v>
+      </c>
+      <c r="K182" t="n">
         <v>10.81042809243085</v>
       </c>
     </row>
@@ -7393,6 +7941,9 @@
         </is>
       </c>
       <c r="J183" t="n">
+        <v>13</v>
+      </c>
+      <c r="K183" t="n">
         <v>10.81042809243085</v>
       </c>
     </row>
@@ -7431,6 +7982,9 @@
         </is>
       </c>
       <c r="J184" t="n">
+        <v>13</v>
+      </c>
+      <c r="K184" t="n">
         <v>10.49792660516642</v>
       </c>
     </row>
@@ -7469,6 +8023,9 @@
         </is>
       </c>
       <c r="J185" t="n">
+        <v>13</v>
+      </c>
+      <c r="K185" t="n">
         <v>10.40823966094027</v>
       </c>
     </row>
@@ -7507,6 +8064,9 @@
         </is>
       </c>
       <c r="J186" t="n">
+        <v>13</v>
+      </c>
+      <c r="K186" t="n">
         <v>10.40234496133875</v>
       </c>
     </row>
@@ -7545,6 +8105,9 @@
         </is>
       </c>
       <c r="J187" t="n">
+        <v>13</v>
+      </c>
+      <c r="K187" t="n">
         <v>10.68338265109615</v>
       </c>
     </row>
@@ -7583,6 +8146,9 @@
         </is>
       </c>
       <c r="J188" t="n">
+        <v>12</v>
+      </c>
+      <c r="K188" t="n">
         <v>11.08605006924444</v>
       </c>
     </row>
@@ -7621,6 +8187,9 @@
         </is>
       </c>
       <c r="J189" t="n">
+        <v>12</v>
+      </c>
+      <c r="K189" t="n">
         <v>11.50207319071896</v>
       </c>
     </row>
@@ -7659,6 +8228,9 @@
         </is>
       </c>
       <c r="J190" t="n">
+        <v>12</v>
+      </c>
+      <c r="K190" t="n">
         <v>11.50207319071896</v>
       </c>
     </row>
@@ -7697,6 +8269,9 @@
         </is>
       </c>
       <c r="J191" t="n">
+        <v>12</v>
+      </c>
+      <c r="K191" t="n">
         <v>11.69557443787491</v>
       </c>
     </row>
@@ -7735,6 +8310,9 @@
         </is>
       </c>
       <c r="J192" t="n">
+        <v>12</v>
+      </c>
+      <c r="K192" t="n">
         <v>12.00427980342408</v>
       </c>
     </row>
@@ -7773,6 +8351,9 @@
         </is>
       </c>
       <c r="J193" t="n">
+        <v>12</v>
+      </c>
+      <c r="K193" t="n">
         <v>12.00427980342408</v>
       </c>
     </row>
@@ -7811,6 +8392,9 @@
         </is>
       </c>
       <c r="J194" t="n">
+        <v>12</v>
+      </c>
+      <c r="K194" t="n">
         <v>11.93485953365033</v>
       </c>
     </row>
@@ -7849,6 +8433,9 @@
         </is>
       </c>
       <c r="J195" t="n">
+        <v>12</v>
+      </c>
+      <c r="K195" t="n">
         <v>8.972531502131083</v>
       </c>
     </row>
@@ -7887,6 +8474,9 @@
         </is>
       </c>
       <c r="J196" t="n">
+        <v>12</v>
+      </c>
+      <c r="K196" t="n">
         <v>8.825164679350966</v>
       </c>
     </row>
@@ -7925,6 +8515,9 @@
         </is>
       </c>
       <c r="J197" t="n">
+        <v>12</v>
+      </c>
+      <c r="K197" t="n">
         <v>8.825164679350966</v>
       </c>
     </row>
@@ -7963,6 +8556,9 @@
         </is>
       </c>
       <c r="J198" t="n">
+        <v>12</v>
+      </c>
+      <c r="K198" t="n">
         <v>8.825164679350966</v>
       </c>
     </row>
@@ -8001,6 +8597,9 @@
         </is>
       </c>
       <c r="J199" t="n">
+        <v>12</v>
+      </c>
+      <c r="K199" t="n">
         <v>8.825164679350966</v>
       </c>
     </row>
@@ -8039,6 +8638,9 @@
         </is>
       </c>
       <c r="J200" t="n">
+        <v>12</v>
+      </c>
+      <c r="K200" t="n">
         <v>8.825164679350966</v>
       </c>
     </row>
@@ -8077,6 +8679,9 @@
         </is>
       </c>
       <c r="J201" t="n">
+        <v>12</v>
+      </c>
+      <c r="K201" t="n">
         <v>8.717469319399115</v>
       </c>
     </row>
@@ -8115,6 +8720,9 @@
         </is>
       </c>
       <c r="J202" t="n">
+        <v>12</v>
+      </c>
+      <c r="K202" t="n">
         <v>8.717469319399115</v>
       </c>
     </row>
@@ -8153,6 +8761,9 @@
         </is>
       </c>
       <c r="J203" t="n">
+        <v>12</v>
+      </c>
+      <c r="K203" t="n">
         <v>11.41624358709508</v>
       </c>
     </row>
@@ -8191,6 +8802,9 @@
         </is>
       </c>
       <c r="J204" t="n">
+        <v>12</v>
+      </c>
+      <c r="K204" t="n">
         <v>11.23747045773712</v>
       </c>
     </row>
@@ -8229,6 +8843,9 @@
         </is>
       </c>
       <c r="J205" t="n">
+        <v>12</v>
+      </c>
+      <c r="K205" t="n">
         <v>11.03780504665424</v>
       </c>
     </row>
@@ -8267,6 +8884,9 @@
         </is>
       </c>
       <c r="J206" t="n">
+        <v>12</v>
+      </c>
+      <c r="K206" t="n">
         <v>11.03780504665424</v>
       </c>
     </row>
@@ -8305,6 +8925,9 @@
         </is>
       </c>
       <c r="J207" t="n">
+        <v>12</v>
+      </c>
+      <c r="K207" t="n">
         <v>7.983917610806308</v>
       </c>
     </row>
@@ -8343,6 +8966,9 @@
         </is>
       </c>
       <c r="J208" t="n">
+        <v>12</v>
+      </c>
+      <c r="K208" t="n">
         <v>7.874938159898531</v>
       </c>
     </row>
@@ -8381,6 +9007,9 @@
         </is>
       </c>
       <c r="J209" t="n">
+        <v>12</v>
+      </c>
+      <c r="K209" t="n">
         <v>7.833592039957618</v>
       </c>
     </row>
@@ -8419,6 +9048,9 @@
         </is>
       </c>
       <c r="J210" t="n">
+        <v>12</v>
+      </c>
+      <c r="K210" t="n">
         <v>7.839185909153782</v>
       </c>
     </row>
@@ -8457,6 +9089,9 @@
         </is>
       </c>
       <c r="J211" t="n">
+        <v>12</v>
+      </c>
+      <c r="K211" t="n">
         <v>7.908825418622827</v>
       </c>
     </row>
@@ -8495,6 +9130,9 @@
         </is>
       </c>
       <c r="J212" t="n">
+        <v>12</v>
+      </c>
+      <c r="K212" t="n">
         <v>7.989403931656994</v>
       </c>
     </row>
@@ -8533,6 +9171,9 @@
         </is>
       </c>
       <c r="J213" t="n">
+        <v>12</v>
+      </c>
+      <c r="K213" t="n">
         <v>8.087241879725132</v>
       </c>
     </row>
@@ -8571,6 +9212,9 @@
         </is>
       </c>
       <c r="J214" t="n">
+        <v>12</v>
+      </c>
+      <c r="K214" t="n">
         <v>8.087241879725132</v>
       </c>
     </row>
@@ -8609,6 +9253,9 @@
         </is>
       </c>
       <c r="J215" t="n">
+        <v>12</v>
+      </c>
+      <c r="K215" t="n">
         <v>8.071607434598153</v>
       </c>
     </row>
@@ -8647,6 +9294,9 @@
         </is>
       </c>
       <c r="J216" t="n">
+        <v>12</v>
+      </c>
+      <c r="K216" t="n">
         <v>7.999783453159843</v>
       </c>
     </row>
@@ -8685,6 +9335,9 @@
         </is>
       </c>
       <c r="J217" t="n">
+        <v>12</v>
+      </c>
+      <c r="K217" t="n">
         <v>7.922922754105595</v>
       </c>
     </row>
@@ -8723,6 +9376,9 @@
         </is>
       </c>
       <c r="J218" t="n">
+        <v>12</v>
+      </c>
+      <c r="K218" t="n">
         <v>7.627780513808081</v>
       </c>
     </row>
@@ -8761,6 +9417,9 @@
         </is>
       </c>
       <c r="J219" t="n">
+        <v>12</v>
+      </c>
+      <c r="K219" t="n">
         <v>7.627780513808081</v>
       </c>
     </row>
@@ -8799,6 +9458,9 @@
         </is>
       </c>
       <c r="J220" t="n">
+        <v>12</v>
+      </c>
+      <c r="K220" t="n">
         <v>7.361633963936813</v>
       </c>
     </row>
@@ -8837,6 +9499,9 @@
         </is>
       </c>
       <c r="J221" t="n">
+        <v>12</v>
+      </c>
+      <c r="K221" t="n">
         <v>7.283758612994068</v>
       </c>
     </row>
@@ -8875,6 +9540,9 @@
         </is>
       </c>
       <c r="J222" t="n">
+        <v>12</v>
+      </c>
+      <c r="K222" t="n">
         <v>7.010906989830274</v>
       </c>
     </row>
@@ -8913,6 +9581,9 @@
         </is>
       </c>
       <c r="J223" t="n">
+        <v>12</v>
+      </c>
+      <c r="K223" t="n">
         <v>6.900876621016146</v>
       </c>
     </row>
@@ -8951,6 +9622,9 @@
         </is>
       </c>
       <c r="J224" t="n">
+        <v>12</v>
+      </c>
+      <c r="K224" t="n">
         <v>6.900876621016146</v>
       </c>
     </row>
@@ -8989,6 +9663,9 @@
         </is>
       </c>
       <c r="J225" t="n">
+        <v>12</v>
+      </c>
+      <c r="K225" t="n">
         <v>6.737143887697933</v>
       </c>
     </row>
@@ -9027,6 +9704,9 @@
         </is>
       </c>
       <c r="J226" t="n">
+        <v>12</v>
+      </c>
+      <c r="K226" t="n">
         <v>6.615940055742713</v>
       </c>
     </row>
@@ -9065,6 +9745,9 @@
         </is>
       </c>
       <c r="J227" t="n">
+        <v>12</v>
+      </c>
+      <c r="K227" t="n">
         <v>6.509331198307068</v>
       </c>
     </row>
@@ -9103,6 +9786,9 @@
         </is>
       </c>
       <c r="J228" t="n">
+        <v>12</v>
+      </c>
+      <c r="K228" t="n">
         <v>6.545151995917883</v>
       </c>
     </row>
@@ -9141,6 +9827,9 @@
         </is>
       </c>
       <c r="J229" t="n">
+        <v>12</v>
+      </c>
+      <c r="K229" t="n">
         <v>6.545151995917883</v>
       </c>
     </row>
@@ -9179,6 +9868,9 @@
         </is>
       </c>
       <c r="J230" t="n">
+        <v>12</v>
+      </c>
+      <c r="K230" t="n">
         <v>6.556691142523668</v>
       </c>
     </row>
@@ -9217,6 +9909,9 @@
         </is>
       </c>
       <c r="J231" t="n">
+        <v>12</v>
+      </c>
+      <c r="K231" t="n">
         <v>6.567497043644606</v>
       </c>
     </row>
@@ -9255,6 +9950,9 @@
         </is>
       </c>
       <c r="J232" t="n">
+        <v>12</v>
+      </c>
+      <c r="K232" t="n">
         <v>6.565789487972189</v>
       </c>
     </row>
@@ -9293,6 +9991,9 @@
         </is>
       </c>
       <c r="J233" t="n">
+        <v>12</v>
+      </c>
+      <c r="K233" t="n">
         <v>6.565789487972189</v>
       </c>
     </row>
@@ -9331,6 +10032,9 @@
         </is>
       </c>
       <c r="J234" t="n">
+        <v>12</v>
+      </c>
+      <c r="K234" t="n">
         <v>6.621840364929129</v>
       </c>
     </row>
@@ -9369,6 +10073,9 @@
         </is>
       </c>
       <c r="J235" t="n">
+        <v>12</v>
+      </c>
+      <c r="K235" t="n">
         <v>6.696952617143972</v>
       </c>
     </row>
@@ -9407,6 +10114,9 @@
         </is>
       </c>
       <c r="J236" t="n">
+        <v>12</v>
+      </c>
+      <c r="K236" t="n">
         <v>7.170545442462363</v>
       </c>
     </row>
@@ -9445,6 +10155,9 @@
         </is>
       </c>
       <c r="J237" t="n">
+        <v>12</v>
+      </c>
+      <c r="K237" t="n">
         <v>7.212529624014738</v>
       </c>
     </row>
@@ -9483,6 +10196,9 @@
         </is>
       </c>
       <c r="J238" t="n">
+        <v>12</v>
+      </c>
+      <c r="K238" t="n">
         <v>7.0694042275373</v>
       </c>
     </row>
@@ -9521,6 +10237,9 @@
         </is>
       </c>
       <c r="J239" t="n">
+        <v>12</v>
+      </c>
+      <c r="K239" t="n">
         <v>6.967208070103951</v>
       </c>
     </row>
@@ -9559,6 +10278,9 @@
         </is>
       </c>
       <c r="J240" t="n">
+        <v>12</v>
+      </c>
+      <c r="K240" t="n">
         <v>6.764525628379063</v>
       </c>
     </row>
@@ -9597,6 +10319,9 @@
         </is>
       </c>
       <c r="J241" t="n">
+        <v>12</v>
+      </c>
+      <c r="K241" t="n">
         <v>6.764525628379063</v>
       </c>
     </row>
@@ -9635,6 +10360,9 @@
         </is>
       </c>
       <c r="J242" t="n">
+        <v>12</v>
+      </c>
+      <c r="K242" t="n">
         <v>6.764525628379063</v>
       </c>
     </row>
@@ -9673,6 +10401,9 @@
         </is>
       </c>
       <c r="J243" t="n">
+        <v>12</v>
+      </c>
+      <c r="K243" t="n">
         <v>6.564601479006817</v>
       </c>
     </row>
@@ -9711,6 +10442,9 @@
         </is>
       </c>
       <c r="J244" t="n">
+        <v>12</v>
+      </c>
+      <c r="K244" t="n">
         <v>6.463719905980114</v>
       </c>
     </row>
@@ -9749,6 +10483,9 @@
         </is>
       </c>
       <c r="J245" t="n">
+        <v>12</v>
+      </c>
+      <c r="K245" t="n">
         <v>6.389770198074604</v>
       </c>
     </row>
@@ -9787,6 +10524,9 @@
         </is>
       </c>
       <c r="J246" t="n">
+        <v>12</v>
+      </c>
+      <c r="K246" t="n">
         <v>6.389770198074604</v>
       </c>
     </row>
@@ -9825,6 +10565,9 @@
         </is>
       </c>
       <c r="J247" t="n">
+        <v>12</v>
+      </c>
+      <c r="K247" t="n">
         <v>6.35355459678128</v>
       </c>
     </row>
@@ -9863,6 +10606,9 @@
         </is>
       </c>
       <c r="J248" t="n">
+        <v>12</v>
+      </c>
+      <c r="K248" t="n">
         <v>6.35355459678128</v>
       </c>
     </row>
@@ -9901,6 +10647,9 @@
         </is>
       </c>
       <c r="J249" t="n">
+        <v>12</v>
+      </c>
+      <c r="K249" t="n">
         <v>6.395779791869125</v>
       </c>
     </row>
@@ -9939,6 +10688,9 @@
         </is>
       </c>
       <c r="J250" t="n">
+        <v>12</v>
+      </c>
+      <c r="K250" t="n">
         <v>6.406404875695161</v>
       </c>
     </row>
@@ -9977,6 +10729,9 @@
         </is>
       </c>
       <c r="J251" t="n">
+        <v>12</v>
+      </c>
+      <c r="K251" t="n">
         <v>6.441383269673444</v>
       </c>
     </row>
@@ -10015,6 +10770,9 @@
         </is>
       </c>
       <c r="J252" t="n">
+        <v>12</v>
+      </c>
+      <c r="K252" t="n">
         <v>6.507154901965544</v>
       </c>
     </row>
@@ -10053,6 +10811,9 @@
         </is>
       </c>
       <c r="J253" t="n">
+        <v>12</v>
+      </c>
+      <c r="K253" t="n">
         <v>6.507154901965544</v>
       </c>
     </row>
@@ -10091,6 +10852,9 @@
         </is>
       </c>
       <c r="J254" t="n">
+        <v>12</v>
+      </c>
+      <c r="K254" t="n">
         <v>6.624889237190102</v>
       </c>
     </row>
@@ -10129,6 +10893,9 @@
         </is>
       </c>
       <c r="J255" t="n">
+        <v>12</v>
+      </c>
+      <c r="K255" t="n">
         <v>6.694697108167018</v>
       </c>
     </row>
@@ -10167,6 +10934,9 @@
         </is>
       </c>
       <c r="J256" t="n">
+        <v>12</v>
+      </c>
+      <c r="K256" t="n">
         <v>6.689351826243123</v>
       </c>
     </row>
@@ -10205,6 +10975,9 @@
         </is>
       </c>
       <c r="J257" t="n">
+        <v>12</v>
+      </c>
+      <c r="K257" t="n">
         <v>6.645961708125747</v>
       </c>
     </row>
@@ -10243,6 +11016,9 @@
         </is>
       </c>
       <c r="J258" t="n">
+        <v>12</v>
+      </c>
+      <c r="K258" t="n">
         <v>6.645961708125747</v>
       </c>
     </row>
@@ -10281,6 +11057,9 @@
         </is>
       </c>
       <c r="J259" t="n">
+        <v>12</v>
+      </c>
+      <c r="K259" t="n">
         <v>6.595609736742639</v>
       </c>
     </row>
@@ -10319,6 +11098,9 @@
         </is>
       </c>
       <c r="J260" t="n">
+        <v>12</v>
+      </c>
+      <c r="K260" t="n">
         <v>6.519483198421881</v>
       </c>
     </row>
@@ -10357,6 +11139,9 @@
         </is>
       </c>
       <c r="J261" t="n">
+        <v>12</v>
+      </c>
+      <c r="K261" t="n">
         <v>6.519483198421881</v>
       </c>
     </row>
@@ -10395,6 +11180,9 @@
         </is>
       </c>
       <c r="J262" t="n">
+        <v>12</v>
+      </c>
+      <c r="K262" t="n">
         <v>6.519483198421881</v>
       </c>
     </row>
@@ -10433,6 +11221,9 @@
         </is>
       </c>
       <c r="J263" t="n">
+        <v>12</v>
+      </c>
+      <c r="K263" t="n">
         <v>6.443409971077021</v>
       </c>
     </row>
@@ -10471,6 +11262,9 @@
         </is>
       </c>
       <c r="J264" t="n">
+        <v>12</v>
+      </c>
+      <c r="K264" t="n">
         <v>6.349420864135906</v>
       </c>
     </row>
@@ -10509,6 +11303,9 @@
         </is>
       </c>
       <c r="J265" t="n">
+        <v>12</v>
+      </c>
+      <c r="K265" t="n">
         <v>6.349420864135906</v>
       </c>
     </row>
@@ -10547,6 +11344,9 @@
         </is>
       </c>
       <c r="J266" t="n">
+        <v>12</v>
+      </c>
+      <c r="K266" t="n">
         <v>6.225251898711105</v>
       </c>
     </row>
@@ -10585,6 +11385,9 @@
         </is>
       </c>
       <c r="J267" t="n">
+        <v>12</v>
+      </c>
+      <c r="K267" t="n">
         <v>6.225251898711105</v>
       </c>
     </row>
@@ -10623,6 +11426,9 @@
         </is>
       </c>
       <c r="J268" t="n">
+        <v>12</v>
+      </c>
+      <c r="K268" t="n">
         <v>5.927076537069531</v>
       </c>
     </row>
@@ -10661,6 +11467,9 @@
         </is>
       </c>
       <c r="J269" t="n">
+        <v>12</v>
+      </c>
+      <c r="K269" t="n">
         <v>5.927076537069531</v>
       </c>
     </row>
@@ -10699,6 +11508,9 @@
         </is>
       </c>
       <c r="J270" t="n">
+        <v>12</v>
+      </c>
+      <c r="K270" t="n">
         <v>5.927076537069531</v>
       </c>
     </row>
@@ -10737,6 +11549,9 @@
         </is>
       </c>
       <c r="J271" t="n">
+        <v>12</v>
+      </c>
+      <c r="K271" t="n">
         <v>5.68721867829009</v>
       </c>
     </row>
@@ -10775,6 +11590,9 @@
         </is>
       </c>
       <c r="J272" t="n">
+        <v>12</v>
+      </c>
+      <c r="K272" t="n">
         <v>5.68721867829009</v>
       </c>
     </row>
@@ -10813,6 +11631,9 @@
         </is>
       </c>
       <c r="J273" t="n">
+        <v>12</v>
+      </c>
+      <c r="K273" t="n">
         <v>5.556439618384283</v>
       </c>
     </row>
@@ -10851,6 +11672,9 @@
         </is>
       </c>
       <c r="J274" t="n">
+        <v>12</v>
+      </c>
+      <c r="K274" t="n">
         <v>5.556439618384283</v>
       </c>
     </row>
@@ -10889,6 +11713,9 @@
         </is>
       </c>
       <c r="J275" t="n">
+        <v>12</v>
+      </c>
+      <c r="K275" t="n">
         <v>5.523015648608387</v>
       </c>
     </row>
@@ -10927,6 +11754,9 @@
         </is>
       </c>
       <c r="J276" t="n">
+        <v>12</v>
+      </c>
+      <c r="K276" t="n">
         <v>5.484651274469442</v>
       </c>
     </row>
@@ -10965,6 +11795,9 @@
         </is>
       </c>
       <c r="J277" t="n">
+        <v>12</v>
+      </c>
+      <c r="K277" t="n">
         <v>5.403615753763492</v>
       </c>
     </row>
@@ -11003,6 +11836,9 @@
         </is>
       </c>
       <c r="J278" t="n">
+        <v>12</v>
+      </c>
+      <c r="K278" t="n">
         <v>5.400035531057761</v>
       </c>
     </row>
@@ -11041,6 +11877,9 @@
         </is>
       </c>
       <c r="J279" t="n">
+        <v>12</v>
+      </c>
+      <c r="K279" t="n">
         <v>5.430625940103638</v>
       </c>
     </row>
@@ -11079,6 +11918,9 @@
         </is>
       </c>
       <c r="J280" t="n">
+        <v>12</v>
+      </c>
+      <c r="K280" t="n">
         <v>5.439540654494466</v>
       </c>
     </row>
@@ -11117,6 +11959,9 @@
         </is>
       </c>
       <c r="J281" t="n">
+        <v>12</v>
+      </c>
+      <c r="K281" t="n">
         <v>5.43045252735542</v>
       </c>
     </row>
@@ -11155,6 +12000,9 @@
         </is>
       </c>
       <c r="J282" t="n">
+        <v>12</v>
+      </c>
+      <c r="K282" t="n">
         <v>5.43045252735542</v>
       </c>
     </row>
@@ -11193,6 +12041,9 @@
         </is>
       </c>
       <c r="J283" t="n">
+        <v>12</v>
+      </c>
+      <c r="K283" t="n">
         <v>5.425405849969438</v>
       </c>
     </row>
@@ -11231,6 +12082,9 @@
         </is>
       </c>
       <c r="J284" t="n">
+        <v>12</v>
+      </c>
+      <c r="K284" t="n">
         <v>5.488011913313641</v>
       </c>
     </row>
@@ -11269,6 +12123,9 @@
         </is>
       </c>
       <c r="J285" t="n">
+        <v>12</v>
+      </c>
+      <c r="K285" t="n">
         <v>5.489626248972863</v>
       </c>
     </row>
@@ -11307,6 +12164,9 @@
         </is>
       </c>
       <c r="J286" t="n">
+        <v>12</v>
+      </c>
+      <c r="K286" t="n">
         <v>5.467548055619861</v>
       </c>
     </row>
@@ -11345,6 +12205,9 @@
         </is>
       </c>
       <c r="J287" t="n">
+        <v>12</v>
+      </c>
+      <c r="K287" t="n">
         <v>5.416349643311261</v>
       </c>
     </row>
@@ -11383,6 +12246,9 @@
         </is>
       </c>
       <c r="J288" t="n">
+        <v>12</v>
+      </c>
+      <c r="K288" t="n">
         <v>5.137232169365259</v>
       </c>
     </row>
@@ -11421,6 +12287,9 @@
         </is>
       </c>
       <c r="J289" t="n">
+        <v>12</v>
+      </c>
+      <c r="K289" t="n">
         <v>5.137232169365259</v>
       </c>
     </row>
@@ -11459,6 +12328,9 @@
         </is>
       </c>
       <c r="J290" t="n">
+        <v>12</v>
+      </c>
+      <c r="K290" t="n">
         <v>4.987184047266204</v>
       </c>
     </row>
@@ -11497,6 +12369,9 @@
         </is>
       </c>
       <c r="J291" t="n">
+        <v>12</v>
+      </c>
+      <c r="K291" t="n">
         <v>4.917981624850995</v>
       </c>
     </row>
@@ -11535,6 +12410,9 @@
         </is>
       </c>
       <c r="J292" t="n">
+        <v>12</v>
+      </c>
+      <c r="K292" t="n">
         <v>4.768398390704161</v>
       </c>
     </row>
@@ -11573,6 +12451,9 @@
         </is>
       </c>
       <c r="J293" t="n">
+        <v>12</v>
+      </c>
+      <c r="K293" t="n">
         <v>4.768398390704161</v>
       </c>
     </row>
@@ -11611,6 +12492,9 @@
         </is>
       </c>
       <c r="J294" t="n">
+        <v>12</v>
+      </c>
+      <c r="K294" t="n">
         <v>4.671140657024297</v>
       </c>
     </row>
@@ -11649,6 +12533,9 @@
         </is>
       </c>
       <c r="J295" t="n">
+        <v>12</v>
+      </c>
+      <c r="K295" t="n">
         <v>4.497705336003175</v>
       </c>
     </row>
@@ -11687,6 +12574,9 @@
         </is>
       </c>
       <c r="J296" t="n">
+        <v>12</v>
+      </c>
+      <c r="K296" t="n">
         <v>4.497705336003175</v>
       </c>
     </row>
@@ -11725,6 +12615,9 @@
         </is>
       </c>
       <c r="J297" t="n">
+        <v>12</v>
+      </c>
+      <c r="K297" t="n">
         <v>4.446491173816532</v>
       </c>
     </row>
@@ -11763,6 +12656,9 @@
         </is>
       </c>
       <c r="J298" t="n">
+        <v>12</v>
+      </c>
+      <c r="K298" t="n">
         <v>4.462156526447973</v>
       </c>
     </row>
@@ -11801,6 +12697,9 @@
         </is>
       </c>
       <c r="J299" t="n">
+        <v>12</v>
+      </c>
+      <c r="K299" t="n">
         <v>4.462156526447973</v>
       </c>
     </row>
@@ -11839,6 +12738,9 @@
         </is>
       </c>
       <c r="J300" t="n">
+        <v>12</v>
+      </c>
+      <c r="K300" t="n">
         <v>4.572961837477169</v>
       </c>
     </row>
@@ -11877,6 +12779,9 @@
         </is>
       </c>
       <c r="J301" t="n">
+        <v>12</v>
+      </c>
+      <c r="K301" t="n">
         <v>4.72510881093438</v>
       </c>
     </row>
@@ -11915,6 +12820,9 @@
         </is>
       </c>
       <c r="J302" t="n">
+        <v>12</v>
+      </c>
+      <c r="K302" t="n">
         <v>4.781057602797377</v>
       </c>
     </row>
@@ -11953,6 +12861,9 @@
         </is>
       </c>
       <c r="J303" t="n">
+        <v>12</v>
+      </c>
+      <c r="K303" t="n">
         <v>4.772145484469391</v>
       </c>
     </row>
@@ -11991,6 +12902,9 @@
         </is>
       </c>
       <c r="J304" t="n">
+        <v>12</v>
+      </c>
+      <c r="K304" t="n">
         <v>4.766457804572893</v>
       </c>
     </row>
@@ -12029,6 +12943,9 @@
         </is>
       </c>
       <c r="J305" t="n">
+        <v>12</v>
+      </c>
+      <c r="K305" t="n">
         <v>4.675680197889633</v>
       </c>
     </row>
@@ -12067,6 +12984,9 @@
         </is>
       </c>
       <c r="J306" t="n">
+        <v>12</v>
+      </c>
+      <c r="K306" t="n">
         <v>4.675680197889633</v>
       </c>
     </row>
@@ -12105,6 +13025,9 @@
         </is>
       </c>
       <c r="J307" t="n">
+        <v>12</v>
+      </c>
+      <c r="K307" t="n">
         <v>4.635708280844956</v>
       </c>
     </row>
@@ -12143,6 +13066,9 @@
         </is>
       </c>
       <c r="J308" t="n">
+        <v>12</v>
+      </c>
+      <c r="K308" t="n">
         <v>4.584732320464307</v>
       </c>
     </row>
@@ -12181,6 +13107,9 @@
         </is>
       </c>
       <c r="J309" t="n">
+        <v>12</v>
+      </c>
+      <c r="K309" t="n">
         <v>4.471231750790213</v>
       </c>
     </row>
@@ -12219,6 +13148,9 @@
         </is>
       </c>
       <c r="J310" t="n">
+        <v>12</v>
+      </c>
+      <c r="K310" t="n">
         <v>4.341696963043866</v>
       </c>
     </row>
@@ -12257,6 +13189,9 @@
         </is>
       </c>
       <c r="J311" t="n">
+        <v>12</v>
+      </c>
+      <c r="K311" t="n">
         <v>4.341696963043866</v>
       </c>
     </row>
@@ -12295,6 +13230,9 @@
         </is>
       </c>
       <c r="J312" t="n">
+        <v>12</v>
+      </c>
+      <c r="K312" t="n">
         <v>4.029491631604353</v>
       </c>
     </row>
@@ -12333,6 +13271,9 @@
         </is>
       </c>
       <c r="J313" t="n">
+        <v>12</v>
+      </c>
+      <c r="K313" t="n">
         <v>3.953661586598497</v>
       </c>
     </row>
@@ -12371,6 +13312,9 @@
         </is>
       </c>
       <c r="J314" t="n">
+        <v>12</v>
+      </c>
+      <c r="K314" t="n">
         <v>3.894104479925181</v>
       </c>
     </row>
@@ -12409,6 +13353,9 @@
         </is>
       </c>
       <c r="J315" t="n">
+        <v>12</v>
+      </c>
+      <c r="K315" t="n">
         <v>3.86504784315993</v>
       </c>
     </row>
@@ -12447,6 +13394,9 @@
         </is>
       </c>
       <c r="J316" t="n">
+        <v>12</v>
+      </c>
+      <c r="K316" t="n">
         <v>3.865919170884787</v>
       </c>
     </row>
@@ -12485,6 +13435,9 @@
         </is>
       </c>
       <c r="J317" t="n">
+        <v>12</v>
+      </c>
+      <c r="K317" t="n">
         <v>3.89903790537417</v>
       </c>
     </row>
@@ -12523,6 +13476,9 @@
         </is>
       </c>
       <c r="J318" t="n">
+        <v>12</v>
+      </c>
+      <c r="K318" t="n">
         <v>3.89903790537417</v>
       </c>
     </row>
@@ -12561,6 +13517,9 @@
         </is>
       </c>
       <c r="J319" t="n">
+        <v>12</v>
+      </c>
+      <c r="K319" t="n">
         <v>3.998180962922512</v>
       </c>
     </row>
@@ -12599,6 +13558,9 @@
         </is>
       </c>
       <c r="J320" t="n">
+        <v>12</v>
+      </c>
+      <c r="K320" t="n">
         <v>3.998180962922512</v>
       </c>
     </row>
@@ -12637,6 +13599,9 @@
         </is>
       </c>
       <c r="J321" t="n">
+        <v>12</v>
+      </c>
+      <c r="K321" t="n">
         <v>4.155107285102944</v>
       </c>
     </row>
@@ -12675,6 +13640,9 @@
         </is>
       </c>
       <c r="J322" t="n">
+        <v>12</v>
+      </c>
+      <c r="K322" t="n">
         <v>4.208420499246</v>
       </c>
     </row>
@@ -12713,6 +13681,9 @@
         </is>
       </c>
       <c r="J323" t="n">
+        <v>12</v>
+      </c>
+      <c r="K323" t="n">
         <v>4.208420499246</v>
       </c>
     </row>
@@ -12751,6 +13722,9 @@
         </is>
       </c>
       <c r="J324" t="n">
+        <v>12</v>
+      </c>
+      <c r="K324" t="n">
         <v>4.253280651244157</v>
       </c>
     </row>
@@ -12789,6 +13763,9 @@
         </is>
       </c>
       <c r="J325" t="n">
+        <v>12</v>
+      </c>
+      <c r="K325" t="n">
         <v>4.253280651244157</v>
       </c>
     </row>
@@ -12827,6 +13804,9 @@
         </is>
       </c>
       <c r="J326" t="n">
+        <v>12</v>
+      </c>
+      <c r="K326" t="n">
         <v>4.204984097251353</v>
       </c>
     </row>
@@ -12865,6 +13845,9 @@
         </is>
       </c>
       <c r="J327" t="n">
+        <v>12</v>
+      </c>
+      <c r="K327" t="n">
         <v>4.11856228728011</v>
       </c>
     </row>
@@ -12903,6 +13886,9 @@
         </is>
       </c>
       <c r="J328" t="n">
+        <v>12</v>
+      </c>
+      <c r="K328" t="n">
         <v>4.11856228728011</v>
       </c>
     </row>
@@ -12941,6 +13927,9 @@
         </is>
       </c>
       <c r="J329" t="n">
+        <v>12</v>
+      </c>
+      <c r="K329" t="n">
         <v>4.016052122628828</v>
       </c>
     </row>
@@ -12979,6 +13968,9 @@
         </is>
       </c>
       <c r="J330" t="n">
+        <v>12</v>
+      </c>
+      <c r="K330" t="n">
         <v>4.016052122628828</v>
       </c>
     </row>
@@ -13017,6 +14009,9 @@
         </is>
       </c>
       <c r="J331" t="n">
+        <v>12</v>
+      </c>
+      <c r="K331" t="n">
         <v>4.016052122628828</v>
       </c>
     </row>
@@ -13055,6 +14050,9 @@
         </is>
       </c>
       <c r="J332" t="n">
+        <v>12</v>
+      </c>
+      <c r="K332" t="n">
         <v>3.976864467947827</v>
       </c>
     </row>
@@ -13093,6 +14091,9 @@
         </is>
       </c>
       <c r="J333" t="n">
+        <v>12</v>
+      </c>
+      <c r="K333" t="n">
         <v>3.829368804988613</v>
       </c>
     </row>
@@ -13131,6 +14132,9 @@
         </is>
       </c>
       <c r="J334" t="n">
+        <v>12</v>
+      </c>
+      <c r="K334" t="n">
         <v>3.717309882233985</v>
       </c>
     </row>
@@ -13169,6 +14173,9 @@
         </is>
       </c>
       <c r="J335" t="n">
+        <v>12</v>
+      </c>
+      <c r="K335" t="n">
         <v>3.717309882233985</v>
       </c>
     </row>
@@ -13207,6 +14214,9 @@
         </is>
       </c>
       <c r="J336" t="n">
+        <v>12</v>
+      </c>
+      <c r="K336" t="n">
         <v>3.601248552599805</v>
       </c>
     </row>
@@ -13245,6 +14255,9 @@
         </is>
       </c>
       <c r="J337" t="n">
+        <v>12</v>
+      </c>
+      <c r="K337" t="n">
         <v>3.614569184025537</v>
       </c>
     </row>
@@ -13283,6 +14296,9 @@
         </is>
       </c>
       <c r="J338" t="n">
+        <v>12</v>
+      </c>
+      <c r="K338" t="n">
         <v>3.614569184025537</v>
       </c>
     </row>
@@ -13321,6 +14337,9 @@
         </is>
       </c>
       <c r="J339" t="n">
+        <v>12</v>
+      </c>
+      <c r="K339" t="n">
         <v>3.642804970467443</v>
       </c>
     </row>
@@ -13359,6 +14378,9 @@
         </is>
       </c>
       <c r="J340" t="n">
+        <v>12</v>
+      </c>
+      <c r="K340" t="n">
         <v>3.651275254337981</v>
       </c>
     </row>
@@ -13397,6 +14419,9 @@
         </is>
       </c>
       <c r="J341" t="n">
+        <v>12</v>
+      </c>
+      <c r="K341" t="n">
         <v>3.726089902536564</v>
       </c>
     </row>
@@ -13435,6 +14460,9 @@
         </is>
       </c>
       <c r="J342" t="n">
+        <v>12</v>
+      </c>
+      <c r="K342" t="n">
         <v>3.716238914904418</v>
       </c>
     </row>
@@ -13473,6 +14501,9 @@
         </is>
       </c>
       <c r="J343" t="n">
+        <v>12</v>
+      </c>
+      <c r="K343" t="n">
         <v>3.647636927009276</v>
       </c>
     </row>
@@ -13511,6 +14542,9 @@
         </is>
       </c>
       <c r="J344" t="n">
+        <v>12</v>
+      </c>
+      <c r="K344" t="n">
         <v>3.616428472844463</v>
       </c>
     </row>
@@ -13549,6 +14583,9 @@
         </is>
       </c>
       <c r="J345" t="n">
+        <v>12</v>
+      </c>
+      <c r="K345" t="n">
         <v>3.544939488492044</v>
       </c>
     </row>
@@ -13587,6 +14624,9 @@
         </is>
       </c>
       <c r="J346" t="n">
+        <v>12</v>
+      </c>
+      <c r="K346" t="n">
         <v>3.442828928590163</v>
       </c>
     </row>
@@ -13625,6 +14665,9 @@
         </is>
       </c>
       <c r="J347" t="n">
+        <v>12</v>
+      </c>
+      <c r="K347" t="n">
         <v>3.442828928590163</v>
       </c>
     </row>
@@ -13663,6 +14706,9 @@
         </is>
       </c>
       <c r="J348" t="n">
+        <v>12</v>
+      </c>
+      <c r="K348" t="n">
         <v>3.224479238105011</v>
       </c>
     </row>
@@ -13701,6 +14747,9 @@
         </is>
       </c>
       <c r="J349" t="n">
+        <v>12</v>
+      </c>
+      <c r="K349" t="n">
         <v>3.179660949132971</v>
       </c>
     </row>
@@ -13739,6 +14788,9 @@
         </is>
       </c>
       <c r="J350" t="n">
+        <v>12</v>
+      </c>
+      <c r="K350" t="n">
         <v>3.141739571348284</v>
       </c>
     </row>
@@ -13777,6 +14829,9 @@
         </is>
       </c>
       <c r="J351" t="n">
+        <v>12</v>
+      </c>
+      <c r="K351" t="n">
         <v>3.103576179581915</v>
       </c>
     </row>
@@ -13815,6 +14870,9 @@
         </is>
       </c>
       <c r="J352" t="n">
+        <v>12</v>
+      </c>
+      <c r="K352" t="n">
         <v>3.271625035111303</v>
       </c>
     </row>
@@ -13853,6 +14911,9 @@
         </is>
       </c>
       <c r="J353" t="n">
+        <v>12</v>
+      </c>
+      <c r="K353" t="n">
         <v>3.332028071578465</v>
       </c>
     </row>
@@ -13891,6 +14952,9 @@
         </is>
       </c>
       <c r="J354" t="n">
+        <v>12</v>
+      </c>
+      <c r="K354" t="n">
         <v>3.39264960925539</v>
       </c>
     </row>
@@ -13929,6 +14993,9 @@
         </is>
       </c>
       <c r="J355" t="n">
+        <v>12</v>
+      </c>
+      <c r="K355" t="n">
         <v>3.39264960925539</v>
       </c>
     </row>
@@ -13967,6 +15034,9 @@
         </is>
       </c>
       <c r="J356" t="n">
+        <v>12</v>
+      </c>
+      <c r="K356" t="n">
         <v>3.681023701356659</v>
       </c>
     </row>
@@ -14005,6 +15075,9 @@
         </is>
       </c>
       <c r="J357" t="n">
+        <v>12</v>
+      </c>
+      <c r="K357" t="n">
         <v>3.681023701356659</v>
       </c>
     </row>
@@ -14043,6 +15116,9 @@
         </is>
       </c>
       <c r="J358" t="n">
+        <v>12</v>
+      </c>
+      <c r="K358" t="n">
         <v>3.681023701356659</v>
       </c>
     </row>
@@ -14081,6 +15157,9 @@
         </is>
       </c>
       <c r="J359" t="n">
+        <v>12</v>
+      </c>
+      <c r="K359" t="n">
         <v>3.681023701356659</v>
       </c>
     </row>
@@ -14119,6 +15198,9 @@
         </is>
       </c>
       <c r="J360" t="n">
+        <v>12</v>
+      </c>
+      <c r="K360" t="n">
         <v>3.93497382716593</v>
       </c>
     </row>
@@ -14157,6 +15239,9 @@
         </is>
       </c>
       <c r="J361" t="n">
+        <v>12</v>
+      </c>
+      <c r="K361" t="n">
         <v>3.93497382716593</v>
       </c>
     </row>
@@ -14195,6 +15280,9 @@
         </is>
       </c>
       <c r="J362" t="n">
+        <v>12</v>
+      </c>
+      <c r="K362" t="n">
         <v>3.93497382716593</v>
       </c>
     </row>
@@ -14233,6 +15321,9 @@
         </is>
       </c>
       <c r="J363" t="n">
+        <v>12</v>
+      </c>
+      <c r="K363" t="n">
         <v>4.046355328597745</v>
       </c>
     </row>
@@ -14271,6 +15362,9 @@
         </is>
       </c>
       <c r="J364" t="n">
+        <v>12</v>
+      </c>
+      <c r="K364" t="n">
         <v>4.094965680458862</v>
       </c>
     </row>
@@ -14309,6 +15403,9 @@
         </is>
       </c>
       <c r="J365" t="n">
+        <v>12</v>
+      </c>
+      <c r="K365" t="n">
         <v>4.090511017821964</v>
       </c>
     </row>
@@ -14347,6 +15444,9 @@
         </is>
       </c>
       <c r="J366" t="n">
+        <v>12</v>
+      </c>
+      <c r="K366" t="n">
         <v>4.079853526575469</v>
       </c>
     </row>
@@ -14385,6 +15485,9 @@
         </is>
       </c>
       <c r="J367" t="n">
+        <v>12</v>
+      </c>
+      <c r="K367" t="n">
         <v>4.064424058259151</v>
       </c>
     </row>
@@ -14423,6 +15526,9 @@
         </is>
       </c>
       <c r="J368" t="n">
+        <v>12</v>
+      </c>
+      <c r="K368" t="n">
         <v>4.064424058259151</v>
       </c>
     </row>
@@ -14461,6 +15567,9 @@
         </is>
       </c>
       <c r="J369" t="n">
+        <v>12</v>
+      </c>
+      <c r="K369" t="n">
         <v>4.051274663213008</v>
       </c>
     </row>
@@ -14499,6 +15608,9 @@
         </is>
       </c>
       <c r="J370" t="n">
+        <v>12</v>
+      </c>
+      <c r="K370" t="n">
         <v>4.032416532855316</v>
       </c>
     </row>
@@ -14537,6 +15649,9 @@
         </is>
       </c>
       <c r="J371" t="n">
+        <v>12</v>
+      </c>
+      <c r="K371" t="n">
         <v>3.995798035708694</v>
       </c>
     </row>
@@ -14575,6 +15690,9 @@
         </is>
       </c>
       <c r="J372" t="n">
+        <v>12</v>
+      </c>
+      <c r="K372" t="n">
         <v>3.904937929069707</v>
       </c>
     </row>
@@ -14613,6 +15731,9 @@
         </is>
       </c>
       <c r="J373" t="n">
+        <v>12</v>
+      </c>
+      <c r="K373" t="n">
         <v>3.904937929069707</v>
       </c>
     </row>
@@ -14651,6 +15772,9 @@
         </is>
       </c>
       <c r="J374" t="n">
+        <v>12</v>
+      </c>
+      <c r="K374" t="n">
         <v>3.902325182219681</v>
       </c>
     </row>
@@ -14689,6 +15813,9 @@
         </is>
       </c>
       <c r="J375" t="n">
+        <v>12</v>
+      </c>
+      <c r="K375" t="n">
         <v>3.902325182219681</v>
       </c>
     </row>
@@ -14727,6 +15854,9 @@
         </is>
       </c>
       <c r="J376" t="n">
+        <v>12</v>
+      </c>
+      <c r="K376" t="n">
         <v>3.89954908275964</v>
       </c>
     </row>
@@ -14765,6 +15895,9 @@
         </is>
       </c>
       <c r="J377" t="n">
+        <v>12</v>
+      </c>
+      <c r="K377" t="n">
         <v>3.81604229559243</v>
       </c>
     </row>
@@ -14803,6 +15936,9 @@
         </is>
       </c>
       <c r="J378" t="n">
+        <v>12</v>
+      </c>
+      <c r="K378" t="n">
         <v>3.81604229559243</v>
       </c>
     </row>
@@ -14841,6 +15977,9 @@
         </is>
       </c>
       <c r="J379" t="n">
+        <v>12</v>
+      </c>
+      <c r="K379" t="n">
         <v>3.81604229559243</v>
       </c>
     </row>
@@ -14879,6 +16018,9 @@
         </is>
       </c>
       <c r="J380" t="n">
+        <v>12</v>
+      </c>
+      <c r="K380" t="n">
         <v>3.747192771849555</v>
       </c>
     </row>
@@ -14917,6 +16059,9 @@
         </is>
       </c>
       <c r="J381" t="n">
+        <v>12</v>
+      </c>
+      <c r="K381" t="n">
         <v>3.747192771849555</v>
       </c>
     </row>
@@ -14955,6 +16100,9 @@
         </is>
       </c>
       <c r="J382" t="n">
+        <v>12</v>
+      </c>
+      <c r="K382" t="n">
         <v>3.716400996354732</v>
       </c>
     </row>
@@ -14993,6 +16141,9 @@
         </is>
       </c>
       <c r="J383" t="n">
+        <v>12</v>
+      </c>
+      <c r="K383" t="n">
         <v>3.716400996354732</v>
       </c>
     </row>
@@ -15031,6 +16182,9 @@
         </is>
       </c>
       <c r="J384" t="n">
+        <v>12</v>
+      </c>
+      <c r="K384" t="n">
         <v>3.695657682922242</v>
       </c>
     </row>
@@ -15069,6 +16223,9 @@
         </is>
       </c>
       <c r="J385" t="n">
+        <v>12</v>
+      </c>
+      <c r="K385" t="n">
         <v>3.7069232042469</v>
       </c>
     </row>
@@ -15107,6 +16264,9 @@
         </is>
       </c>
       <c r="J386" t="n">
+        <v>12</v>
+      </c>
+      <c r="K386" t="n">
         <v>3.7069232042469</v>
       </c>
     </row>
@@ -15145,6 +16305,9 @@
         </is>
       </c>
       <c r="J387" t="n">
+        <v>12</v>
+      </c>
+      <c r="K387" t="n">
         <v>3.727054906519708</v>
       </c>
     </row>
@@ -15183,6 +16346,9 @@
         </is>
       </c>
       <c r="J388" t="n">
+        <v>12</v>
+      </c>
+      <c r="K388" t="n">
         <v>3.727485012341275</v>
       </c>
     </row>
@@ -15221,6 +16387,9 @@
         </is>
       </c>
       <c r="J389" t="n">
+        <v>12</v>
+      </c>
+      <c r="K389" t="n">
         <v>3.777891374981178</v>
       </c>
     </row>
@@ -15259,6 +16428,9 @@
         </is>
       </c>
       <c r="J390" t="n">
+        <v>12</v>
+      </c>
+      <c r="K390" t="n">
         <v>3.777891374981178</v>
       </c>
     </row>
@@ -15297,6 +16469,9 @@
         </is>
       </c>
       <c r="J391" t="n">
+        <v>12</v>
+      </c>
+      <c r="K391" t="n">
         <v>3.927068517355079</v>
       </c>
     </row>
@@ -15335,6 +16510,9 @@
         </is>
       </c>
       <c r="J392" t="n">
+        <v>12</v>
+      </c>
+      <c r="K392" t="n">
         <v>3.942216011569942</v>
       </c>
     </row>
@@ -15373,6 +16551,9 @@
         </is>
       </c>
       <c r="J393" t="n">
+        <v>12</v>
+      </c>
+      <c r="K393" t="n">
         <v>3.910924677918464</v>
       </c>
     </row>
@@ -15411,6 +16592,9 @@
         </is>
       </c>
       <c r="J394" t="n">
+        <v>12</v>
+      </c>
+      <c r="K394" t="n">
         <v>3.646452506582347</v>
       </c>
     </row>
@@ -15449,6 +16633,9 @@
         </is>
       </c>
       <c r="J395" t="n">
+        <v>12</v>
+      </c>
+      <c r="K395" t="n">
         <v>3.646452506582347</v>
       </c>
     </row>
@@ -15487,6 +16674,9 @@
         </is>
       </c>
       <c r="J396" t="n">
+        <v>12</v>
+      </c>
+      <c r="K396" t="n">
         <v>3.330273535484118</v>
       </c>
     </row>
@@ -15525,6 +16715,9 @@
         </is>
       </c>
       <c r="J397" t="n">
+        <v>12</v>
+      </c>
+      <c r="K397" t="n">
         <v>3.371835260867346</v>
       </c>
     </row>
@@ -15563,6 +16756,9 @@
         </is>
       </c>
       <c r="J398" t="n">
+        <v>12</v>
+      </c>
+      <c r="K398" t="n">
         <v>3.371835260867346</v>
       </c>
     </row>
@@ -15601,6 +16797,9 @@
         </is>
       </c>
       <c r="J399" t="n">
+        <v>12</v>
+      </c>
+      <c r="K399" t="n">
         <v>4.181236727920914</v>
       </c>
     </row>
@@ -15639,6 +16838,9 @@
         </is>
       </c>
       <c r="J400" t="n">
+        <v>12</v>
+      </c>
+      <c r="K400" t="n">
         <v>4.534175874821312</v>
       </c>
     </row>
@@ -15677,6 +16879,9 @@
         </is>
       </c>
       <c r="J401" t="n">
+        <v>12</v>
+      </c>
+      <c r="K401" t="n">
         <v>4.556854453507473</v>
       </c>
     </row>
@@ -15715,6 +16920,9 @@
         </is>
       </c>
       <c r="J402" t="n">
+        <v>12</v>
+      </c>
+      <c r="K402" t="n">
         <v>4.539443432680001</v>
       </c>
     </row>
@@ -15753,6 +16961,9 @@
         </is>
       </c>
       <c r="J403" t="n">
+        <v>12</v>
+      </c>
+      <c r="K403" t="n">
         <v>4.539443432680001</v>
       </c>
     </row>
@@ -15791,6 +17002,9 @@
         </is>
       </c>
       <c r="J404" t="n">
+        <v>12</v>
+      </c>
+      <c r="K404" t="n">
         <v>4.280797347338424</v>
       </c>
     </row>
@@ -15829,6 +17043,9 @@
         </is>
       </c>
       <c r="J405" t="n">
+        <v>12</v>
+      </c>
+      <c r="K405" t="n">
         <v>4.269384811731056</v>
       </c>
     </row>
@@ -15867,6 +17084,9 @@
         </is>
       </c>
       <c r="J406" t="n">
+        <v>12</v>
+      </c>
+      <c r="K406" t="n">
         <v>4.264735244902993</v>
       </c>
     </row>
@@ -15905,6 +17125,9 @@
         </is>
       </c>
       <c r="J407" t="n">
+        <v>12</v>
+      </c>
+      <c r="K407" t="n">
         <v>4.262292726504922</v>
       </c>
     </row>
@@ -15943,6 +17166,9 @@
         </is>
       </c>
       <c r="J408" t="n">
+        <v>12</v>
+      </c>
+      <c r="K408" t="n">
         <v>4.262292726504922</v>
       </c>
     </row>
@@ -15981,6 +17207,9 @@
         </is>
       </c>
       <c r="J409" t="n">
+        <v>12</v>
+      </c>
+      <c r="K409" t="n">
         <v>4.26986651340288</v>
       </c>
     </row>
@@ -16019,6 +17248,9 @@
         </is>
       </c>
       <c r="J410" t="n">
+        <v>12</v>
+      </c>
+      <c r="K410" t="n">
         <v>4.300321810001186</v>
       </c>
     </row>
@@ -16057,6 +17289,9 @@
         </is>
       </c>
       <c r="J411" t="n">
+        <v>12</v>
+      </c>
+      <c r="K411" t="n">
         <v>4.300321810001186</v>
       </c>
     </row>
@@ -16095,6 +17330,9 @@
         </is>
       </c>
       <c r="J412" t="n">
+        <v>12</v>
+      </c>
+      <c r="K412" t="n">
         <v>4.300321810001186</v>
       </c>
     </row>
@@ -16133,6 +17371,9 @@
         </is>
       </c>
       <c r="J413" t="n">
+        <v>12</v>
+      </c>
+      <c r="K413" t="n">
         <v>4.31852538377336</v>
       </c>
     </row>
@@ -16171,6 +17412,9 @@
         </is>
       </c>
       <c r="J414" t="n">
+        <v>12</v>
+      </c>
+      <c r="K414" t="n">
         <v>4.356460355585511</v>
       </c>
     </row>
@@ -16209,6 +17453,9 @@
         </is>
       </c>
       <c r="J415" t="n">
+        <v>12</v>
+      </c>
+      <c r="K415" t="n">
         <v>4.356460355585511</v>
       </c>
     </row>
@@ -16247,6 +17494,9 @@
         </is>
       </c>
       <c r="J416" t="n">
+        <v>12</v>
+      </c>
+      <c r="K416" t="n">
         <v>4.361701931419487</v>
       </c>
     </row>
@@ -16285,6 +17535,9 @@
         </is>
       </c>
       <c r="J417" t="n">
+        <v>12</v>
+      </c>
+      <c r="K417" t="n">
         <v>4.301398698094448</v>
       </c>
     </row>
@@ -16323,6 +17576,9 @@
         </is>
       </c>
       <c r="J418" t="n">
+        <v>12</v>
+      </c>
+      <c r="K418" t="n">
         <v>4.209401645323718</v>
       </c>
     </row>
@@ -16361,6 +17617,9 @@
         </is>
       </c>
       <c r="J419" t="n">
+        <v>12</v>
+      </c>
+      <c r="K419" t="n">
         <v>4.209401645323718</v>
       </c>
     </row>
@@ -16399,6 +17658,9 @@
         </is>
       </c>
       <c r="J420" t="n">
+        <v>12</v>
+      </c>
+      <c r="K420" t="n">
         <v>4.191447476468136</v>
       </c>
     </row>
@@ -16437,6 +17699,9 @@
         </is>
       </c>
       <c r="J421" t="n">
+        <v>12</v>
+      </c>
+      <c r="K421" t="n">
         <v>4.191447476468136</v>
       </c>
     </row>
@@ -16475,6 +17740,9 @@
         </is>
       </c>
       <c r="J422" t="n">
+        <v>12</v>
+      </c>
+      <c r="K422" t="n">
         <v>4.056703917921547</v>
       </c>
     </row>
@@ -16513,6 +17781,9 @@
         </is>
       </c>
       <c r="J423" t="n">
+        <v>12</v>
+      </c>
+      <c r="K423" t="n">
         <v>3.840503814125141</v>
       </c>
     </row>
@@ -16551,6 +17822,9 @@
         </is>
       </c>
       <c r="J424" t="n">
+        <v>12</v>
+      </c>
+      <c r="K424" t="n">
         <v>3.661907100190235</v>
       </c>
     </row>
@@ -16589,6 +17863,9 @@
         </is>
       </c>
       <c r="J425" t="n">
+        <v>12</v>
+      </c>
+      <c r="K425" t="n">
         <v>3.681006404116291</v>
       </c>
     </row>
@@ -16627,6 +17904,9 @@
         </is>
       </c>
       <c r="J426" t="n">
+        <v>12</v>
+      </c>
+      <c r="K426" t="n">
         <v>3.718439743789945</v>
       </c>
     </row>
@@ -16665,6 +17945,9 @@
         </is>
       </c>
       <c r="J427" t="n">
+        <v>12</v>
+      </c>
+      <c r="K427" t="n">
         <v>3.835209738029023</v>
       </c>
     </row>
@@ -16703,6 +17986,9 @@
         </is>
       </c>
       <c r="J428" t="n">
+        <v>12</v>
+      </c>
+      <c r="K428" t="n">
         <v>3.900174829512212</v>
       </c>
     </row>
@@ -16741,6 +18027,9 @@
         </is>
       </c>
       <c r="J429" t="n">
+        <v>12</v>
+      </c>
+      <c r="K429" t="n">
         <v>3.908977539916504</v>
       </c>
     </row>
@@ -16779,6 +18068,9 @@
         </is>
       </c>
       <c r="J430" t="n">
+        <v>12</v>
+      </c>
+      <c r="K430" t="n">
         <v>3.906161595795428</v>
       </c>
     </row>
@@ -16817,6 +18109,9 @@
         </is>
       </c>
       <c r="J431" t="n">
+        <v>12</v>
+      </c>
+      <c r="K431" t="n">
         <v>3.584134533687182</v>
       </c>
     </row>
@@ -16855,6 +18150,9 @@
         </is>
       </c>
       <c r="J432" t="n">
+        <v>12</v>
+      </c>
+      <c r="K432" t="n">
         <v>3.533546784800124</v>
       </c>
     </row>
@@ -16893,6 +18191,9 @@
         </is>
       </c>
       <c r="J433" t="n">
+        <v>12</v>
+      </c>
+      <c r="K433" t="n">
         <v>3.533546784800124</v>
       </c>
     </row>
@@ -16931,6 +18232,9 @@
         </is>
       </c>
       <c r="J434" t="n">
+        <v>12</v>
+      </c>
+      <c r="K434" t="n">
         <v>3.327066270127058</v>
       </c>
     </row>
@@ -16969,6 +18273,9 @@
         </is>
       </c>
       <c r="J435" t="n">
+        <v>12</v>
+      </c>
+      <c r="K435" t="n">
         <v>3.327066270127058</v>
       </c>
     </row>
@@ -17007,6 +18314,9 @@
         </is>
       </c>
       <c r="J436" t="n">
+        <v>12</v>
+      </c>
+      <c r="K436" t="n">
         <v>3.327066270127058</v>
       </c>
     </row>
@@ -17045,6 +18355,9 @@
         </is>
       </c>
       <c r="J437" t="n">
+        <v>12</v>
+      </c>
+      <c r="K437" t="n">
         <v>3.095225708236811</v>
       </c>
     </row>
@@ -17083,6 +18396,9 @@
         </is>
       </c>
       <c r="J438" t="n">
+        <v>12</v>
+      </c>
+      <c r="K438" t="n">
         <v>3.095225708236811</v>
       </c>
     </row>
@@ -17121,6 +18437,9 @@
         </is>
       </c>
       <c r="J439" t="n">
+        <v>12</v>
+      </c>
+      <c r="K439" t="n">
         <v>3.095225708236811</v>
       </c>
     </row>
@@ -17159,6 +18478,9 @@
         </is>
       </c>
       <c r="J440" t="n">
+        <v>12</v>
+      </c>
+      <c r="K440" t="n">
         <v>3.085222887440137</v>
       </c>
     </row>
@@ -17197,6 +18519,9 @@
         </is>
       </c>
       <c r="J441" t="n">
+        <v>12</v>
+      </c>
+      <c r="K441" t="n">
         <v>3.070451231867775</v>
       </c>
     </row>
@@ -17235,6 +18560,9 @@
         </is>
       </c>
       <c r="J442" t="n">
+        <v>12</v>
+      </c>
+      <c r="K442" t="n">
         <v>3.070451231867775</v>
       </c>
     </row>
@@ -17273,6 +18601,9 @@
         </is>
       </c>
       <c r="J443" t="n">
+        <v>12</v>
+      </c>
+      <c r="K443" t="n">
         <v>3.054657340524292</v>
       </c>
     </row>
@@ -17311,6 +18642,9 @@
         </is>
       </c>
       <c r="J444" t="n">
+        <v>12</v>
+      </c>
+      <c r="K444" t="n">
         <v>2.994197312714582</v>
       </c>
     </row>
@@ -17349,6 +18683,9 @@
         </is>
       </c>
       <c r="J445" t="n">
+        <v>12</v>
+      </c>
+      <c r="K445" t="n">
         <v>2.994197312714582</v>
       </c>
     </row>
@@ -17387,6 +18724,9 @@
         </is>
       </c>
       <c r="J446" t="n">
+        <v>12</v>
+      </c>
+      <c r="K446" t="n">
         <v>3.035501156476267</v>
       </c>
     </row>
@@ -17425,6 +18765,9 @@
         </is>
       </c>
       <c r="J447" t="n">
+        <v>12</v>
+      </c>
+      <c r="K447" t="n">
         <v>3.120447987653189</v>
       </c>
     </row>
@@ -17463,6 +18806,9 @@
         </is>
       </c>
       <c r="J448" t="n">
+        <v>12</v>
+      </c>
+      <c r="K448" t="n">
         <v>3.120447987653189</v>
       </c>
     </row>
@@ -17501,6 +18847,9 @@
         </is>
       </c>
       <c r="J449" t="n">
+        <v>12</v>
+      </c>
+      <c r="K449" t="n">
         <v>4.017516597766641</v>
       </c>
     </row>
@@ -17539,6 +18888,9 @@
         </is>
       </c>
       <c r="J450" t="n">
+        <v>12</v>
+      </c>
+      <c r="K450" t="n">
         <v>4.017516597766641</v>
       </c>
     </row>
@@ -17577,6 +18929,9 @@
         </is>
       </c>
       <c r="J451" t="n">
+        <v>12</v>
+      </c>
+      <c r="K451" t="n">
         <v>4.017516597766641</v>
       </c>
     </row>
@@ -17615,6 +18970,9 @@
         </is>
       </c>
       <c r="J452" t="n">
+        <v>12</v>
+      </c>
+      <c r="K452" t="n">
         <v>3.740667489898562</v>
       </c>
     </row>
@@ -17653,6 +19011,9 @@
         </is>
       </c>
       <c r="J453" t="n">
+        <v>12</v>
+      </c>
+      <c r="K453" t="n">
         <v>3.740667489898562</v>
       </c>
     </row>
@@ -17691,6 +19052,9 @@
         </is>
       </c>
       <c r="J454" t="n">
+        <v>12</v>
+      </c>
+      <c r="K454" t="n">
         <v>3.64663006678194</v>
       </c>
     </row>
@@ -17729,6 +19093,9 @@
         </is>
       </c>
       <c r="J455" t="n">
+        <v>12</v>
+      </c>
+      <c r="K455" t="n">
         <v>3.463980192763072</v>
       </c>
     </row>
@@ -17767,6 +19134,9 @@
         </is>
       </c>
       <c r="J456" t="n">
+        <v>12</v>
+      </c>
+      <c r="K456" t="n">
         <v>3.367743287209818</v>
       </c>
     </row>
@@ -17805,6 +19175,9 @@
         </is>
       </c>
       <c r="J457" t="n">
+        <v>12</v>
+      </c>
+      <c r="K457" t="n">
         <v>3.178041040309818</v>
       </c>
     </row>
@@ -17843,6 +19216,9 @@
         </is>
       </c>
       <c r="J458" t="n">
+        <v>12</v>
+      </c>
+      <c r="K458" t="n">
         <v>2.654812161131455</v>
       </c>
     </row>
@@ -17881,6 +19257,9 @@
         </is>
       </c>
       <c r="J459" t="n">
+        <v>12</v>
+      </c>
+      <c r="K459" t="n">
         <v>2.385789925665169</v>
       </c>
     </row>
@@ -17919,6 +19298,9 @@
         </is>
       </c>
       <c r="J460" t="n">
+        <v>12</v>
+      </c>
+      <c r="K460" t="n">
         <v>2.344520445367832</v>
       </c>
     </row>
@@ -17957,6 +19339,9 @@
         </is>
       </c>
       <c r="J461" t="n">
+        <v>12</v>
+      </c>
+      <c r="K461" t="n">
         <v>2.309188151326286</v>
       </c>
     </row>
@@ -17995,6 +19380,9 @@
         </is>
       </c>
       <c r="J462" t="n">
+        <v>12</v>
+      </c>
+      <c r="K462" t="n">
         <v>2.309188151326286</v>
       </c>
     </row>
@@ -18033,6 +19421,9 @@
         </is>
       </c>
       <c r="J463" t="n">
+        <v>12</v>
+      </c>
+      <c r="K463" t="n">
         <v>2.358530936970293</v>
       </c>
     </row>
@@ -18071,6 +19462,9 @@
         </is>
       </c>
       <c r="J464" t="n">
+        <v>12</v>
+      </c>
+      <c r="K464" t="n">
         <v>2.443440184160005</v>
       </c>
     </row>
@@ -18109,6 +19503,9 @@
         </is>
       </c>
       <c r="J465" t="n">
+        <v>12</v>
+      </c>
+      <c r="K465" t="n">
         <v>2.833815609846221</v>
       </c>
     </row>
@@ -18147,6 +19544,9 @@
         </is>
       </c>
       <c r="J466" t="n">
+        <v>12</v>
+      </c>
+      <c r="K466" t="n">
         <v>3.319334674415779</v>
       </c>
     </row>
@@ -18185,6 +19585,9 @@
         </is>
       </c>
       <c r="J467" t="n">
+        <v>12</v>
+      </c>
+      <c r="K467" t="n">
         <v>3.424620809557982</v>
       </c>
     </row>
@@ -18223,6 +19626,9 @@
         </is>
       </c>
       <c r="J468" t="n">
+        <v>12</v>
+      </c>
+      <c r="K468" t="n">
         <v>3.509789395642378</v>
       </c>
     </row>
@@ -18261,6 +19667,9 @@
         </is>
       </c>
       <c r="J469" t="n">
+        <v>12</v>
+      </c>
+      <c r="K469" t="n">
         <v>3.52600150151872</v>
       </c>
     </row>
@@ -18299,6 +19708,9 @@
         </is>
       </c>
       <c r="J470" t="n">
+        <v>12</v>
+      </c>
+      <c r="K470" t="n">
         <v>3.520404145499782</v>
       </c>
     </row>
@@ -18337,6 +19749,9 @@
         </is>
       </c>
       <c r="J471" t="n">
+        <v>12</v>
+      </c>
+      <c r="K471" t="n">
         <v>3.520404145499782</v>
       </c>
     </row>
@@ -18375,6 +19790,9 @@
         </is>
       </c>
       <c r="J472" t="n">
+        <v>12</v>
+      </c>
+      <c r="K472" t="n">
         <v>3.502669227366506</v>
       </c>
     </row>
@@ -18413,6 +19831,9 @@
         </is>
       </c>
       <c r="J473" t="n">
+        <v>12</v>
+      </c>
+      <c r="K473" t="n">
         <v>3.469876409859785</v>
       </c>
     </row>
@@ -18451,6 +19872,9 @@
         </is>
       </c>
       <c r="J474" t="n">
+        <v>12</v>
+      </c>
+      <c r="K474" t="n">
         <v>3.378969325078366</v>
       </c>
     </row>
@@ -18489,6 +19913,9 @@
         </is>
       </c>
       <c r="J475" t="n">
+        <v>12</v>
+      </c>
+      <c r="K475" t="n">
         <v>3.378969325078366</v>
       </c>
     </row>
@@ -18527,6 +19954,9 @@
         </is>
       </c>
       <c r="J476" t="n">
+        <v>12</v>
+      </c>
+      <c r="K476" t="n">
         <v>3.378969325078366</v>
       </c>
     </row>
@@ -18565,6 +19995,9 @@
         </is>
       </c>
       <c r="J477" t="n">
+        <v>12</v>
+      </c>
+      <c r="K477" t="n">
         <v>3.360699052426705</v>
       </c>
     </row>
@@ -18603,6 +20036,9 @@
         </is>
       </c>
       <c r="J478" t="n">
+        <v>12</v>
+      </c>
+      <c r="K478" t="n">
         <v>3.360699052426705</v>
       </c>
     </row>
@@ -18641,6 +20077,9 @@
         </is>
       </c>
       <c r="J479" t="n">
+        <v>12</v>
+      </c>
+      <c r="K479" t="n">
         <v>3.264016425666739</v>
       </c>
     </row>
@@ -18679,6 +20118,9 @@
         </is>
       </c>
       <c r="J480" t="n">
+        <v>12</v>
+      </c>
+      <c r="K480" t="n">
         <v>3.222467693662079</v>
       </c>
     </row>
@@ -18717,6 +20159,9 @@
         </is>
       </c>
       <c r="J481" t="n">
+        <v>12</v>
+      </c>
+      <c r="K481" t="n">
         <v>3.227675240392746</v>
       </c>
     </row>
@@ -18755,6 +20200,9 @@
         </is>
       </c>
       <c r="J482" t="n">
+        <v>12</v>
+      </c>
+      <c r="K482" t="n">
         <v>3.254083343790902</v>
       </c>
     </row>
@@ -18793,6 +20241,9 @@
         </is>
       </c>
       <c r="J483" t="n">
+        <v>12</v>
+      </c>
+      <c r="K483" t="n">
         <v>3.277185011623322</v>
       </c>
     </row>
@@ -18831,6 +20282,9 @@
         </is>
       </c>
       <c r="J484" t="n">
+        <v>12</v>
+      </c>
+      <c r="K484" t="n">
         <v>3.296364545227487</v>
       </c>
     </row>
@@ -18869,6 +20323,9 @@
         </is>
       </c>
       <c r="J485" t="n">
+        <v>12</v>
+      </c>
+      <c r="K485" t="n">
         <v>3.380435284289128</v>
       </c>
     </row>
@@ -18907,6 +20364,9 @@
         </is>
       </c>
       <c r="J486" t="n">
+        <v>12</v>
+      </c>
+      <c r="K486" t="n">
         <v>3.506124698668016</v>
       </c>
     </row>
@@ -18945,6 +20405,9 @@
         </is>
       </c>
       <c r="J487" t="n">
+        <v>12</v>
+      </c>
+      <c r="K487" t="n">
         <v>3.506124698668016</v>
       </c>
     </row>
@@ -18983,6 +20446,9 @@
         </is>
       </c>
       <c r="J488" t="n">
+        <v>12</v>
+      </c>
+      <c r="K488" t="n">
         <v>3.506124698668016</v>
       </c>
     </row>
@@ -19021,6 +20487,9 @@
         </is>
       </c>
       <c r="J489" t="n">
+        <v>12</v>
+      </c>
+      <c r="K489" t="n">
         <v>3.580366731520999</v>
       </c>
     </row>
@@ -19059,6 +20528,9 @@
         </is>
       </c>
       <c r="J490" t="n">
+        <v>12</v>
+      </c>
+      <c r="K490" t="n">
         <v>3.641136051269071</v>
       </c>
     </row>
@@ -19097,6 +20569,9 @@
         </is>
       </c>
       <c r="J491" t="n">
+        <v>12</v>
+      </c>
+      <c r="K491" t="n">
         <v>3.817250625797078</v>
       </c>
     </row>
@@ -19135,6 +20610,9 @@
         </is>
       </c>
       <c r="J492" t="n">
+        <v>12</v>
+      </c>
+      <c r="K492" t="n">
         <v>3.932050941054031</v>
       </c>
     </row>
@@ -19173,6 +20651,9 @@
         </is>
       </c>
       <c r="J493" t="n">
+        <v>12</v>
+      </c>
+      <c r="K493" t="n">
         <v>3.973387840843553</v>
       </c>
     </row>
@@ -19211,6 +20692,9 @@
         </is>
       </c>
       <c r="J494" t="n">
+        <v>12</v>
+      </c>
+      <c r="K494" t="n">
         <v>4.022133969641607</v>
       </c>
     </row>
@@ -19249,6 +20733,9 @@
         </is>
       </c>
       <c r="J495" t="n">
+        <v>12</v>
+      </c>
+      <c r="K495" t="n">
         <v>4.200818098804361</v>
       </c>
     </row>
@@ -19287,6 +20774,9 @@
         </is>
       </c>
       <c r="J496" t="n">
+        <v>12</v>
+      </c>
+      <c r="K496" t="n">
         <v>4.315126756231936</v>
       </c>
     </row>
@@ -19325,6 +20815,9 @@
         </is>
       </c>
       <c r="J497" t="n">
+        <v>12</v>
+      </c>
+      <c r="K497" t="n">
         <v>4.315126756231936</v>
       </c>
     </row>
@@ -19363,6 +20856,9 @@
         </is>
       </c>
       <c r="J498" t="n">
+        <v>12</v>
+      </c>
+      <c r="K498" t="n">
         <v>4.297127956467921</v>
       </c>
     </row>
@@ -19401,6 +20897,9 @@
         </is>
       </c>
       <c r="J499" t="n">
+        <v>12</v>
+      </c>
+      <c r="K499" t="n">
         <v>4.297127956467921</v>
       </c>
     </row>
@@ -19439,6 +20938,9 @@
         </is>
       </c>
       <c r="J500" t="n">
+        <v>12</v>
+      </c>
+      <c r="K500" t="n">
         <v>4.297127956467921</v>
       </c>
     </row>
@@ -19477,6 +20979,9 @@
         </is>
       </c>
       <c r="J501" t="n">
+        <v>12</v>
+      </c>
+      <c r="K501" t="n">
         <v>4.283628632022507</v>
       </c>
     </row>
@@ -19515,6 +21020,9 @@
         </is>
       </c>
       <c r="J502" t="n">
+        <v>12</v>
+      </c>
+      <c r="K502" t="n">
         <v>4.305141370084162</v>
       </c>
     </row>
@@ -19553,6 +21061,9 @@
         </is>
       </c>
       <c r="J503" t="n">
+        <v>12</v>
+      </c>
+      <c r="K503" t="n">
         <v>3.973190519160861</v>
       </c>
     </row>
@@ -19591,6 +21102,9 @@
         </is>
       </c>
       <c r="J504" t="n">
+        <v>12</v>
+      </c>
+      <c r="K504" t="n">
         <v>3.825682358829234</v>
       </c>
     </row>
@@ -19629,6 +21143,9 @@
         </is>
       </c>
       <c r="J505" t="n">
+        <v>12</v>
+      </c>
+      <c r="K505" t="n">
         <v>3.616933261821356</v>
       </c>
     </row>
@@ -19667,6 +21184,9 @@
         </is>
       </c>
       <c r="J506" t="n">
+        <v>12</v>
+      </c>
+      <c r="K506" t="n">
         <v>3.433420371344115</v>
       </c>
     </row>
@@ -19705,6 +21225,9 @@
         </is>
       </c>
       <c r="J507" t="n">
+        <v>12</v>
+      </c>
+      <c r="K507" t="n">
         <v>3.409845417042359</v>
       </c>
     </row>
@@ -19743,6 +21266,9 @@
         </is>
       </c>
       <c r="J508" t="n">
+        <v>12</v>
+      </c>
+      <c r="K508" t="n">
         <v>3.418430893528654</v>
       </c>
     </row>
@@ -19781,6 +21307,9 @@
         </is>
       </c>
       <c r="J509" t="n">
+        <v>12</v>
+      </c>
+      <c r="K509" t="n">
         <v>3.42398838245801</v>
       </c>
     </row>
@@ -19819,6 +21348,9 @@
         </is>
       </c>
       <c r="J510" t="n">
+        <v>12</v>
+      </c>
+      <c r="K510" t="n">
         <v>3.39009739675213</v>
       </c>
     </row>
@@ -19857,6 +21389,9 @@
         </is>
       </c>
       <c r="J511" t="n">
+        <v>12</v>
+      </c>
+      <c r="K511" t="n">
         <v>3.346645761129527</v>
       </c>
     </row>
@@ -19895,6 +21430,9 @@
         </is>
       </c>
       <c r="J512" t="n">
+        <v>12</v>
+      </c>
+      <c r="K512" t="n">
         <v>3.346645761129527</v>
       </c>
     </row>
@@ -19933,6 +21471,9 @@
         </is>
       </c>
       <c r="J513" t="n">
+        <v>12</v>
+      </c>
+      <c r="K513" t="n">
         <v>3.277448409795145</v>
       </c>
     </row>
@@ -19971,6 +21512,9 @@
         </is>
       </c>
       <c r="J514" t="n">
+        <v>12</v>
+      </c>
+      <c r="K514" t="n">
         <v>3.117778391676748</v>
       </c>
     </row>
@@ -20009,6 +21553,9 @@
         </is>
       </c>
       <c r="J515" t="n">
+        <v>12</v>
+      </c>
+      <c r="K515" t="n">
         <v>3.037325650889228</v>
       </c>
     </row>
@@ -20047,6 +21594,9 @@
         </is>
       </c>
       <c r="J516" t="n">
+        <v>12</v>
+      </c>
+      <c r="K516" t="n">
         <v>2.979135510186737</v>
       </c>
     </row>
@@ -20085,6 +21635,9 @@
         </is>
       </c>
       <c r="J517" t="n">
+        <v>12</v>
+      </c>
+      <c r="K517" t="n">
         <v>2.964856408929588</v>
       </c>
     </row>
@@ -20123,6 +21676,9 @@
         </is>
       </c>
       <c r="J518" t="n">
+        <v>12</v>
+      </c>
+      <c r="K518" t="n">
         <v>2.964856408929588</v>
       </c>
     </row>
@@ -20161,6 +21717,9 @@
         </is>
       </c>
       <c r="J519" t="n">
+        <v>12</v>
+      </c>
+      <c r="K519" t="n">
         <v>2.953197421311996</v>
       </c>
     </row>
@@ -20199,6 +21758,9 @@
         </is>
       </c>
       <c r="J520" t="n">
+        <v>12</v>
+      </c>
+      <c r="K520" t="n">
         <v>2.960118765800137</v>
       </c>
     </row>
@@ -20237,6 +21799,9 @@
         </is>
       </c>
       <c r="J521" t="n">
+        <v>12</v>
+      </c>
+      <c r="K521" t="n">
         <v>2.977676564514107</v>
       </c>
     </row>
@@ -20275,6 +21840,9 @@
         </is>
       </c>
       <c r="J522" t="n">
+        <v>12</v>
+      </c>
+      <c r="K522" t="n">
         <v>2.977676564514107</v>
       </c>
     </row>
@@ -20313,6 +21881,9 @@
         </is>
       </c>
       <c r="J523" t="n">
+        <v>12</v>
+      </c>
+      <c r="K523" t="n">
         <v>3.049480923241088</v>
       </c>
     </row>
@@ -20351,6 +21922,9 @@
         </is>
       </c>
       <c r="J524" t="n">
+        <v>12</v>
+      </c>
+      <c r="K524" t="n">
         <v>3.089282371386736</v>
       </c>
     </row>
@@ -20389,6 +21963,9 @@
         </is>
       </c>
       <c r="J525" t="n">
+        <v>12</v>
+      </c>
+      <c r="K525" t="n">
         <v>3.314714429986739</v>
       </c>
     </row>
@@ -20427,6 +22004,9 @@
         </is>
       </c>
       <c r="J526" t="n">
+        <v>12</v>
+      </c>
+      <c r="K526" t="n">
         <v>3.383795625959729</v>
       </c>
     </row>
@@ -20465,6 +22045,9 @@
         </is>
       </c>
       <c r="J527" t="n">
+        <v>12</v>
+      </c>
+      <c r="K527" t="n">
         <v>3.394777914940569</v>
       </c>
     </row>
@@ -20503,6 +22086,9 @@
         </is>
       </c>
       <c r="J528" t="n">
+        <v>12</v>
+      </c>
+      <c r="K528" t="n">
         <v>3.032040403374441</v>
       </c>
     </row>
@@ -20541,6 +22127,9 @@
         </is>
       </c>
       <c r="J529" t="n">
+        <v>12</v>
+      </c>
+      <c r="K529" t="n">
         <v>2.75159478100331</v>
       </c>
     </row>
@@ -20579,6 +22168,9 @@
         </is>
       </c>
       <c r="J530" t="n">
+        <v>12</v>
+      </c>
+      <c r="K530" t="n">
         <v>2.75159478100331</v>
       </c>
     </row>
@@ -20617,6 +22209,9 @@
         </is>
       </c>
       <c r="J531" t="n">
+        <v>12</v>
+      </c>
+      <c r="K531" t="n">
         <v>2.635841574812391</v>
       </c>
     </row>
@@ -20655,6 +22250,9 @@
         </is>
       </c>
       <c r="J532" t="n">
+        <v>12</v>
+      </c>
+      <c r="K532" t="n">
         <v>2.57590298010928</v>
       </c>
     </row>
@@ -20693,6 +22291,9 @@
         </is>
       </c>
       <c r="J533" t="n">
+        <v>12</v>
+      </c>
+      <c r="K533" t="n">
         <v>2.470687257553676</v>
       </c>
     </row>
@@ -20731,6 +22332,9 @@
         </is>
       </c>
       <c r="J534" t="n">
+        <v>12</v>
+      </c>
+      <c r="K534" t="n">
         <v>2.470687257553676</v>
       </c>
     </row>
@@ -20769,6 +22373,9 @@
         </is>
       </c>
       <c r="J535" t="n">
+        <v>12</v>
+      </c>
+      <c r="K535" t="n">
         <v>2.470687257553676</v>
       </c>
     </row>
@@ -20807,6 +22414,9 @@
         </is>
       </c>
       <c r="J536" t="n">
+        <v>12</v>
+      </c>
+      <c r="K536" t="n">
         <v>2.473572347030824</v>
       </c>
     </row>
@@ -20845,6 +22455,9 @@
         </is>
       </c>
       <c r="J537" t="n">
+        <v>12</v>
+      </c>
+      <c r="K537" t="n">
         <v>2.512067072199121</v>
       </c>
     </row>
@@ -20883,6 +22496,9 @@
         </is>
       </c>
       <c r="J538" t="n">
+        <v>12</v>
+      </c>
+      <c r="K538" t="n">
         <v>2.574071522284209</v>
       </c>
     </row>
@@ -20921,6 +22537,9 @@
         </is>
       </c>
       <c r="J539" t="n">
+        <v>12</v>
+      </c>
+      <c r="K539" t="n">
         <v>2.574071522284209</v>
       </c>
     </row>
@@ -20959,6 +22578,9 @@
         </is>
       </c>
       <c r="J540" t="n">
+        <v>12</v>
+      </c>
+      <c r="K540" t="n">
         <v>2.672693687813754</v>
       </c>
     </row>
@@ -20997,6 +22619,9 @@
         </is>
       </c>
       <c r="J541" t="n">
+        <v>12</v>
+      </c>
+      <c r="K541" t="n">
         <v>2.672693687813754</v>
       </c>
     </row>
@@ -21035,6 +22660,9 @@
         </is>
       </c>
       <c r="J542" t="n">
+        <v>12</v>
+      </c>
+      <c r="K542" t="n">
         <v>2.672693687813754</v>
       </c>
     </row>
@@ -21073,6 +22701,9 @@
         </is>
       </c>
       <c r="J543" t="n">
+        <v>12</v>
+      </c>
+      <c r="K543" t="n">
         <v>2.672693687813754</v>
       </c>
     </row>
@@ -21111,6 +22742,9 @@
         </is>
       </c>
       <c r="J544" t="n">
+        <v>12</v>
+      </c>
+      <c r="K544" t="n">
         <v>2.472705570597032</v>
       </c>
     </row>
@@ -21149,6 +22783,9 @@
         </is>
       </c>
       <c r="J545" t="n">
+        <v>12</v>
+      </c>
+      <c r="K545" t="n">
         <v>2.400297296824222</v>
       </c>
     </row>
@@ -21187,6 +22824,9 @@
         </is>
       </c>
       <c r="J546" t="n">
+        <v>12</v>
+      </c>
+      <c r="K546" t="n">
         <v>2.379675900625711</v>
       </c>
     </row>
@@ -21225,6 +22865,9 @@
         </is>
       </c>
       <c r="J547" t="n">
+        <v>12</v>
+      </c>
+      <c r="K547" t="n">
         <v>2.379675900625711</v>
       </c>
     </row>
@@ -21263,6 +22906,9 @@
         </is>
       </c>
       <c r="J548" t="n">
+        <v>12</v>
+      </c>
+      <c r="K548" t="n">
         <v>2.379675900625711</v>
       </c>
     </row>
@@ -21301,6 +22947,9 @@
         </is>
       </c>
       <c r="J549" t="n">
+        <v>12</v>
+      </c>
+      <c r="K549" t="n">
         <v>2.4166260687925</v>
       </c>
     </row>
@@ -21339,6 +22988,9 @@
         </is>
       </c>
       <c r="J550" t="n">
+        <v>12</v>
+      </c>
+      <c r="K550" t="n">
         <v>2.447244536282783</v>
       </c>
     </row>
@@ -21377,6 +23029,9 @@
         </is>
       </c>
       <c r="J551" t="n">
+        <v>12</v>
+      </c>
+      <c r="K551" t="n">
         <v>2.175054442349441</v>
       </c>
     </row>
@@ -21415,6 +23070,9 @@
         </is>
       </c>
       <c r="J552" t="n">
+        <v>12</v>
+      </c>
+      <c r="K552" t="n">
         <v>2.175054442349441</v>
       </c>
     </row>
@@ -21453,6 +23111,9 @@
         </is>
       </c>
       <c r="J553" t="n">
+        <v>12</v>
+      </c>
+      <c r="K553" t="n">
         <v>1.925066695757111</v>
       </c>
     </row>
@@ -21491,6 +23152,9 @@
         </is>
       </c>
       <c r="J554" t="n">
+        <v>12</v>
+      </c>
+      <c r="K554" t="n">
         <v>1.416087250369463</v>
       </c>
     </row>
@@ -21529,6 +23193,9 @@
         </is>
       </c>
       <c r="J555" t="n">
+        <v>12</v>
+      </c>
+      <c r="K555" t="n">
         <v>1.123894382083565</v>
       </c>
     </row>
@@ -21567,6 +23234,9 @@
         </is>
       </c>
       <c r="J556" t="n">
+        <v>12</v>
+      </c>
+      <c r="K556" t="n">
         <v>1.131080114638559</v>
       </c>
     </row>
@@ -21605,6 +23275,9 @@
         </is>
       </c>
       <c r="J557" t="n">
+        <v>12</v>
+      </c>
+      <c r="K557" t="n">
         <v>1.145245298816898</v>
       </c>
     </row>
@@ -21643,6 +23316,9 @@
         </is>
       </c>
       <c r="J558" t="n">
+        <v>12</v>
+      </c>
+      <c r="K558" t="n">
         <v>1.149221173839038</v>
       </c>
     </row>
@@ -21681,6 +23357,9 @@
         </is>
       </c>
       <c r="J559" t="n">
+        <v>12</v>
+      </c>
+      <c r="K559" t="n">
         <v>1.159187990093719</v>
       </c>
     </row>
@@ -21719,6 +23398,9 @@
         </is>
       </c>
       <c r="J560" t="n">
+        <v>12</v>
+      </c>
+      <c r="K560" t="n">
         <v>1.159187990093719</v>
       </c>
     </row>
@@ -21757,6 +23439,9 @@
         </is>
       </c>
       <c r="J561" t="n">
+        <v>12</v>
+      </c>
+      <c r="K561" t="n">
         <v>1.115603605624463</v>
       </c>
     </row>
@@ -21795,6 +23480,9 @@
         </is>
       </c>
       <c r="J562" t="n">
+        <v>12</v>
+      </c>
+      <c r="K562" t="n">
         <v>1.085638435459307</v>
       </c>
     </row>
@@ -21833,6 +23521,9 @@
         </is>
       </c>
       <c r="J563" t="n">
+        <v>12</v>
+      </c>
+      <c r="K563" t="n">
         <v>1.085638435459307</v>
       </c>
     </row>
@@ -21871,6 +23562,9 @@
         </is>
       </c>
       <c r="J564" t="n">
+        <v>12</v>
+      </c>
+      <c r="K564" t="n">
         <v>1.034396063423756</v>
       </c>
     </row>
@@ -21909,6 +23603,9 @@
         </is>
       </c>
       <c r="J565" t="n">
+        <v>12</v>
+      </c>
+      <c r="K565" t="n">
         <v>1.012846939319374</v>
       </c>
     </row>
@@ -21947,6 +23644,9 @@
         </is>
       </c>
       <c r="J566" t="n">
+        <v>12</v>
+      </c>
+      <c r="K566" t="n">
         <v>0.9694245790712051</v>
       </c>
     </row>
@@ -21985,6 +23685,9 @@
         </is>
       </c>
       <c r="J567" t="n">
+        <v>12</v>
+      </c>
+      <c r="K567" t="n">
         <v>0.9694245790712051</v>
       </c>
     </row>
@@ -22023,6 +23726,9 @@
         </is>
       </c>
       <c r="J568" t="n">
+        <v>12</v>
+      </c>
+      <c r="K568" t="n">
         <v>0.9743226145299796</v>
       </c>
     </row>
@@ -22061,6 +23767,9 @@
         </is>
       </c>
       <c r="J569" t="n">
+        <v>12</v>
+      </c>
+      <c r="K569" t="n">
         <v>0.9813648320274109</v>
       </c>
     </row>
@@ -22099,6 +23808,9 @@
         </is>
       </c>
       <c r="J570" t="n">
+        <v>12</v>
+      </c>
+      <c r="K570" t="n">
         <v>1.004683167683627</v>
       </c>
     </row>
@@ -22137,6 +23849,9 @@
         </is>
       </c>
       <c r="J571" t="n">
+        <v>12</v>
+      </c>
+      <c r="K571" t="n">
         <v>1.176159351903023</v>
       </c>
     </row>
@@ -22175,6 +23890,9 @@
         </is>
       </c>
       <c r="J572" t="n">
+        <v>12</v>
+      </c>
+      <c r="K572" t="n">
         <v>1.176159351903023</v>
       </c>
     </row>
@@ -22213,6 +23931,9 @@
         </is>
       </c>
       <c r="J573" t="n">
+        <v>12</v>
+      </c>
+      <c r="K573" t="n">
         <v>1.318042797516942</v>
       </c>
     </row>
@@ -22251,6 +23972,9 @@
         </is>
       </c>
       <c r="J574" t="n">
+        <v>12</v>
+      </c>
+      <c r="K574" t="n">
         <v>1.565989837566988</v>
       </c>
     </row>
@@ -22289,6 +24013,9 @@
         </is>
       </c>
       <c r="J575" t="n">
+        <v>12</v>
+      </c>
+      <c r="K575" t="n">
         <v>1.722219658620811</v>
       </c>
     </row>
@@ -22327,6 +24054,9 @@
         </is>
       </c>
       <c r="J576" t="n">
+        <v>12</v>
+      </c>
+      <c r="K576" t="n">
         <v>1.783594776161037</v>
       </c>
     </row>
@@ -22365,6 +24095,9 @@
         </is>
       </c>
       <c r="J577" t="n">
+        <v>12</v>
+      </c>
+      <c r="K577" t="n">
         <v>1.837233702001744</v>
       </c>
     </row>
@@ -22403,6 +24136,9 @@
         </is>
       </c>
       <c r="J578" t="n">
+        <v>12</v>
+      </c>
+      <c r="K578" t="n">
         <v>1.860843114853313</v>
       </c>
     </row>
@@ -22441,6 +24177,9 @@
         </is>
       </c>
       <c r="J579" t="n">
+        <v>12</v>
+      </c>
+      <c r="K579" t="n">
         <v>1.831540491402372</v>
       </c>
     </row>
@@ -22479,6 +24218,9 @@
         </is>
       </c>
       <c r="J580" t="n">
+        <v>12</v>
+      </c>
+      <c r="K580" t="n">
         <v>1.831540491402372</v>
       </c>
     </row>
@@ -22517,6 +24259,9 @@
         </is>
       </c>
       <c r="J581" t="n">
+        <v>12</v>
+      </c>
+      <c r="K581" t="n">
         <v>1.730775162375606</v>
       </c>
     </row>
@@ -22555,6 +24300,9 @@
         </is>
       </c>
       <c r="J582" t="n">
+        <v>12</v>
+      </c>
+      <c r="K582" t="n">
         <v>1.626495109009087</v>
       </c>
     </row>
@@ -22593,6 +24341,9 @@
         </is>
       </c>
       <c r="J583" t="n">
+        <v>12</v>
+      </c>
+      <c r="K583" t="n">
         <v>1.508042810549869</v>
       </c>
     </row>
@@ -22631,6 +24382,9 @@
         </is>
       </c>
       <c r="J584" t="n">
+        <v>12</v>
+      </c>
+      <c r="K584" t="n">
         <v>1.508042810549869</v>
       </c>
     </row>
@@ -22669,6 +24423,9 @@
         </is>
       </c>
       <c r="J585" t="n">
+        <v>12</v>
+      </c>
+      <c r="K585" t="n">
         <v>1.464517592491746</v>
       </c>
     </row>
@@ -22707,6 +24464,9 @@
         </is>
       </c>
       <c r="J586" t="n">
+        <v>12</v>
+      </c>
+      <c r="K586" t="n">
         <v>1.358106769468824</v>
       </c>
     </row>
@@ -22745,6 +24505,9 @@
         </is>
       </c>
       <c r="J587" t="n">
+        <v>12</v>
+      </c>
+      <c r="K587" t="n">
         <v>1.294085224276774</v>
       </c>
     </row>
@@ -22783,6 +24546,9 @@
         </is>
       </c>
       <c r="J588" t="n">
+        <v>12</v>
+      </c>
+      <c r="K588" t="n">
         <v>1.28182156009641</v>
       </c>
     </row>
@@ -22821,6 +24587,9 @@
         </is>
       </c>
       <c r="J589" t="n">
+        <v>12</v>
+      </c>
+      <c r="K589" t="n">
         <v>1.279328290163807</v>
       </c>
     </row>
@@ -22859,6 +24628,9 @@
         </is>
       </c>
       <c r="J590" t="n">
+        <v>12</v>
+      </c>
+      <c r="K590" t="n">
         <v>1.279627798168528</v>
       </c>
     </row>
@@ -22897,6 +24669,9 @@
         </is>
       </c>
       <c r="J591" t="n">
+        <v>12</v>
+      </c>
+      <c r="K591" t="n">
         <v>1.279627798168528</v>
       </c>
     </row>
@@ -22935,6 +24710,9 @@
         </is>
       </c>
       <c r="J592" t="n">
+        <v>12</v>
+      </c>
+      <c r="K592" t="n">
         <v>1.315739881847221</v>
       </c>
     </row>
@@ -22973,6 +24751,9 @@
         </is>
       </c>
       <c r="J593" t="n">
+        <v>12</v>
+      </c>
+      <c r="K593" t="n">
         <v>1.315739881847221</v>
       </c>
     </row>
@@ -23011,6 +24792,9 @@
         </is>
       </c>
       <c r="J594" t="n">
+        <v>12</v>
+      </c>
+      <c r="K594" t="n">
         <v>1.310577091057348</v>
       </c>
     </row>
@@ -23049,6 +24833,9 @@
         </is>
       </c>
       <c r="J595" t="n">
+        <v>12</v>
+      </c>
+      <c r="K595" t="n">
         <v>1.30326866984884</v>
       </c>
     </row>
@@ -23087,6 +24874,9 @@
         </is>
       </c>
       <c r="J596" t="n">
+        <v>12</v>
+      </c>
+      <c r="K596" t="n">
         <v>1.30326866984884</v>
       </c>
     </row>
@@ -23125,6 +24915,9 @@
         </is>
       </c>
       <c r="J597" t="n">
+        <v>12</v>
+      </c>
+      <c r="K597" t="n">
         <v>1.263554554362516</v>
       </c>
     </row>
@@ -23163,6 +24956,9 @@
         </is>
       </c>
       <c r="J598" t="n">
+        <v>12</v>
+      </c>
+      <c r="K598" t="n">
         <v>1.227518049780225</v>
       </c>
     </row>
@@ -23201,6 +24997,9 @@
         </is>
       </c>
       <c r="J599" t="n">
+        <v>12</v>
+      </c>
+      <c r="K599" t="n">
         <v>1.207156264275681</v>
       </c>
     </row>
@@ -23239,6 +25038,9 @@
         </is>
       </c>
       <c r="J600" t="n">
+        <v>12</v>
+      </c>
+      <c r="K600" t="n">
         <v>1.207156264275681</v>
       </c>
     </row>
@@ -23277,6 +25079,9 @@
         </is>
       </c>
       <c r="J601" t="n">
+        <v>12</v>
+      </c>
+      <c r="K601" t="n">
         <v>1.134033155534923</v>
       </c>
     </row>
@@ -23315,6 +25120,9 @@
         </is>
       </c>
       <c r="J602" t="n">
+        <v>12</v>
+      </c>
+      <c r="K602" t="n">
         <v>1.134033155534923</v>
       </c>
     </row>
@@ -23353,6 +25161,9 @@
         </is>
       </c>
       <c r="J603" t="n">
+        <v>12</v>
+      </c>
+      <c r="K603" t="n">
         <v>1.134033155534923</v>
       </c>
     </row>
@@ -23391,6 +25202,9 @@
         </is>
       </c>
       <c r="J604" t="n">
+        <v>12</v>
+      </c>
+      <c r="K604" t="n">
         <v>0.8704435224870194</v>
       </c>
     </row>
@@ -23429,6 +25243,9 @@
         </is>
       </c>
       <c r="J605" t="n">
+        <v>12</v>
+      </c>
+      <c r="K605" t="n">
         <v>0.8704435224870194</v>
       </c>
     </row>
@@ -23467,6 +25284,9 @@
         </is>
       </c>
       <c r="J606" t="n">
+        <v>12</v>
+      </c>
+      <c r="K606" t="n">
         <v>0.8163402738983425</v>
       </c>
     </row>
@@ -23505,6 +25325,9 @@
         </is>
       </c>
       <c r="J607" t="n">
+        <v>12</v>
+      </c>
+      <c r="K607" t="n">
         <v>0.6948645988460298</v>
       </c>
     </row>
@@ -23543,6 +25366,9 @@
         </is>
       </c>
       <c r="J608" t="n">
+        <v>12</v>
+      </c>
+      <c r="K608" t="n">
         <v>0.723704314141481</v>
       </c>
     </row>
@@ -23581,6 +25407,9 @@
         </is>
       </c>
       <c r="J609" t="n">
+        <v>12</v>
+      </c>
+      <c r="K609" t="n">
         <v>0.7572489164461016</v>
       </c>
     </row>
@@ -23619,6 +25448,9 @@
         </is>
       </c>
       <c r="J610" t="n">
+        <v>12</v>
+      </c>
+      <c r="K610" t="n">
         <v>0.7984816878000636</v>
       </c>
     </row>
@@ -23657,6 +25489,9 @@
         </is>
       </c>
       <c r="J611" t="n">
+        <v>12</v>
+      </c>
+      <c r="K611" t="n">
         <v>0.861434023328604</v>
       </c>
     </row>
@@ -23695,6 +25530,9 @@
         </is>
       </c>
       <c r="J612" t="n">
+        <v>12</v>
+      </c>
+      <c r="K612" t="n">
         <v>1.194708569544332</v>
       </c>
     </row>
@@ -23733,6 +25571,9 @@
         </is>
       </c>
       <c r="J613" t="n">
+        <v>12</v>
+      </c>
+      <c r="K613" t="n">
         <v>1.539742672602747</v>
       </c>
     </row>
@@ -23771,6 +25612,9 @@
         </is>
       </c>
       <c r="J614" t="n">
+        <v>12</v>
+      </c>
+      <c r="K614" t="n">
         <v>1.539742672602747</v>
       </c>
     </row>
@@ -23809,6 +25653,9 @@
         </is>
       </c>
       <c r="J615" t="n">
+        <v>12</v>
+      </c>
+      <c r="K615" t="n">
         <v>1.745410162807558</v>
       </c>
     </row>
@@ -23847,6 +25694,9 @@
         </is>
       </c>
       <c r="J616" t="n">
+        <v>12</v>
+      </c>
+      <c r="K616" t="n">
         <v>1.745410162807558</v>
       </c>
     </row>
@@ -23885,6 +25735,9 @@
         </is>
       </c>
       <c r="J617" t="n">
+        <v>12</v>
+      </c>
+      <c r="K617" t="n">
         <v>1.745410162807558</v>
       </c>
     </row>
@@ -23923,6 +25776,9 @@
         </is>
       </c>
       <c r="J618" t="n">
+        <v>12</v>
+      </c>
+      <c r="K618" t="n">
         <v>1.784111323469488</v>
       </c>
     </row>
@@ -23961,6 +25817,9 @@
         </is>
       </c>
       <c r="J619" t="n">
+        <v>12</v>
+      </c>
+      <c r="K619" t="n">
         <v>1.784111323469488</v>
       </c>
     </row>
@@ -23999,6 +25858,9 @@
         </is>
       </c>
       <c r="J620" t="n">
+        <v>12</v>
+      </c>
+      <c r="K620" t="n">
         <v>1.832790042436139</v>
       </c>
     </row>
@@ -24037,6 +25899,9 @@
         </is>
       </c>
       <c r="J621" t="n">
+        <v>12</v>
+      </c>
+      <c r="K621" t="n">
         <v>1.846529331080078</v>
       </c>
     </row>
@@ -24075,6 +25940,9 @@
         </is>
       </c>
       <c r="J622" t="n">
+        <v>12</v>
+      </c>
+      <c r="K622" t="n">
         <v>1.790405020241955</v>
       </c>
     </row>
@@ -24113,6 +25981,9 @@
         </is>
       </c>
       <c r="J623" t="n">
+        <v>12</v>
+      </c>
+      <c r="K623" t="n">
         <v>1.790405020241955</v>
       </c>
     </row>
@@ -24151,6 +26022,9 @@
         </is>
       </c>
       <c r="J624" t="n">
+        <v>12</v>
+      </c>
+      <c r="K624" t="n">
         <v>1.783828697312045</v>
       </c>
     </row>
@@ -24189,6 +26063,9 @@
         </is>
       </c>
       <c r="J625" t="n">
+        <v>12</v>
+      </c>
+      <c r="K625" t="n">
         <v>1.783828697312045</v>
       </c>
     </row>
@@ -24227,6 +26104,9 @@
         </is>
       </c>
       <c r="J626" t="n">
+        <v>12</v>
+      </c>
+      <c r="K626" t="n">
         <v>1.783828697312045</v>
       </c>
     </row>
@@ -24265,6 +26145,9 @@
         </is>
       </c>
       <c r="J627" t="n">
+        <v>12</v>
+      </c>
+      <c r="K627" t="n">
         <v>1.789326123264181</v>
       </c>
     </row>
@@ -24303,6 +26186,9 @@
         </is>
       </c>
       <c r="J628" t="n">
+        <v>12</v>
+      </c>
+      <c r="K628" t="n">
         <v>1.807139070882643</v>
       </c>
     </row>
@@ -24341,6 +26227,9 @@
         </is>
       </c>
       <c r="J629" t="n">
+        <v>12</v>
+      </c>
+      <c r="K629" t="n">
         <v>1.807139070882643</v>
       </c>
     </row>
@@ -24379,6 +26268,9 @@
         </is>
       </c>
       <c r="J630" t="n">
+        <v>12</v>
+      </c>
+      <c r="K630" t="n">
         <v>1.868468090956951</v>
       </c>
     </row>
@@ -24417,6 +26309,9 @@
         </is>
       </c>
       <c r="J631" t="n">
+        <v>12</v>
+      </c>
+      <c r="K631" t="n">
         <v>2.001773745122148</v>
       </c>
     </row>
@@ -24455,6 +26350,9 @@
         </is>
       </c>
       <c r="J632" t="n">
+        <v>12</v>
+      </c>
+      <c r="K632" t="n">
         <v>1.997460093098258</v>
       </c>
     </row>
@@ -24493,6 +26391,9 @@
         </is>
       </c>
       <c r="J633" t="n">
+        <v>12</v>
+      </c>
+      <c r="K633" t="n">
         <v>1.997460093098258</v>
       </c>
     </row>
@@ -24531,6 +26432,9 @@
         </is>
       </c>
       <c r="J634" t="n">
+        <v>12</v>
+      </c>
+      <c r="K634" t="n">
         <v>1.922001367796436</v>
       </c>
     </row>
@@ -24569,6 +26473,9 @@
         </is>
       </c>
       <c r="J635" t="n">
+        <v>12</v>
+      </c>
+      <c r="K635" t="n">
         <v>1.85971668888828</v>
       </c>
     </row>
@@ -24607,6 +26514,9 @@
         </is>
       </c>
       <c r="J636" t="n">
+        <v>12</v>
+      </c>
+      <c r="K636" t="n">
         <v>1.85971668888828</v>
       </c>
     </row>
@@ -24645,6 +26555,9 @@
         </is>
       </c>
       <c r="J637" t="n">
+        <v>12</v>
+      </c>
+      <c r="K637" t="n">
         <v>1.80011545421401</v>
       </c>
     </row>
@@ -24683,6 +26596,9 @@
         </is>
       </c>
       <c r="J638" t="n">
+        <v>12</v>
+      </c>
+      <c r="K638" t="n">
         <v>1.60787978877463</v>
       </c>
     </row>
@@ -24721,6 +26637,9 @@
         </is>
       </c>
       <c r="J639" t="n">
+        <v>12</v>
+      </c>
+      <c r="K639" t="n">
         <v>1.523194373871843</v>
       </c>
     </row>
@@ -24759,6 +26678,9 @@
         </is>
       </c>
       <c r="J640" t="n">
+        <v>12</v>
+      </c>
+      <c r="K640" t="n">
         <v>1.43457899949546</v>
       </c>
     </row>
@@ -24797,6 +26719,9 @@
         </is>
       </c>
       <c r="J641" t="n">
+        <v>12</v>
+      </c>
+      <c r="K641" t="n">
         <v>1.43457899949546</v>
       </c>
     </row>
@@ -24835,6 +26760,9 @@
         </is>
       </c>
       <c r="J642" t="n">
+        <v>12</v>
+      </c>
+      <c r="K642" t="n">
         <v>1.43457899949546</v>
       </c>
     </row>
@@ -24873,6 +26801,9 @@
         </is>
       </c>
       <c r="J643" t="n">
+        <v>12</v>
+      </c>
+      <c r="K643" t="n">
         <v>1.43457899949546</v>
       </c>
     </row>
@@ -24911,6 +26842,9 @@
         </is>
       </c>
       <c r="J644" t="n">
+        <v>12</v>
+      </c>
+      <c r="K644" t="n">
         <v>1.39055408208409</v>
       </c>
     </row>
@@ -24949,6 +26883,9 @@
         </is>
       </c>
       <c r="J645" t="n">
+        <v>12</v>
+      </c>
+      <c r="K645" t="n">
         <v>1.39055408208409</v>
       </c>
     </row>
@@ -24987,6 +26924,9 @@
         </is>
       </c>
       <c r="J646" t="n">
+        <v>12</v>
+      </c>
+      <c r="K646" t="n">
         <v>1.355687483893385</v>
       </c>
     </row>
@@ -25025,6 +26965,9 @@
         </is>
       </c>
       <c r="J647" t="n">
+        <v>12</v>
+      </c>
+      <c r="K647" t="n">
         <v>1.355687483893385</v>
       </c>
     </row>
@@ -25063,6 +27006,9 @@
         </is>
       </c>
       <c r="J648" t="n">
+        <v>12</v>
+      </c>
+      <c r="K648" t="n">
         <v>1.355687483893385</v>
       </c>
     </row>
@@ -25101,6 +27047,9 @@
         </is>
       </c>
       <c r="J649" t="n">
+        <v>12</v>
+      </c>
+      <c r="K649" t="n">
         <v>1.316049262162023</v>
       </c>
     </row>
@@ -25139,6 +27088,9 @@
         </is>
       </c>
       <c r="J650" t="n">
+        <v>12</v>
+      </c>
+      <c r="K650" t="n">
         <v>1.316049262162023</v>
       </c>
     </row>
@@ -25177,6 +27129,9 @@
         </is>
       </c>
       <c r="J651" t="n">
+        <v>12</v>
+      </c>
+      <c r="K651" t="n">
         <v>1.308278324154629</v>
       </c>
     </row>
@@ -25215,6 +27170,9 @@
         </is>
       </c>
       <c r="J652" t="n">
+        <v>12</v>
+      </c>
+      <c r="K652" t="n">
         <v>1.303477941053459</v>
       </c>
     </row>
@@ -25253,6 +27211,9 @@
         </is>
       </c>
       <c r="J653" t="n">
+        <v>12</v>
+      </c>
+      <c r="K653" t="n">
         <v>1.298838943376611</v>
       </c>
     </row>
@@ -25291,6 +27252,9 @@
         </is>
       </c>
       <c r="J654" t="n">
+        <v>12</v>
+      </c>
+      <c r="K654" t="n">
         <v>1.298838943376611</v>
       </c>
     </row>
@@ -25329,6 +27293,9 @@
         </is>
       </c>
       <c r="J655" t="n">
+        <v>12</v>
+      </c>
+      <c r="K655" t="n">
         <v>1.298838943376611</v>
       </c>
     </row>
@@ -25367,6 +27334,9 @@
         </is>
       </c>
       <c r="J656" t="n">
+        <v>12</v>
+      </c>
+      <c r="K656" t="n">
         <v>1.307751244711193</v>
       </c>
     </row>
@@ -25405,6 +27375,9 @@
         </is>
       </c>
       <c r="J657" t="n">
+        <v>12</v>
+      </c>
+      <c r="K657" t="n">
         <v>1.32627407966019</v>
       </c>
     </row>
@@ -25443,6 +27416,9 @@
         </is>
       </c>
       <c r="J658" t="n">
+        <v>12</v>
+      </c>
+      <c r="K658" t="n">
         <v>1.32627407966019</v>
       </c>
     </row>
@@ -25481,6 +27457,9 @@
         </is>
       </c>
       <c r="J659" t="n">
+        <v>12</v>
+      </c>
+      <c r="K659" t="n">
         <v>1.445278265952763</v>
       </c>
     </row>
@@ -25519,6 +27498,9 @@
         </is>
       </c>
       <c r="J660" t="n">
+        <v>12</v>
+      </c>
+      <c r="K660" t="n">
         <v>1.531232477808799</v>
       </c>
     </row>
@@ -25557,6 +27539,9 @@
         </is>
       </c>
       <c r="J661" t="n">
+        <v>12</v>
+      </c>
+      <c r="K661" t="n">
         <v>1.610719542423982</v>
       </c>
     </row>
@@ -25595,6 +27580,9 @@
         </is>
       </c>
       <c r="J662" t="n">
+        <v>12</v>
+      </c>
+      <c r="K662" t="n">
         <v>1.610719542423982</v>
       </c>
     </row>
@@ -25633,6 +27621,9 @@
         </is>
       </c>
       <c r="J663" t="n">
+        <v>12</v>
+      </c>
+      <c r="K663" t="n">
         <v>1.677597541477979</v>
       </c>
     </row>
@@ -25671,6 +27662,9 @@
         </is>
       </c>
       <c r="J664" t="n">
+        <v>12</v>
+      </c>
+      <c r="K664" t="n">
         <v>2.007281387903658</v>
       </c>
     </row>
@@ -25709,6 +27703,9 @@
         </is>
       </c>
       <c r="J665" t="n">
+        <v>12</v>
+      </c>
+      <c r="K665" t="n">
         <v>2.007281387903658</v>
       </c>
     </row>
@@ -25747,6 +27744,9 @@
         </is>
       </c>
       <c r="J666" t="n">
+        <v>12</v>
+      </c>
+      <c r="K666" t="n">
         <v>2.090168976303147</v>
       </c>
     </row>
@@ -25785,6 +27785,9 @@
         </is>
       </c>
       <c r="J667" t="n">
+        <v>12</v>
+      </c>
+      <c r="K667" t="n">
         <v>2.090168976303147</v>
       </c>
     </row>
@@ -25823,6 +27826,9 @@
         </is>
       </c>
       <c r="J668" t="n">
+        <v>12</v>
+      </c>
+      <c r="K668" t="n">
         <v>2.267254130189872</v>
       </c>
     </row>
@@ -25861,6 +27867,9 @@
         </is>
       </c>
       <c r="J669" t="n">
+        <v>12</v>
+      </c>
+      <c r="K669" t="n">
         <v>2.363372231430629</v>
       </c>
     </row>
@@ -25899,6 +27908,9 @@
         </is>
       </c>
       <c r="J670" t="n">
+        <v>12</v>
+      </c>
+      <c r="K670" t="n">
         <v>2.360552832004548</v>
       </c>
     </row>
@@ -25937,6 +27949,9 @@
         </is>
       </c>
       <c r="J671" t="n">
+        <v>12</v>
+      </c>
+      <c r="K671" t="n">
         <v>2.360552832004548</v>
       </c>
     </row>
@@ -25975,6 +27990,9 @@
         </is>
       </c>
       <c r="J672" t="n">
+        <v>12</v>
+      </c>
+      <c r="K672" t="n">
         <v>2.289717396500576</v>
       </c>
     </row>
@@ -26013,6 +28031,9 @@
         </is>
       </c>
       <c r="J673" t="n">
+        <v>12</v>
+      </c>
+      <c r="K673" t="n">
         <v>2.230781576977644</v>
       </c>
     </row>
@@ -26051,6 +28072,9 @@
         </is>
       </c>
       <c r="J674" t="n">
+        <v>12</v>
+      </c>
+      <c r="K674" t="n">
         <v>2.16026318861172</v>
       </c>
     </row>
@@ -26089,6 +28113,9 @@
         </is>
       </c>
       <c r="J675" t="n">
+        <v>12</v>
+      </c>
+      <c r="K675" t="n">
         <v>1.944230033228157</v>
       </c>
     </row>
@@ -26127,6 +28154,9 @@
         </is>
       </c>
       <c r="J676" t="n">
+        <v>12</v>
+      </c>
+      <c r="K676" t="n">
         <v>1.882953043862903</v>
       </c>
     </row>
@@ -26165,6 +28195,9 @@
         </is>
       </c>
       <c r="J677" t="n">
+        <v>12</v>
+      </c>
+      <c r="K677" t="n">
         <v>1.767672420572199</v>
       </c>
     </row>
@@ -26203,6 +28236,9 @@
         </is>
       </c>
       <c r="J678" t="n">
+        <v>12</v>
+      </c>
+      <c r="K678" t="n">
         <v>1.767672420572199</v>
       </c>
     </row>
@@ -26241,6 +28277,9 @@
         </is>
       </c>
       <c r="J679" t="n">
+        <v>12</v>
+      </c>
+      <c r="K679" t="n">
         <v>1.680817090937332</v>
       </c>
     </row>
@@ -26279,6 +28318,9 @@
         </is>
       </c>
       <c r="J680" t="n">
+        <v>12</v>
+      </c>
+      <c r="K680" t="n">
         <v>1.658627175004368</v>
       </c>
     </row>
@@ -26317,6 +28359,9 @@
         </is>
       </c>
       <c r="J681" t="n">
+        <v>12</v>
+      </c>
+      <c r="K681" t="n">
         <v>1.639458829253433</v>
       </c>
     </row>
@@ -26355,6 +28400,9 @@
         </is>
       </c>
       <c r="J682" t="n">
+        <v>12</v>
+      </c>
+      <c r="K682" t="n">
         <v>1.629020728744538</v>
       </c>
     </row>
@@ -26393,6 +28441,9 @@
         </is>
       </c>
       <c r="J683" t="n">
+        <v>12</v>
+      </c>
+      <c r="K683" t="n">
         <v>1.629020728744538</v>
       </c>
     </row>
@@ -26431,6 +28482,9 @@
         </is>
       </c>
       <c r="J684" t="n">
+        <v>12</v>
+      </c>
+      <c r="K684" t="n">
         <v>1.588054462942365</v>
       </c>
     </row>
@@ -26469,6 +28523,9 @@
         </is>
       </c>
       <c r="J685" t="n">
+        <v>12</v>
+      </c>
+      <c r="K685" t="n">
         <v>1.559738234354261</v>
       </c>
     </row>
@@ -26507,6 +28564,9 @@
         </is>
       </c>
       <c r="J686" t="n">
+        <v>12</v>
+      </c>
+      <c r="K686" t="n">
         <v>1.5341851165311</v>
       </c>
     </row>
@@ -26545,6 +28605,9 @@
         </is>
       </c>
       <c r="J687" t="n">
+        <v>12</v>
+      </c>
+      <c r="K687" t="n">
         <v>1.397551012967835</v>
       </c>
     </row>
@@ -26583,6 +28646,9 @@
         </is>
       </c>
       <c r="J688" t="n">
+        <v>12</v>
+      </c>
+      <c r="K688" t="n">
         <v>1.367327122229794</v>
       </c>
     </row>
@@ -26621,6 +28687,9 @@
         </is>
       </c>
       <c r="J689" t="n">
+        <v>12</v>
+      </c>
+      <c r="K689" t="n">
         <v>1.298828102585088</v>
       </c>
     </row>
@@ -26659,6 +28728,9 @@
         </is>
       </c>
       <c r="J690" t="n">
+        <v>12</v>
+      </c>
+      <c r="K690" t="n">
         <v>1.286767569665152</v>
       </c>
     </row>
@@ -26697,6 +28769,9 @@
         </is>
       </c>
       <c r="J691" t="n">
+        <v>12</v>
+      </c>
+      <c r="K691" t="n">
         <v>1.307378016707403</v>
       </c>
     </row>
@@ -26735,6 +28810,9 @@
         </is>
       </c>
       <c r="J692" t="n">
+        <v>12</v>
+      </c>
+      <c r="K692" t="n">
         <v>1.369275685855511</v>
       </c>
     </row>
@@ -26773,6 +28851,9 @@
         </is>
       </c>
       <c r="J693" t="n">
+        <v>12</v>
+      </c>
+      <c r="K693" t="n">
         <v>1.388918172996225</v>
       </c>
     </row>
@@ -26811,6 +28892,9 @@
         </is>
       </c>
       <c r="J694" t="n">
+        <v>12</v>
+      </c>
+      <c r="K694" t="n">
         <v>1.388918172996225</v>
       </c>
     </row>
@@ -26849,6 +28933,9 @@
         </is>
       </c>
       <c r="J695" t="n">
+        <v>12</v>
+      </c>
+      <c r="K695" t="n">
         <v>1.393261488738817</v>
       </c>
     </row>
@@ -26887,6 +28974,9 @@
         </is>
       </c>
       <c r="J696" t="n">
+        <v>12</v>
+      </c>
+      <c r="K696" t="n">
         <v>1.393261488738817</v>
       </c>
     </row>
@@ -26925,6 +29015,9 @@
         </is>
       </c>
       <c r="J697" t="n">
+        <v>12</v>
+      </c>
+      <c r="K697" t="n">
         <v>1.390212443793561</v>
       </c>
     </row>
@@ -26963,6 +29056,9 @@
         </is>
       </c>
       <c r="J698" t="n">
+        <v>12</v>
+      </c>
+      <c r="K698" t="n">
         <v>1.379839203880424</v>
       </c>
     </row>
@@ -27001,6 +29097,9 @@
         </is>
       </c>
       <c r="J699" t="n">
+        <v>12</v>
+      </c>
+      <c r="K699" t="n">
         <v>1.357495870955582</v>
       </c>
     </row>
@@ -27039,6 +29138,9 @@
         </is>
       </c>
       <c r="J700" t="n">
+        <v>12</v>
+      </c>
+      <c r="K700" t="n">
         <v>1.32667353055303</v>
       </c>
     </row>
@@ -27077,6 +29179,9 @@
         </is>
       </c>
       <c r="J701" t="n">
+        <v>12</v>
+      </c>
+      <c r="K701" t="n">
         <v>1.22583659553023</v>
       </c>
     </row>
@@ -27115,6 +29220,9 @@
         </is>
       </c>
       <c r="J702" t="n">
+        <v>12</v>
+      </c>
+      <c r="K702" t="n">
         <v>1.069529902851154</v>
       </c>
     </row>
@@ -27153,6 +29261,9 @@
         </is>
       </c>
       <c r="J703" t="n">
+        <v>12</v>
+      </c>
+      <c r="K703" t="n">
         <v>0.8633362960477872</v>
       </c>
     </row>
@@ -27191,6 +29302,9 @@
         </is>
       </c>
       <c r="J704" t="n">
+        <v>12</v>
+      </c>
+      <c r="K704" t="n">
         <v>0.8633362960477872</v>
       </c>
     </row>
@@ -27229,6 +29343,9 @@
         </is>
       </c>
       <c r="J705" t="n">
+        <v>12</v>
+      </c>
+      <c r="K705" t="n">
         <v>0.7379015239748975</v>
       </c>
     </row>
@@ -27267,6 +29384,9 @@
         </is>
       </c>
       <c r="J706" t="n">
+        <v>12</v>
+      </c>
+      <c r="K706" t="n">
         <v>0.600382964889476</v>
       </c>
     </row>
@@ -27305,6 +29425,9 @@
         </is>
       </c>
       <c r="J707" t="n">
+        <v>12</v>
+      </c>
+      <c r="K707" t="n">
         <v>0.5415301479515319</v>
       </c>
     </row>
@@ -27343,6 +29466,9 @@
         </is>
       </c>
       <c r="J708" t="n">
+        <v>12</v>
+      </c>
+      <c r="K708" t="n">
         <v>0.5415301479515319</v>
       </c>
     </row>
@@ -27381,6 +29507,9 @@
         </is>
       </c>
       <c r="J709" t="n">
+        <v>12</v>
+      </c>
+      <c r="K709" t="n">
         <v>0.456056272287301</v>
       </c>
     </row>
@@ -27419,6 +29548,9 @@
         </is>
       </c>
       <c r="J710" t="n">
+        <v>12</v>
+      </c>
+      <c r="K710" t="n">
         <v>0.4627113003074372</v>
       </c>
     </row>
@@ -27457,6 +29589,9 @@
         </is>
       </c>
       <c r="J711" t="n">
+        <v>12</v>
+      </c>
+      <c r="K711" t="n">
         <v>0.6459922151241548</v>
       </c>
     </row>
@@ -27495,6 +29630,9 @@
         </is>
       </c>
       <c r="J712" t="n">
+        <v>12</v>
+      </c>
+      <c r="K712" t="n">
         <v>0.8054878637196621</v>
       </c>
     </row>
@@ -27533,6 +29671,9 @@
         </is>
       </c>
       <c r="J713" t="n">
+        <v>12</v>
+      </c>
+      <c r="K713" t="n">
         <v>0.8054878637196621</v>
       </c>
     </row>
@@ -27571,6 +29712,9 @@
         </is>
       </c>
       <c r="J714" t="n">
+        <v>12</v>
+      </c>
+      <c r="K714" t="n">
         <v>0.8175305434328686</v>
       </c>
     </row>
@@ -27609,6 +29753,9 @@
         </is>
       </c>
       <c r="J715" t="n">
+        <v>12</v>
+      </c>
+      <c r="K715" t="n">
         <v>0.8537506637873348</v>
       </c>
     </row>
@@ -27647,6 +29794,9 @@
         </is>
       </c>
       <c r="J716" t="n">
+        <v>12</v>
+      </c>
+      <c r="K716" t="n">
         <v>0.9410003644165074</v>
       </c>
     </row>
@@ -27685,6 +29835,9 @@
         </is>
       </c>
       <c r="J717" t="n">
+        <v>12</v>
+      </c>
+      <c r="K717" t="n">
         <v>0.9035678519035831</v>
       </c>
     </row>
@@ -27723,6 +29876,9 @@
         </is>
       </c>
       <c r="J718" t="n">
+        <v>12</v>
+      </c>
+      <c r="K718" t="n">
         <v>0.8739316917510455</v>
       </c>
     </row>
@@ -27761,6 +29917,9 @@
         </is>
       </c>
       <c r="J719" t="n">
+        <v>12</v>
+      </c>
+      <c r="K719" t="n">
         <v>0.8739316917510455</v>
       </c>
     </row>
@@ -27799,6 +29958,9 @@
         </is>
       </c>
       <c r="J720" t="n">
+        <v>12</v>
+      </c>
+      <c r="K720" t="n">
         <v>0.857571476277871</v>
       </c>
     </row>
@@ -27837,6 +29999,9 @@
         </is>
       </c>
       <c r="J721" t="n">
+        <v>12</v>
+      </c>
+      <c r="K721" t="n">
         <v>0.8336366264806322</v>
       </c>
     </row>
@@ -27875,6 +30040,9 @@
         </is>
       </c>
       <c r="J722" t="n">
+        <v>12</v>
+      </c>
+      <c r="K722" t="n">
         <v>0.8336366264806322</v>
       </c>
     </row>
@@ -27913,6 +30081,9 @@
         </is>
       </c>
       <c r="J723" t="n">
+        <v>12</v>
+      </c>
+      <c r="K723" t="n">
         <v>0.8336366264806322</v>
       </c>
     </row>
@@ -27951,6 +30122,9 @@
         </is>
       </c>
       <c r="J724" t="n">
+        <v>12</v>
+      </c>
+      <c r="K724" t="n">
         <v>0.8999185573363259</v>
       </c>
     </row>
@@ -27989,6 +30163,9 @@
         </is>
       </c>
       <c r="J725" t="n">
+        <v>12</v>
+      </c>
+      <c r="K725" t="n">
         <v>0.8999185573363259</v>
       </c>
     </row>
@@ -28027,6 +30204,9 @@
         </is>
       </c>
       <c r="J726" t="n">
+        <v>12</v>
+      </c>
+      <c r="K726" t="n">
         <v>0.9579656969267958</v>
       </c>
     </row>
@@ -28065,6 +30245,9 @@
         </is>
       </c>
       <c r="J727" t="n">
+        <v>12</v>
+      </c>
+      <c r="K727" t="n">
         <v>0.9579656969267958</v>
       </c>
     </row>
@@ -28103,6 +30286,9 @@
         </is>
       </c>
       <c r="J728" t="n">
+        <v>12</v>
+      </c>
+      <c r="K728" t="n">
         <v>0.9357829140065571</v>
       </c>
     </row>
@@ -28141,6 +30327,9 @@
         </is>
       </c>
       <c r="J729" t="n">
+        <v>12</v>
+      </c>
+      <c r="K729" t="n">
         <v>0.9357829140065571</v>
       </c>
     </row>
@@ -28179,6 +30368,9 @@
         </is>
       </c>
       <c r="J730" t="n">
+        <v>12</v>
+      </c>
+      <c r="K730" t="n">
         <v>0.9271736626573989</v>
       </c>
     </row>
@@ -28217,6 +30409,9 @@
         </is>
       </c>
       <c r="J731" t="n">
+        <v>12</v>
+      </c>
+      <c r="K731" t="n">
         <v>0.9448753482394272</v>
       </c>
     </row>
@@ -28255,6 +30450,9 @@
         </is>
       </c>
       <c r="J732" t="n">
+        <v>12</v>
+      </c>
+      <c r="K732" t="n">
         <v>1.180046920007321</v>
       </c>
     </row>
@@ -28293,6 +30491,9 @@
         </is>
       </c>
       <c r="J733" t="n">
+        <v>12</v>
+      </c>
+      <c r="K733" t="n">
         <v>1.274051686376322</v>
       </c>
     </row>
@@ -28331,6 +30532,9 @@
         </is>
       </c>
       <c r="J734" t="n">
+        <v>12</v>
+      </c>
+      <c r="K734" t="n">
         <v>1.404131438623516</v>
       </c>
     </row>
@@ -28369,6 +30573,9 @@
         </is>
       </c>
       <c r="J735" t="n">
+        <v>12</v>
+      </c>
+      <c r="K735" t="n">
         <v>1.45289325137742</v>
       </c>
     </row>
@@ -28407,6 +30614,9 @@
         </is>
       </c>
       <c r="J736" t="n">
+        <v>12</v>
+      </c>
+      <c r="K736" t="n">
         <v>1.480714902937465</v>
       </c>
     </row>
@@ -28445,6 +30655,9 @@
         </is>
       </c>
       <c r="J737" t="n">
+        <v>12</v>
+      </c>
+      <c r="K737" t="n">
         <v>1.480714902937465</v>
       </c>
     </row>
@@ -28483,6 +30696,9 @@
         </is>
       </c>
       <c r="J738" t="n">
+        <v>12</v>
+      </c>
+      <c r="K738" t="n">
         <v>1.426528439507999</v>
       </c>
     </row>
@@ -28521,6 +30737,9 @@
         </is>
       </c>
       <c r="J739" t="n">
+        <v>12</v>
+      </c>
+      <c r="K739" t="n">
         <v>1.426528439507999</v>
       </c>
     </row>
@@ -28559,6 +30778,9 @@
         </is>
       </c>
       <c r="J740" t="n">
+        <v>12</v>
+      </c>
+      <c r="K740" t="n">
         <v>1.320483388157286</v>
       </c>
     </row>
@@ -28597,6 +30819,9 @@
         </is>
       </c>
       <c r="J741" t="n">
+        <v>12</v>
+      </c>
+      <c r="K741" t="n">
         <v>1.27395507353025</v>
       </c>
     </row>
@@ -28635,6 +30860,9 @@
         </is>
       </c>
       <c r="J742" t="n">
+        <v>12</v>
+      </c>
+      <c r="K742" t="n">
         <v>1.27395507353025</v>
       </c>
     </row>
@@ -28673,6 +30901,9 @@
         </is>
       </c>
       <c r="J743" t="n">
+        <v>12</v>
+      </c>
+      <c r="K743" t="n">
         <v>1.265384868890062</v>
       </c>
     </row>
@@ -28711,6 +30942,9 @@
         </is>
       </c>
       <c r="J744" t="n">
+        <v>12</v>
+      </c>
+      <c r="K744" t="n">
         <v>1.303822642536857</v>
       </c>
     </row>
@@ -28749,6 +30983,9 @@
         </is>
       </c>
       <c r="J745" t="n">
+        <v>12</v>
+      </c>
+      <c r="K745" t="n">
         <v>1.303822642536857</v>
       </c>
     </row>
@@ -28787,6 +31024,9 @@
         </is>
       </c>
       <c r="J746" t="n">
+        <v>12</v>
+      </c>
+      <c r="K746" t="n">
         <v>1.363041934445349</v>
       </c>
     </row>
@@ -28825,6 +31065,9 @@
         </is>
       </c>
       <c r="J747" t="n">
+        <v>12</v>
+      </c>
+      <c r="K747" t="n">
         <v>1.436695540169181</v>
       </c>
     </row>
@@ -28863,6 +31106,9 @@
         </is>
       </c>
       <c r="J748" t="n">
+        <v>12</v>
+      </c>
+      <c r="K748" t="n">
         <v>1.436695540169181</v>
       </c>
     </row>
@@ -28901,6 +31147,9 @@
         </is>
       </c>
       <c r="J749" t="n">
+        <v>12</v>
+      </c>
+      <c r="K749" t="n">
         <v>1.502618499091818</v>
       </c>
     </row>
@@ -28939,6 +31188,9 @@
         </is>
       </c>
       <c r="J750" t="n">
+        <v>12</v>
+      </c>
+      <c r="K750" t="n">
         <v>1.502618499091818</v>
       </c>
     </row>
@@ -28977,6 +31229,9 @@
         </is>
       </c>
       <c r="J751" t="n">
+        <v>12</v>
+      </c>
+      <c r="K751" t="n">
         <v>1.441810765271844</v>
       </c>
     </row>
@@ -29015,6 +31270,9 @@
         </is>
       </c>
       <c r="J752" t="n">
+        <v>12</v>
+      </c>
+      <c r="K752" t="n">
         <v>1.404795770268469</v>
       </c>
     </row>
@@ -29053,6 +31311,9 @@
         </is>
       </c>
       <c r="J753" t="n">
+        <v>12</v>
+      </c>
+      <c r="K753" t="n">
         <v>1.256752776860887</v>
       </c>
     </row>
@@ -29091,6 +31352,9 @@
         </is>
       </c>
       <c r="J754" t="n">
+        <v>12</v>
+      </c>
+      <c r="K754" t="n">
         <v>1.256752776860887</v>
       </c>
     </row>
@@ -29129,6 +31393,9 @@
         </is>
       </c>
       <c r="J755" t="n">
+        <v>12</v>
+      </c>
+      <c r="K755" t="n">
         <v>1.203118079175934</v>
       </c>
     </row>
@@ -29167,6 +31434,9 @@
         </is>
       </c>
       <c r="J756" t="n">
+        <v>12</v>
+      </c>
+      <c r="K756" t="n">
         <v>1.172163889343052</v>
       </c>
     </row>
@@ -29205,6 +31475,9 @@
         </is>
       </c>
       <c r="J757" t="n">
+        <v>12</v>
+      </c>
+      <c r="K757" t="n">
         <v>1.172163889343052</v>
       </c>
     </row>
@@ -29243,6 +31516,9 @@
         </is>
       </c>
       <c r="J758" t="n">
+        <v>12</v>
+      </c>
+      <c r="K758" t="n">
         <v>1.196848691332015</v>
       </c>
     </row>
@@ -29281,6 +31557,9 @@
         </is>
       </c>
       <c r="J759" t="n">
+        <v>12</v>
+      </c>
+      <c r="K759" t="n">
         <v>1.279988141944838</v>
       </c>
     </row>
@@ -29319,6 +31598,9 @@
         </is>
       </c>
       <c r="J760" t="n">
+        <v>12</v>
+      </c>
+      <c r="K760" t="n">
         <v>1.33774645115203</v>
       </c>
     </row>
@@ -29357,6 +31639,9 @@
         </is>
       </c>
       <c r="J761" t="n">
+        <v>12</v>
+      </c>
+      <c r="K761" t="n">
         <v>1.33774645115203</v>
       </c>
     </row>
@@ -29395,6 +31680,9 @@
         </is>
       </c>
       <c r="J762" t="n">
+        <v>12</v>
+      </c>
+      <c r="K762" t="n">
         <v>1.339094749193525</v>
       </c>
     </row>
@@ -29433,6 +31721,9 @@
         </is>
       </c>
       <c r="J763" t="n">
+        <v>12</v>
+      </c>
+      <c r="K763" t="n">
         <v>1.238409889066349</v>
       </c>
     </row>
@@ -29471,6 +31762,9 @@
         </is>
       </c>
       <c r="J764" t="n">
+        <v>12</v>
+      </c>
+      <c r="K764" t="n">
         <v>1.238409889066349</v>
       </c>
     </row>
@@ -29509,6 +31803,9 @@
         </is>
       </c>
       <c r="J765" t="n">
+        <v>12</v>
+      </c>
+      <c r="K765" t="n">
         <v>1.153798433927621</v>
       </c>
     </row>
@@ -29547,6 +31844,9 @@
         </is>
       </c>
       <c r="J766" t="n">
+        <v>12</v>
+      </c>
+      <c r="K766" t="n">
         <v>0.9054037680415632</v>
       </c>
     </row>
@@ -29585,6 +31885,9 @@
         </is>
       </c>
       <c r="J767" t="n">
+        <v>12</v>
+      </c>
+      <c r="K767" t="n">
         <v>0.9054037680415632</v>
       </c>
     </row>
@@ -29623,6 +31926,9 @@
         </is>
       </c>
       <c r="J768" t="n">
+        <v>12</v>
+      </c>
+      <c r="K768" t="n">
         <v>0.7822182797546607</v>
       </c>
     </row>
@@ -29661,6 +31967,9 @@
         </is>
       </c>
       <c r="J769" t="n">
+        <v>12</v>
+      </c>
+      <c r="K769" t="n">
         <v>0.6931997822076109</v>
       </c>
     </row>
@@ -29699,6 +32008,9 @@
         </is>
       </c>
       <c r="J770" t="n">
+        <v>12</v>
+      </c>
+      <c r="K770" t="n">
         <v>0.4303462304751228</v>
       </c>
     </row>
@@ -29737,6 +32049,9 @@
         </is>
       </c>
       <c r="J771" t="n">
+        <v>12</v>
+      </c>
+      <c r="K771" t="n">
         <v>0.425736883868912</v>
       </c>
     </row>
@@ -29775,6 +32090,9 @@
         </is>
       </c>
       <c r="J772" t="n">
+        <v>12</v>
+      </c>
+      <c r="K772" t="n">
         <v>0.425736883868912</v>
       </c>
     </row>
@@ -29813,6 +32131,9 @@
         </is>
       </c>
       <c r="J773" t="n">
+        <v>12</v>
+      </c>
+      <c r="K773" t="n">
         <v>0.425736883868912</v>
       </c>
     </row>
@@ -29851,6 +32172,9 @@
         </is>
       </c>
       <c r="J774" t="n">
+        <v>12</v>
+      </c>
+      <c r="K774" t="n">
         <v>0.4741406117715971</v>
       </c>
     </row>
@@ -29889,6 +32213,9 @@
         </is>
       </c>
       <c r="J775" t="n">
+        <v>12</v>
+      </c>
+      <c r="K775" t="n">
         <v>0.6179878715603118</v>
       </c>
     </row>
@@ -29927,6 +32254,9 @@
         </is>
       </c>
       <c r="J776" t="n">
+        <v>12</v>
+      </c>
+      <c r="K776" t="n">
         <v>0.7245889203903195</v>
       </c>
     </row>
@@ -29965,6 +32295,9 @@
         </is>
       </c>
       <c r="J777" t="n">
+        <v>12</v>
+      </c>
+      <c r="K777" t="n">
         <v>0.7245889203903195</v>
       </c>
     </row>
@@ -30003,6 +32336,9 @@
         </is>
       </c>
       <c r="J778" t="n">
+        <v>12</v>
+      </c>
+      <c r="K778" t="n">
         <v>0.7483247600716969</v>
       </c>
     </row>
@@ -30041,6 +32377,9 @@
         </is>
       </c>
       <c r="J779" t="n">
+        <v>12</v>
+      </c>
+      <c r="K779" t="n">
         <v>0.8256520674606761</v>
       </c>
     </row>
@@ -30079,6 +32418,9 @@
         </is>
       </c>
       <c r="J780" t="n">
+        <v>12</v>
+      </c>
+      <c r="K780" t="n">
         <v>0.8256520674606761</v>
       </c>
     </row>
@@ -30117,6 +32459,9 @@
         </is>
       </c>
       <c r="J781" t="n">
+        <v>12</v>
+      </c>
+      <c r="K781" t="n">
         <v>0.8256520674606761</v>
       </c>
     </row>
@@ -30155,6 +32500,9 @@
         </is>
       </c>
       <c r="J782" t="n">
+        <v>12</v>
+      </c>
+      <c r="K782" t="n">
         <v>0.8312276366585113</v>
       </c>
     </row>
@@ -30193,6 +32541,9 @@
         </is>
       </c>
       <c r="J783" t="n">
+        <v>12</v>
+      </c>
+      <c r="K783" t="n">
         <v>0.8312276366585113</v>
       </c>
     </row>
@@ -30231,6 +32582,9 @@
         </is>
       </c>
       <c r="J784" t="n">
+        <v>12</v>
+      </c>
+      <c r="K784" t="n">
         <v>0.8195009571327245</v>
       </c>
     </row>
@@ -30269,6 +32623,9 @@
         </is>
       </c>
       <c r="J785" t="n">
+        <v>12</v>
+      </c>
+      <c r="K785" t="n">
         <v>0.7411302170477566</v>
       </c>
     </row>
@@ -30307,6 +32664,9 @@
         </is>
       </c>
       <c r="J786" t="n">
+        <v>12</v>
+      </c>
+      <c r="K786" t="n">
         <v>0.7489625352557558</v>
       </c>
     </row>
@@ -30345,6 +32705,9 @@
         </is>
       </c>
       <c r="J787" t="n">
+        <v>12</v>
+      </c>
+      <c r="K787" t="n">
         <v>0.7571139453758954</v>
       </c>
     </row>
@@ -30383,6 +32746,9 @@
         </is>
       </c>
       <c r="J788" t="n">
+        <v>12</v>
+      </c>
+      <c r="K788" t="n">
         <v>0.7571139453758954</v>
       </c>
     </row>
@@ -30421,6 +32787,9 @@
         </is>
       </c>
       <c r="J789" t="n">
+        <v>12</v>
+      </c>
+      <c r="K789" t="n">
         <v>0.7640387245539881</v>
       </c>
     </row>
@@ -30459,6 +32828,9 @@
         </is>
       </c>
       <c r="J790" t="n">
+        <v>12</v>
+      </c>
+      <c r="K790" t="n">
         <v>0.8931849015680801</v>
       </c>
     </row>
@@ -30497,6 +32869,9 @@
         </is>
       </c>
       <c r="J791" t="n">
+        <v>12</v>
+      </c>
+      <c r="K791" t="n">
         <v>0.9409017862981774</v>
       </c>
     </row>
@@ -30535,6 +32910,9 @@
         </is>
       </c>
       <c r="J792" t="n">
+        <v>12</v>
+      </c>
+      <c r="K792" t="n">
         <v>0.9840217771270924</v>
       </c>
     </row>
@@ -30573,6 +32951,9 @@
         </is>
       </c>
       <c r="J793" t="n">
+        <v>12</v>
+      </c>
+      <c r="K793" t="n">
         <v>1.013839090125002</v>
       </c>
     </row>
@@ -30611,6 +32992,9 @@
         </is>
       </c>
       <c r="J794" t="n">
+        <v>12</v>
+      </c>
+      <c r="K794" t="n">
         <v>1.021732293330856</v>
       </c>
     </row>
@@ -30649,6 +33033,9 @@
         </is>
       </c>
       <c r="J795" t="n">
+        <v>12</v>
+      </c>
+      <c r="K795" t="n">
         <v>1.021510315205498</v>
       </c>
     </row>
@@ -30687,6 +33074,9 @@
         </is>
       </c>
       <c r="J796" t="n">
+        <v>12</v>
+      </c>
+      <c r="K796" t="n">
         <v>1.024611421402347</v>
       </c>
     </row>
@@ -30725,6 +33115,9 @@
         </is>
       </c>
       <c r="J797" t="n">
+        <v>12</v>
+      </c>
+      <c r="K797" t="n">
         <v>1.023170799233587</v>
       </c>
     </row>
@@ -30763,6 +33156,9 @@
         </is>
       </c>
       <c r="J798" t="n">
+        <v>12</v>
+      </c>
+      <c r="K798" t="n">
         <v>1.037660039716004</v>
       </c>
     </row>
@@ -30801,6 +33197,9 @@
         </is>
       </c>
       <c r="J799" t="n">
+        <v>12</v>
+      </c>
+      <c r="K799" t="n">
         <v>1.037660039716004</v>
       </c>
     </row>
@@ -30839,6 +33238,9 @@
         </is>
       </c>
       <c r="J800" t="n">
+        <v>12</v>
+      </c>
+      <c r="K800" t="n">
         <v>1.035876368716922</v>
       </c>
     </row>
@@ -30877,6 +33279,9 @@
         </is>
       </c>
       <c r="J801" t="n">
+        <v>12</v>
+      </c>
+      <c r="K801" t="n">
         <v>1.02304057128544</v>
       </c>
     </row>
@@ -30915,6 +33320,9 @@
         </is>
       </c>
       <c r="J802" t="n">
+        <v>12</v>
+      </c>
+      <c r="K802" t="n">
         <v>1.04993575399346</v>
       </c>
     </row>
@@ -30953,6 +33361,9 @@
         </is>
       </c>
       <c r="J803" t="n">
+        <v>12</v>
+      </c>
+      <c r="K803" t="n">
         <v>1.045087730343041</v>
       </c>
     </row>
@@ -30991,6 +33402,9 @@
         </is>
       </c>
       <c r="J804" t="n">
+        <v>12</v>
+      </c>
+      <c r="K804" t="n">
         <v>1.01356277959666</v>
       </c>
     </row>
@@ -31029,6 +33443,9 @@
         </is>
       </c>
       <c r="J805" t="n">
+        <v>12</v>
+      </c>
+      <c r="K805" t="n">
         <v>0.9865866182871941</v>
       </c>
     </row>
@@ -31067,6 +33484,9 @@
         </is>
       </c>
       <c r="J806" t="n">
+        <v>12</v>
+      </c>
+      <c r="K806" t="n">
         <v>0.9430045533821274</v>
       </c>
     </row>
@@ -31105,6 +33525,9 @@
         </is>
       </c>
       <c r="J807" t="n">
+        <v>12</v>
+      </c>
+      <c r="K807" t="n">
         <v>0.8991554120777662</v>
       </c>
     </row>
@@ -31143,6 +33566,9 @@
         </is>
       </c>
       <c r="J808" t="n">
+        <v>12</v>
+      </c>
+      <c r="K808" t="n">
         <v>0.8901445688078437</v>
       </c>
     </row>
@@ -31181,6 +33607,9 @@
         </is>
       </c>
       <c r="J809" t="n">
+        <v>12</v>
+      </c>
+      <c r="K809" t="n">
         <v>0.8901445688078437</v>
       </c>
     </row>
@@ -31219,6 +33648,9 @@
         </is>
       </c>
       <c r="J810" t="n">
+        <v>12</v>
+      </c>
+      <c r="K810" t="n">
         <v>0.887951663664214</v>
       </c>
     </row>
@@ -31257,6 +33689,9 @@
         </is>
       </c>
       <c r="J811" t="n">
+        <v>12</v>
+      </c>
+      <c r="K811" t="n">
         <v>0.8334971394147027</v>
       </c>
     </row>
@@ -31295,6 +33730,9 @@
         </is>
       </c>
       <c r="J812" t="n">
+        <v>12</v>
+      </c>
+      <c r="K812" t="n">
         <v>0.6864573158648335</v>
       </c>
     </row>
@@ -31333,6 +33771,9 @@
         </is>
       </c>
       <c r="J813" t="n">
+        <v>12</v>
+      </c>
+      <c r="K813" t="n">
         <v>0.6864573158648335</v>
       </c>
     </row>
@@ -31371,6 +33812,9 @@
         </is>
       </c>
       <c r="J814" t="n">
+        <v>12</v>
+      </c>
+      <c r="K814" t="n">
         <v>0.5737825821688167</v>
       </c>
     </row>
@@ -31409,6 +33853,9 @@
         </is>
       </c>
       <c r="J815" t="n">
+        <v>12</v>
+      </c>
+      <c r="K815" t="n">
         <v>0.5737825821688167</v>
       </c>
     </row>
@@ -31447,6 +33894,9 @@
         </is>
       </c>
       <c r="J816" t="n">
+        <v>12</v>
+      </c>
+      <c r="K816" t="n">
         <v>0.4717068837457349</v>
       </c>
     </row>
@@ -31485,6 +33935,9 @@
         </is>
       </c>
       <c r="J817" t="n">
+        <v>12</v>
+      </c>
+      <c r="K817" t="n">
         <v>0.4717068837457349</v>
       </c>
     </row>
@@ -31523,6 +33976,9 @@
         </is>
       </c>
       <c r="J818" t="n">
+        <v>12</v>
+      </c>
+      <c r="K818" t="n">
         <v>0.2742043165589557</v>
       </c>
     </row>
@@ -31561,6 +34017,9 @@
         </is>
       </c>
       <c r="J819" t="n">
+        <v>12</v>
+      </c>
+      <c r="K819" t="n">
         <v>0.2742043165589557</v>
       </c>
     </row>
@@ -31599,6 +34058,9 @@
         </is>
       </c>
       <c r="J820" t="n">
+        <v>12</v>
+      </c>
+      <c r="K820" t="n">
         <v>0.1860603252607773</v>
       </c>
     </row>
@@ -31637,6 +34099,9 @@
         </is>
       </c>
       <c r="J821" t="n">
+        <v>12</v>
+      </c>
+      <c r="K821" t="n">
         <v>0.149548527462926</v>
       </c>
     </row>
@@ -31675,6 +34140,9 @@
         </is>
       </c>
       <c r="J822" t="n">
+        <v>12</v>
+      </c>
+      <c r="K822" t="n">
         <v>0.08941611297199926</v>
       </c>
     </row>
@@ -31713,6 +34181,9 @@
         </is>
       </c>
       <c r="J823" t="n">
+        <v>12</v>
+      </c>
+      <c r="K823" t="n">
         <v>0.08941611297199926</v>
       </c>
     </row>

--- a/results/block2_results/area/Normal_1/branches/dataframes/dataset_LCA_B01_Normal_1.xlsx
+++ b/results/block2_results/area/Normal_1/branches/dataframes/dataset_LCA_B01_Normal_1.xlsx
@@ -523,7 +523,7 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>24.44938674448072</v>
+        <v>22.73756640125236</v>
       </c>
     </row>
     <row r="3">
@@ -564,7 +564,7 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
     </row>
     <row r="5">
@@ -646,7 +646,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
     </row>
     <row r="6">
@@ -687,7 +687,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>16.22537890841612</v>
+        <v>16.29324050952215</v>
       </c>
     </row>
     <row r="7">
@@ -728,7 +728,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>15.92519383307983</v>
+        <v>15.99543613326018</v>
       </c>
     </row>
     <row r="8">
@@ -769,7 +769,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>15.55123726155539</v>
+        <v>15.62439489880449</v>
       </c>
     </row>
     <row r="9">
@@ -810,7 +810,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>15.50392193361757</v>
+        <v>15.51994773639756</v>
       </c>
     </row>
     <row r="10">
@@ -851,7 +851,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>15.43409332138252</v>
+        <v>15.51994773639756</v>
       </c>
     </row>
     <row r="11">
@@ -892,7 +892,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>15.43409332138252</v>
+        <v>15.51994773639756</v>
       </c>
     </row>
     <row r="12">
@@ -933,7 +933,7 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>14.91383648998964</v>
+        <v>14.86969785602394</v>
       </c>
     </row>
     <row r="13">
@@ -974,7 +974,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>14.91383648998964</v>
+        <v>14.86959415022024</v>
       </c>
     </row>
     <row r="14">
@@ -1015,7 +1015,7 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>13.96252814601202</v>
+        <v>13.91864954866779</v>
       </c>
     </row>
     <row r="15">
@@ -1056,7 +1056,7 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>12.8845474029381</v>
+        <v>12.87463469178007</v>
       </c>
     </row>
     <row r="16">
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>12.56557511094277</v>
+        <v>12.56213898660848</v>
       </c>
     </row>
     <row r="17">
@@ -1138,7 +1138,7 @@
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>12.56557511094277</v>
+        <v>12.55954078162074</v>
       </c>
     </row>
     <row r="18">
@@ -1179,7 +1179,7 @@
         <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>12.42650727241244</v>
+        <v>12.41804037237105</v>
       </c>
     </row>
     <row r="19">
@@ -1220,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>12.61222121789064</v>
+        <v>12.61235401004429</v>
       </c>
     </row>
     <row r="20">
@@ -1261,7 +1261,7 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>12.6149723565889</v>
+        <v>12.61235401004429</v>
       </c>
     </row>
     <row r="21">
@@ -1302,7 +1302,7 @@
         <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>12.6149723565889</v>
+        <v>12.61235401004429</v>
       </c>
     </row>
     <row r="22">
@@ -1343,7 +1343,7 @@
         <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>12.88726856229838</v>
+        <v>12.89114719647669</v>
       </c>
     </row>
     <row r="23">
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>13.08268414389388</v>
+        <v>13.08601325120547</v>
       </c>
     </row>
     <row r="24">
@@ -1425,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>13.11655963642752</v>
+        <v>13.1112961343127</v>
       </c>
     </row>
     <row r="25">
@@ -1466,7 +1466,7 @@
         <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>13.06477406907523</v>
+        <v>13.06050754757873</v>
       </c>
     </row>
     <row r="26">
@@ -1507,7 +1507,7 @@
         <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>13.00822550737505</v>
+        <v>13.00560877247013</v>
       </c>
     </row>
     <row r="27">
@@ -1548,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>13.00822550737505</v>
+        <v>13.00560877247013</v>
       </c>
     </row>
     <row r="28">
@@ -1589,7 +1589,7 @@
         <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>12.82946633796654</v>
+        <v>12.82287865109407</v>
       </c>
     </row>
     <row r="29">
@@ -1630,7 +1630,7 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>12.72199060197538</v>
+        <v>12.71927945377958</v>
       </c>
     </row>
     <row r="30">
@@ -1671,7 +1671,7 @@
         <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>12.76786570293602</v>
+        <v>12.77031387086443</v>
       </c>
     </row>
     <row r="31">
@@ -1712,7 +1712,7 @@
         <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>12.94918332241907</v>
+        <v>12.95485717835137</v>
       </c>
     </row>
     <row r="32">
@@ -1753,7 +1753,7 @@
         <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>13.29202663846189</v>
+        <v>13.29520804089071</v>
       </c>
     </row>
     <row r="33">
@@ -1794,7 +1794,7 @@
         <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>13.29202663846189</v>
+        <v>13.29710102990174</v>
       </c>
     </row>
     <row r="34">
@@ -1835,7 +1835,7 @@
         <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>13.74461230569916</v>
+        <v>13.75403391875815</v>
       </c>
     </row>
     <row r="35">
@@ -1876,7 +1876,7 @@
         <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>14.01711486461985</v>
+        <v>14.02366076953313</v>
       </c>
     </row>
     <row r="36">
@@ -1917,7 +1917,7 @@
         <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>14.02341868198291</v>
+        <v>14.02914779581027</v>
       </c>
     </row>
     <row r="37">
@@ -1958,7 +1958,7 @@
         <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>14.4136984000467</v>
+        <v>14.4135370281724</v>
       </c>
     </row>
     <row r="38">
@@ -1999,7 +1999,7 @@
         <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>14.4136984000467</v>
+        <v>14.4135370281724</v>
       </c>
     </row>
     <row r="39">
@@ -2040,7 +2040,7 @@
         <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>14.4136984000467</v>
+        <v>14.4135370281724</v>
       </c>
     </row>
     <row r="40">
@@ -2081,7 +2081,7 @@
         <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>14.37286417316269</v>
+        <v>14.37156478609048</v>
       </c>
     </row>
     <row r="41">
@@ -2122,7 +2122,7 @@
         <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>14.36056284287022</v>
+        <v>14.36020323793898</v>
       </c>
     </row>
     <row r="42">
@@ -2163,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="K42" t="n">
-        <v>14.32918239439808</v>
+        <v>14.3290624341717</v>
       </c>
     </row>
     <row r="43">
@@ -2204,7 +2204,7 @@
         <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>14.33140447444988</v>
+        <v>14.3325069672442</v>
       </c>
     </row>
     <row r="44">
@@ -2245,7 +2245,7 @@
         <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>14.33266758623184</v>
+        <v>14.33386682670858</v>
       </c>
     </row>
     <row r="45">
@@ -2286,7 +2286,7 @@
         <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>14.47432312940295</v>
+        <v>14.4778957262455</v>
       </c>
     </row>
     <row r="46">
@@ -2327,7 +2327,7 @@
         <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>14.69408070284003</v>
+        <v>14.70491730440479</v>
       </c>
     </row>
     <row r="47">
@@ -2368,7 +2368,7 @@
         <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>14.90097207929845</v>
+        <v>14.70491730440479</v>
       </c>
     </row>
     <row r="48">
@@ -2409,7 +2409,7 @@
         <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>14.90097207929845</v>
+        <v>14.9139321578258</v>
       </c>
     </row>
     <row r="49">
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>15.39058793177672</v>
+        <v>15.39818561758153</v>
       </c>
     </row>
     <row r="50">
@@ -2491,7 +2491,7 @@
         <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>15.55279586015389</v>
+        <v>15.55789316181155</v>
       </c>
     </row>
     <row r="51">
@@ -2532,7 +2532,7 @@
         <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>16.46410452789935</v>
+        <v>16.44727977295515</v>
       </c>
     </row>
     <row r="52">
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>17.37544874440357</v>
+        <v>17.34712478394894</v>
       </c>
     </row>
     <row r="53">
@@ -2614,7 +2614,7 @@
         <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>18.99504856873714</v>
+        <v>19.09058139794423</v>
       </c>
     </row>
     <row r="54">
@@ -2655,7 +2655,7 @@
         <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>19.35440687995326</v>
+        <v>19.36955181416631</v>
       </c>
     </row>
     <row r="55">
@@ -2696,7 +2696,7 @@
         <v>11</v>
       </c>
       <c r="K55" t="n">
-        <v>20.85858809627996</v>
+        <v>20.81524252050833</v>
       </c>
     </row>
     <row r="56">
@@ -2737,7 +2737,7 @@
         <v>11</v>
       </c>
       <c r="K56" t="n">
-        <v>20.89169658899361</v>
+        <v>20.84331547113941</v>
       </c>
     </row>
     <row r="57">
@@ -2778,7 +2778,7 @@
         <v>11</v>
       </c>
       <c r="K57" t="n">
-        <v>21.75595998124422</v>
+        <v>21.75006574949062</v>
       </c>
     </row>
     <row r="58">
@@ -2819,7 +2819,7 @@
         <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>22.23426731578168</v>
+        <v>22.25305706353997</v>
       </c>
     </row>
     <row r="59">
@@ -2860,7 +2860,7 @@
         <v>11</v>
       </c>
       <c r="K59" t="n">
-        <v>21.95138014089535</v>
+        <v>21.9712890272184</v>
       </c>
     </row>
     <row r="60">
@@ -2901,7 +2901,7 @@
         <v>11</v>
       </c>
       <c r="K60" t="n">
-        <v>24.63649424087505</v>
+        <v>24.65959851968772</v>
       </c>
     </row>
     <row r="61">
@@ -2942,7 +2942,7 @@
         <v>11</v>
       </c>
       <c r="K61" t="n">
-        <v>25.18536911583633</v>
+        <v>24.65959851968772</v>
       </c>
     </row>
     <row r="62">
@@ -2983,7 +2983,7 @@
         <v>11</v>
       </c>
       <c r="K62" t="n">
-        <v>27.31329478260586</v>
+        <v>27.34628858172988</v>
       </c>
     </row>
     <row r="63">
@@ -3024,7 +3024,7 @@
         <v>11</v>
       </c>
       <c r="K63" t="n">
-        <v>27.18205504873007</v>
+        <v>27.25367540568017</v>
       </c>
     </row>
     <row r="64">
@@ -3065,7 +3065,7 @@
         <v>11</v>
       </c>
       <c r="K64" t="n">
-        <v>26.71182468007363</v>
+        <v>26.69655756684118</v>
       </c>
     </row>
     <row r="65">
@@ -3106,7 +3106,7 @@
         <v>11</v>
       </c>
       <c r="K65" t="n">
-        <v>26.61477337250786</v>
+        <v>26.59925138949226</v>
       </c>
     </row>
     <row r="66">
@@ -3147,7 +3147,7 @@
         <v>11</v>
       </c>
       <c r="K66" t="n">
-        <v>9.819882390104297</v>
+        <v>9.796381120057267</v>
       </c>
     </row>
     <row r="67">
@@ -3188,7 +3188,7 @@
         <v>11</v>
       </c>
       <c r="K67" t="n">
-        <v>9.819882390104297</v>
+        <v>9.796381120057267</v>
       </c>
     </row>
     <row r="68">
@@ -3229,7 +3229,7 @@
         <v>11</v>
       </c>
       <c r="K68" t="n">
-        <v>9.745667235392832</v>
+        <v>9.741185129511519</v>
       </c>
     </row>
     <row r="69">
@@ -3270,7 +3270,7 @@
         <v>11</v>
       </c>
       <c r="K69" t="n">
-        <v>9.745667235392832</v>
+        <v>9.741185129511519</v>
       </c>
     </row>
     <row r="70">
@@ -3311,7 +3311,7 @@
         <v>11</v>
       </c>
       <c r="K70" t="n">
-        <v>9.75609596068019</v>
+        <v>9.74618151868393</v>
       </c>
     </row>
     <row r="71">
@@ -3352,7 +3352,7 @@
         <v>11</v>
       </c>
       <c r="K71" t="n">
-        <v>9.75609596068019</v>
+        <v>9.74618151868393</v>
       </c>
     </row>
     <row r="72">
@@ -3393,7 +3393,7 @@
         <v>11</v>
       </c>
       <c r="K72" t="n">
-        <v>9.981290382682612</v>
+        <v>9.934397059286889</v>
       </c>
     </row>
     <row r="73">
@@ -3434,7 +3434,7 @@
         <v>11</v>
       </c>
       <c r="K73" t="n">
-        <v>9.981290382682612</v>
+        <v>9.934397059286889</v>
       </c>
     </row>
     <row r="74">
@@ -3475,7 +3475,7 @@
         <v>11</v>
       </c>
       <c r="K74" t="n">
-        <v>12.09167051507188</v>
+        <v>12.10118790918484</v>
       </c>
     </row>
     <row r="75">
@@ -3516,7 +3516,7 @@
         <v>11</v>
       </c>
       <c r="K75" t="n">
-        <v>12.31620569749018</v>
+        <v>12.32151040736936</v>
       </c>
     </row>
     <row r="76">
@@ -3557,7 +3557,7 @@
         <v>11</v>
       </c>
       <c r="K76" t="n">
-        <v>12.66141284150133</v>
+        <v>12.66772849390226</v>
       </c>
     </row>
     <row r="77">
@@ -3598,7 +3598,7 @@
         <v>11</v>
       </c>
       <c r="K77" t="n">
-        <v>13.00449390422686</v>
+        <v>12.9966977715787</v>
       </c>
     </row>
     <row r="78">
@@ -3639,7 +3639,7 @@
         <v>11</v>
       </c>
       <c r="K78" t="n">
-        <v>9.12738816852228</v>
+        <v>9.12138807972668</v>
       </c>
     </row>
     <row r="79">
@@ -3680,7 +3680,7 @@
         <v>11</v>
       </c>
       <c r="K79" t="n">
-        <v>8.68658704571123</v>
+        <v>8.685163559773121</v>
       </c>
     </row>
     <row r="80">
@@ -3721,7 +3721,7 @@
         <v>11</v>
       </c>
       <c r="K80" t="n">
-        <v>8.681894726582</v>
+        <v>8.680606216873509</v>
       </c>
     </row>
     <row r="81">
@@ -3762,7 +3762,7 @@
         <v>11</v>
       </c>
       <c r="K81" t="n">
-        <v>8.693004759293984</v>
+        <v>8.693592028238019</v>
       </c>
     </row>
     <row r="82">
@@ -3803,7 +3803,7 @@
         <v>11</v>
       </c>
       <c r="K82" t="n">
-        <v>8.725149125649589</v>
+        <v>8.725792306726596</v>
       </c>
     </row>
     <row r="83">
@@ -3844,7 +3844,7 @@
         <v>11</v>
       </c>
       <c r="K83" t="n">
-        <v>8.767374629969833</v>
+        <v>8.767927440838232</v>
       </c>
     </row>
     <row r="84">
@@ -3885,7 +3885,7 @@
         <v>11</v>
       </c>
       <c r="K84" t="n">
-        <v>8.810038227616156</v>
+        <v>8.811057918534789</v>
       </c>
     </row>
     <row r="85">
@@ -3926,7 +3926,7 @@
         <v>11</v>
       </c>
       <c r="K85" t="n">
-        <v>8.810038227616156</v>
+        <v>8.811057918534789</v>
       </c>
     </row>
     <row r="86">
@@ -3967,7 +3967,7 @@
         <v>11</v>
       </c>
       <c r="K86" t="n">
-        <v>8.979920966893374</v>
+        <v>8.981518238291311</v>
       </c>
     </row>
     <row r="87">
@@ -4008,7 +4008,7 @@
         <v>11</v>
       </c>
       <c r="K87" t="n">
-        <v>9.189485465294592</v>
+        <v>9.191916534395689</v>
       </c>
     </row>
     <row r="88">
@@ -4049,7 +4049,7 @@
         <v>11</v>
       </c>
       <c r="K88" t="n">
-        <v>9.20061339885968</v>
+        <v>9.202788083270709</v>
       </c>
     </row>
     <row r="89">
@@ -4090,7 +4090,7 @@
         <v>11</v>
       </c>
       <c r="K89" t="n">
-        <v>9.385776211530537</v>
+        <v>9.388153658429088</v>
       </c>
     </row>
     <row r="90">
@@ -4131,7 +4131,7 @@
         <v>11</v>
       </c>
       <c r="K90" t="n">
-        <v>9.385776211530537</v>
+        <v>9.388153658429088</v>
       </c>
     </row>
     <row r="91">
@@ -4172,7 +4172,7 @@
         <v>11</v>
       </c>
       <c r="K91" t="n">
-        <v>9.594901878548837</v>
+        <v>9.597404951859314</v>
       </c>
     </row>
     <row r="92">
@@ -4213,7 +4213,7 @@
         <v>11</v>
       </c>
       <c r="K92" t="n">
-        <v>9.711631620980414</v>
+        <v>9.714352824288483</v>
       </c>
     </row>
     <row r="93">
@@ -4254,7 +4254,7 @@
         <v>11</v>
       </c>
       <c r="K93" t="n">
-        <v>9.812453513515775</v>
+        <v>9.815291677891272</v>
       </c>
     </row>
     <row r="94">
@@ -4295,7 +4295,7 @@
         <v>11</v>
       </c>
       <c r="K94" t="n">
-        <v>9.974311185902952</v>
+        <v>9.97553945435223</v>
       </c>
     </row>
     <row r="95">
@@ -4336,7 +4336,7 @@
         <v>11</v>
       </c>
       <c r="K95" t="n">
-        <v>10.02205133288883</v>
+        <v>10.02345565142805</v>
       </c>
     </row>
     <row r="96">
@@ -4377,7 +4377,7 @@
         <v>11</v>
       </c>
       <c r="K96" t="n">
-        <v>10.28025187896138</v>
+        <v>10.28152909818356</v>
       </c>
     </row>
     <row r="97">
@@ -4418,7 +4418,7 @@
         <v>11</v>
       </c>
       <c r="K97" t="n">
-        <v>10.38618001855317</v>
+        <v>10.3872519732941</v>
       </c>
     </row>
     <row r="98">
@@ -4459,7 +4459,7 @@
         <v>11</v>
       </c>
       <c r="K98" t="n">
-        <v>10.44776992585482</v>
+        <v>10.44898465681968</v>
       </c>
     </row>
     <row r="99">
@@ -4500,7 +4500,7 @@
         <v>11</v>
       </c>
       <c r="K99" t="n">
-        <v>10.55026105538567</v>
+        <v>10.55078913230849</v>
       </c>
     </row>
     <row r="100">
@@ -4541,7 +4541,7 @@
         <v>11</v>
       </c>
       <c r="K100" t="n">
-        <v>10.55640596549939</v>
+        <v>10.55568052545157</v>
       </c>
     </row>
     <row r="101">
@@ -4582,7 +4582,7 @@
         <v>11</v>
       </c>
       <c r="K101" t="n">
-        <v>10.52219052114853</v>
+        <v>10.52133522511898</v>
       </c>
     </row>
     <row r="102">
@@ -4623,7 +4623,7 @@
         <v>11</v>
       </c>
       <c r="K102" t="n">
-        <v>10.4808184702455</v>
+        <v>10.48015718504093</v>
       </c>
     </row>
     <row r="103">
@@ -4664,7 +4664,7 @@
         <v>11</v>
       </c>
       <c r="K103" t="n">
-        <v>10.45075109019776</v>
+        <v>10.4501027583802</v>
       </c>
     </row>
     <row r="104">
@@ -4705,7 +4705,7 @@
         <v>11</v>
       </c>
       <c r="K104" t="n">
-        <v>10.42180488538178</v>
+        <v>10.42127072509713</v>
       </c>
     </row>
     <row r="105">
@@ -4746,7 +4746,7 @@
         <v>11</v>
       </c>
       <c r="K105" t="n">
-        <v>10.41806567842505</v>
+        <v>10.4176749266558</v>
       </c>
     </row>
     <row r="106">
@@ -4787,7 +4787,7 @@
         <v>11</v>
       </c>
       <c r="K106" t="n">
-        <v>10.3885771773526</v>
+        <v>10.38882430504399</v>
       </c>
     </row>
     <row r="107">
@@ -4828,7 +4828,7 @@
         <v>11</v>
       </c>
       <c r="K107" t="n">
-        <v>10.45060969889723</v>
+        <v>10.45129953850017</v>
       </c>
     </row>
     <row r="108">
@@ -4869,7 +4869,7 @@
         <v>11</v>
       </c>
       <c r="K108" t="n">
-        <v>10.50364497429563</v>
+        <v>10.50448765753914</v>
       </c>
     </row>
     <row r="109">
@@ -4910,7 +4910,7 @@
         <v>11</v>
       </c>
       <c r="K109" t="n">
-        <v>10.81779559383239</v>
+        <v>10.8198000389266</v>
       </c>
     </row>
     <row r="110">
@@ -4951,7 +4951,7 @@
         <v>11</v>
       </c>
       <c r="K110" t="n">
-        <v>10.9357231825844</v>
+        <v>10.93789873648171</v>
       </c>
     </row>
     <row r="111">
@@ -4992,7 +4992,7 @@
         <v>11</v>
       </c>
       <c r="K111" t="n">
-        <v>11.55281843846564</v>
+        <v>11.55704364183319</v>
       </c>
     </row>
     <row r="112">
@@ -5033,7 +5033,7 @@
         <v>11</v>
       </c>
       <c r="K112" t="n">
-        <v>13.24905110056308</v>
+        <v>13.31560369386983</v>
       </c>
     </row>
     <row r="113">
@@ -5074,7 +5074,7 @@
         <v>11</v>
       </c>
       <c r="K113" t="n">
-        <v>13.24905110056308</v>
+        <v>13.31560369386983</v>
       </c>
     </row>
     <row r="114">
@@ -5115,7 +5115,7 @@
         <v>11</v>
       </c>
       <c r="K114" t="n">
-        <v>13.96546733948439</v>
+        <v>14.40688162462841</v>
       </c>
     </row>
     <row r="115">
@@ -5156,7 +5156,7 @@
         <v>11</v>
       </c>
       <c r="K115" t="n">
-        <v>14.09499060277884</v>
+        <v>14.09612157306057</v>
       </c>
     </row>
     <row r="116">
@@ -5197,7 +5197,7 @@
         <v>11</v>
       </c>
       <c r="K116" t="n">
-        <v>14.10231971947695</v>
+        <v>14.10138450013956</v>
       </c>
     </row>
     <row r="117">
@@ -5238,7 +5238,7 @@
         <v>11</v>
       </c>
       <c r="K117" t="n">
-        <v>13.32115312121745</v>
+        <v>13.326414149434</v>
       </c>
     </row>
     <row r="118">
@@ -5279,7 +5279,7 @@
         <v>11</v>
       </c>
       <c r="K118" t="n">
-        <v>12.18673597949732</v>
+        <v>12.13198070255896</v>
       </c>
     </row>
     <row r="119">
@@ -5320,7 +5320,7 @@
         <v>11</v>
       </c>
       <c r="K119" t="n">
-        <v>11.61520007469289</v>
+        <v>11.55600136387979</v>
       </c>
     </row>
     <row r="120">
@@ -5361,7 +5361,7 @@
         <v>11</v>
       </c>
       <c r="K120" t="n">
-        <v>10.7717653162068</v>
+        <v>10.77116273756967</v>
       </c>
     </row>
     <row r="121">
@@ -5402,7 +5402,7 @@
         <v>11</v>
       </c>
       <c r="K121" t="n">
-        <v>10.62118096941062</v>
+        <v>10.62822165545307</v>
       </c>
     </row>
     <row r="122">
@@ -5443,7 +5443,7 @@
         <v>11</v>
       </c>
       <c r="K122" t="n">
-        <v>10.62118096941062</v>
+        <v>10.62822165545307</v>
       </c>
     </row>
     <row r="123">
@@ -5484,7 +5484,7 @@
         <v>11</v>
       </c>
       <c r="K123" t="n">
-        <v>10.45511537631013</v>
+        <v>10.45563919377957</v>
       </c>
     </row>
     <row r="124">
@@ -5525,7 +5525,7 @@
         <v>11</v>
       </c>
       <c r="K124" t="n">
-        <v>10.44611547119964</v>
+        <v>10.44624520062144</v>
       </c>
     </row>
     <row r="125">
@@ -5566,7 +5566,7 @@
         <v>11</v>
       </c>
       <c r="K125" t="n">
-        <v>10.40516927885814</v>
+        <v>10.40283994622784</v>
       </c>
     </row>
     <row r="126">
@@ -5607,7 +5607,7 @@
         <v>11</v>
       </c>
       <c r="K126" t="n">
-        <v>10.15234578612369</v>
+        <v>10.1516257817853</v>
       </c>
     </row>
     <row r="127">
@@ -5648,7 +5648,7 @@
         <v>11</v>
       </c>
       <c r="K127" t="n">
-        <v>10.12854983494127</v>
+        <v>10.1268169564278</v>
       </c>
     </row>
     <row r="128">
@@ -5689,7 +5689,7 @@
         <v>11</v>
       </c>
       <c r="K128" t="n">
-        <v>10.13429438631349</v>
+        <v>10.13136169448493</v>
       </c>
     </row>
     <row r="129">
@@ -5730,7 +5730,7 @@
         <v>11</v>
       </c>
       <c r="K129" t="n">
-        <v>10.16702268282531</v>
+        <v>10.16258449880304</v>
       </c>
     </row>
     <row r="130">
@@ -5771,7 +5771,7 @@
         <v>11</v>
       </c>
       <c r="K130" t="n">
-        <v>10.19850456500321</v>
+        <v>10.19799380980201</v>
       </c>
     </row>
     <row r="131">
@@ -5812,7 +5812,7 @@
         <v>11</v>
       </c>
       <c r="K131" t="n">
-        <v>10.15988699682155</v>
+        <v>10.1601319628132</v>
       </c>
     </row>
     <row r="132">
@@ -5853,7 +5853,7 @@
         <v>11</v>
       </c>
       <c r="K132" t="n">
-        <v>10.15045600603868</v>
+        <v>10.15094173673778</v>
       </c>
     </row>
     <row r="133">
@@ -5894,7 +5894,7 @@
         <v>11</v>
       </c>
       <c r="K133" t="n">
-        <v>10.15045600603868</v>
+        <v>10.15094173673778</v>
       </c>
     </row>
     <row r="134">
@@ -5935,7 +5935,7 @@
         <v>11</v>
       </c>
       <c r="K134" t="n">
-        <v>9.889113576235221</v>
+        <v>9.889344493517445</v>
       </c>
     </row>
     <row r="135">
@@ -5976,7 +5976,7 @@
         <v>11</v>
       </c>
       <c r="K135" t="n">
-        <v>9.889113576235221</v>
+        <v>9.889344493517445</v>
       </c>
     </row>
     <row r="136">
@@ -6017,7 +6017,7 @@
         <v>11</v>
       </c>
       <c r="K136" t="n">
-        <v>9.503480022823256</v>
+        <v>9.502205430969047</v>
       </c>
     </row>
     <row r="137">
@@ -6058,7 +6058,7 @@
         <v>11</v>
       </c>
       <c r="K137" t="n">
-        <v>9.503480022823256</v>
+        <v>9.502205430969047</v>
       </c>
     </row>
     <row r="138">
@@ -6099,7 +6099,7 @@
         <v>11</v>
       </c>
       <c r="K138" t="n">
-        <v>9.273302827189962</v>
+        <v>9.2747641829085</v>
       </c>
     </row>
     <row r="139">
@@ -6140,7 +6140,7 @@
         <v>11</v>
       </c>
       <c r="K139" t="n">
-        <v>9.323353732391949</v>
+        <v>9.324573665658882</v>
       </c>
     </row>
     <row r="140">
@@ -6181,7 +6181,7 @@
         <v>11</v>
       </c>
       <c r="K140" t="n">
-        <v>9.538199059605576</v>
+        <v>9.538440518080224</v>
       </c>
     </row>
     <row r="141">
@@ -6222,7 +6222,7 @@
         <v>11</v>
       </c>
       <c r="K141" t="n">
-        <v>9.595159351550077</v>
+        <v>9.595754876251377</v>
       </c>
     </row>
     <row r="142">
@@ -6263,7 +6263,7 @@
         <v>11</v>
       </c>
       <c r="K142" t="n">
-        <v>9.640228187381412</v>
+        <v>9.635538819217883</v>
       </c>
     </row>
     <row r="143">
@@ -6304,7 +6304,7 @@
         <v>11</v>
       </c>
       <c r="K143" t="n">
-        <v>9.67585678642285</v>
+        <v>9.660118069178658</v>
       </c>
     </row>
     <row r="144">
@@ -6345,7 +6345,7 @@
         <v>11</v>
       </c>
       <c r="K144" t="n">
-        <v>9.67585678642285</v>
+        <v>9.660118069178658</v>
       </c>
     </row>
     <row r="145">
@@ -6386,7 +6386,7 @@
         <v>11</v>
       </c>
       <c r="K145" t="n">
-        <v>9.644544295013892</v>
+        <v>9.630258149575942</v>
       </c>
     </row>
     <row r="146">
@@ -6427,7 +6427,7 @@
         <v>11</v>
       </c>
       <c r="K146" t="n">
-        <v>9.575393468358264</v>
+        <v>9.568585070538559</v>
       </c>
     </row>
     <row r="147">
@@ -6468,7 +6468,7 @@
         <v>11</v>
       </c>
       <c r="K147" t="n">
-        <v>9.509165247009472</v>
+        <v>9.501834150982846</v>
       </c>
     </row>
     <row r="148">
@@ -6509,7 +6509,7 @@
         <v>11</v>
       </c>
       <c r="K148" t="n">
-        <v>9.186890150588898</v>
+        <v>9.182957295513431</v>
       </c>
     </row>
     <row r="149">
@@ -6550,7 +6550,7 @@
         <v>11</v>
       </c>
       <c r="K149" t="n">
-        <v>8.892310645809815</v>
+        <v>8.890417392763156</v>
       </c>
     </row>
     <row r="150">
@@ -6591,7 +6591,7 @@
         <v>11</v>
       </c>
       <c r="K150" t="n">
-        <v>8.798285875284799</v>
+        <v>8.798409828292209</v>
       </c>
     </row>
     <row r="151">
@@ -6632,7 +6632,7 @@
         <v>11</v>
       </c>
       <c r="K151" t="n">
-        <v>8.875333945274798</v>
+        <v>8.875679267296459</v>
       </c>
     </row>
     <row r="152">
@@ -6673,7 +6673,7 @@
         <v>11</v>
       </c>
       <c r="K152" t="n">
-        <v>8.916837319105506</v>
+        <v>8.916880621754231</v>
       </c>
     </row>
     <row r="153">
@@ -6714,7 +6714,7 @@
         <v>11</v>
       </c>
       <c r="K153" t="n">
-        <v>9.076727962887233</v>
+        <v>9.078526140339113</v>
       </c>
     </row>
     <row r="154">
@@ -6755,7 +6755,7 @@
         <v>11</v>
       </c>
       <c r="K154" t="n">
-        <v>9.266264516167034</v>
+        <v>9.26822225201467</v>
       </c>
     </row>
     <row r="155">
@@ -6796,7 +6796,7 @@
         <v>11</v>
       </c>
       <c r="K155" t="n">
-        <v>9.383051777516972</v>
+        <v>9.385469462371724</v>
       </c>
     </row>
     <row r="156">
@@ -6837,7 +6837,7 @@
         <v>11</v>
       </c>
       <c r="K156" t="n">
-        <v>9.383051777516972</v>
+        <v>9.385469462371724</v>
       </c>
     </row>
     <row r="157">
@@ -6878,7 +6878,7 @@
         <v>11</v>
       </c>
       <c r="K157" t="n">
-        <v>9.460674517214896</v>
+        <v>9.460685228661809</v>
       </c>
     </row>
     <row r="158">
@@ -6919,7 +6919,7 @@
         <v>11</v>
       </c>
       <c r="K158" t="n">
-        <v>9.460674517214896</v>
+        <v>9.460685228661809</v>
       </c>
     </row>
     <row r="159">
@@ -6960,7 +6960,7 @@
         <v>11</v>
       </c>
       <c r="K159" t="n">
-        <v>9.459995832832561</v>
+        <v>9.459172912215124</v>
       </c>
     </row>
     <row r="160">
@@ -7001,7 +7001,7 @@
         <v>11</v>
       </c>
       <c r="K160" t="n">
-        <v>9.459995832832561</v>
+        <v>9.459172912215124</v>
       </c>
     </row>
     <row r="161">
@@ -7042,7 +7042,7 @@
         <v>11</v>
       </c>
       <c r="K161" t="n">
-        <v>9.442058385983874</v>
+        <v>9.44774546930241</v>
       </c>
     </row>
     <row r="162">
@@ -7083,7 +7083,7 @@
         <v>11</v>
       </c>
       <c r="K162" t="n">
-        <v>9.445691342095797</v>
+        <v>9.453663212098906</v>
       </c>
     </row>
     <row r="163">
@@ -7124,7 +7124,7 @@
         <v>11</v>
       </c>
       <c r="K163" t="n">
-        <v>9.44635359893042</v>
+        <v>9.450594952595399</v>
       </c>
     </row>
     <row r="164">
@@ -7165,7 +7165,7 @@
         <v>11</v>
       </c>
       <c r="K164" t="n">
-        <v>9.358002915936485</v>
+        <v>9.35747673899648</v>
       </c>
     </row>
     <row r="165">
@@ -7206,7 +7206,7 @@
         <v>11</v>
       </c>
       <c r="K165" t="n">
-        <v>9.358002915936485</v>
+        <v>9.35747673899648</v>
       </c>
     </row>
     <row r="166">
@@ -7247,7 +7247,7 @@
         <v>11</v>
       </c>
       <c r="K166" t="n">
-        <v>9.273348983270356</v>
+        <v>9.272148731580678</v>
       </c>
     </row>
     <row r="167">
@@ -7288,7 +7288,7 @@
         <v>11</v>
       </c>
       <c r="K167" t="n">
-        <v>9.273348983270356</v>
+        <v>9.272148731580678</v>
       </c>
     </row>
     <row r="168">
@@ -7329,7 +7329,7 @@
         <v>11</v>
       </c>
       <c r="K168" t="n">
-        <v>9.202805814248382</v>
+        <v>9.203725134342601</v>
       </c>
     </row>
     <row r="169">
@@ -7370,7 +7370,7 @@
         <v>11</v>
       </c>
       <c r="K169" t="n">
-        <v>9.202805814248382</v>
+        <v>9.203725134342601</v>
       </c>
     </row>
     <row r="170">
@@ -7411,7 +7411,7 @@
         <v>11</v>
       </c>
       <c r="K170" t="n">
-        <v>9.202805814248382</v>
+        <v>9.203725134342601</v>
       </c>
     </row>
     <row r="171">
@@ -7452,7 +7452,7 @@
         <v>11</v>
       </c>
       <c r="K171" t="n">
-        <v>9.202805814248382</v>
+        <v>9.203725134342601</v>
       </c>
     </row>
     <row r="172">
@@ -7493,7 +7493,7 @@
         <v>11</v>
       </c>
       <c r="K172" t="n">
-        <v>9.325700165492846</v>
+        <v>9.3272822998037</v>
       </c>
     </row>
     <row r="173">
@@ -7534,7 +7534,7 @@
         <v>11</v>
       </c>
       <c r="K173" t="n">
-        <v>9.439273478382294</v>
+        <v>9.440685451800245</v>
       </c>
     </row>
     <row r="174">
@@ -7575,7 +7575,7 @@
         <v>13</v>
       </c>
       <c r="K174" t="n">
-        <v>9.578592148482896</v>
+        <v>9.580494734612239</v>
       </c>
     </row>
     <row r="175">
@@ -7616,7 +7616,7 @@
         <v>13</v>
       </c>
       <c r="K175" t="n">
-        <v>9.807680959686632</v>
+        <v>9.810298692875696</v>
       </c>
     </row>
     <row r="176">
@@ -7657,7 +7657,7 @@
         <v>13</v>
       </c>
       <c r="K176" t="n">
-        <v>9.807680959686632</v>
+        <v>9.810298692875696</v>
       </c>
     </row>
     <row r="177">
@@ -7698,7 +7698,7 @@
         <v>13</v>
       </c>
       <c r="K177" t="n">
-        <v>10.78022689352067</v>
+        <v>10.78343087639578</v>
       </c>
     </row>
     <row r="178">
@@ -7739,7 +7739,7 @@
         <v>13</v>
       </c>
       <c r="K178" t="n">
-        <v>10.78022689352067</v>
+        <v>10.78343087639578</v>
       </c>
     </row>
     <row r="179">
@@ -7780,7 +7780,7 @@
         <v>13</v>
       </c>
       <c r="K179" t="n">
-        <v>10.97632303694578</v>
+        <v>10.97763145315968</v>
       </c>
     </row>
     <row r="180">
@@ -7821,7 +7821,7 @@
         <v>13</v>
       </c>
       <c r="K180" t="n">
-        <v>10.89437294526549</v>
+        <v>10.89364066814197</v>
       </c>
     </row>
     <row r="181">
@@ -7862,7 +7862,7 @@
         <v>13</v>
       </c>
       <c r="K181" t="n">
-        <v>10.89437294526549</v>
+        <v>10.89364066814197</v>
       </c>
     </row>
     <row r="182">
@@ -7903,7 +7903,7 @@
         <v>13</v>
       </c>
       <c r="K182" t="n">
-        <v>10.81042809243085</v>
+        <v>10.80935617696883</v>
       </c>
     </row>
     <row r="183">
@@ -7944,7 +7944,7 @@
         <v>13</v>
       </c>
       <c r="K183" t="n">
-        <v>10.81042809243085</v>
+        <v>10.80935617696883</v>
       </c>
     </row>
     <row r="184">
@@ -7985,7 +7985,7 @@
         <v>13</v>
       </c>
       <c r="K184" t="n">
-        <v>10.49792660516642</v>
+        <v>10.49717080563149</v>
       </c>
     </row>
     <row r="185">
@@ -8026,7 +8026,7 @@
         <v>13</v>
       </c>
       <c r="K185" t="n">
-        <v>10.40823966094027</v>
+        <v>10.40817824379519</v>
       </c>
     </row>
     <row r="186">
@@ -8067,7 +8067,7 @@
         <v>13</v>
       </c>
       <c r="K186" t="n">
-        <v>10.40234496133875</v>
+        <v>10.40279981897792</v>
       </c>
     </row>
     <row r="187">
@@ -8108,7 +8108,7 @@
         <v>13</v>
       </c>
       <c r="K187" t="n">
-        <v>10.68338265109615</v>
+        <v>10.68360389112607</v>
       </c>
     </row>
     <row r="188">
@@ -8149,7 +8149,7 @@
         <v>12</v>
       </c>
       <c r="K188" t="n">
-        <v>11.08605006924444</v>
+        <v>11.15079076063861</v>
       </c>
     </row>
     <row r="189">
@@ -8190,7 +8190,7 @@
         <v>12</v>
       </c>
       <c r="K189" t="n">
-        <v>11.50207319071896</v>
+        <v>11.50237600466004</v>
       </c>
     </row>
     <row r="190">
@@ -8231,7 +8231,7 @@
         <v>12</v>
       </c>
       <c r="K190" t="n">
-        <v>11.50207319071896</v>
+        <v>11.50237600466004</v>
       </c>
     </row>
     <row r="191">
@@ -8272,7 +8272,7 @@
         <v>12</v>
       </c>
       <c r="K191" t="n">
-        <v>11.69557443787491</v>
+        <v>11.69600200347392</v>
       </c>
     </row>
     <row r="192">
@@ -8313,7 +8313,7 @@
         <v>12</v>
       </c>
       <c r="K192" t="n">
-        <v>12.00427980342408</v>
+        <v>11.78864937484268</v>
       </c>
     </row>
     <row r="193">
@@ -8354,7 +8354,7 @@
         <v>12</v>
       </c>
       <c r="K193" t="n">
-        <v>12.00427980342408</v>
+        <v>11.78864937484268</v>
       </c>
     </row>
     <row r="194">
@@ -8395,7 +8395,7 @@
         <v>12</v>
       </c>
       <c r="K194" t="n">
-        <v>11.93485953365033</v>
+        <v>11.92885928331267</v>
       </c>
     </row>
     <row r="195">
@@ -8436,7 +8436,7 @@
         <v>12</v>
       </c>
       <c r="K195" t="n">
-        <v>8.972531502131083</v>
+        <v>8.951270482839831</v>
       </c>
     </row>
     <row r="196">
@@ -8477,7 +8477,7 @@
         <v>12</v>
       </c>
       <c r="K196" t="n">
-        <v>8.825164679350966</v>
+        <v>8.822007691565409</v>
       </c>
     </row>
     <row r="197">
@@ -8518,7 +8518,7 @@
         <v>12</v>
       </c>
       <c r="K197" t="n">
-        <v>8.825164679350966</v>
+        <v>8.822007691565409</v>
       </c>
     </row>
     <row r="198">
@@ -8559,7 +8559,7 @@
         <v>12</v>
       </c>
       <c r="K198" t="n">
-        <v>8.825164679350966</v>
+        <v>8.822007691565409</v>
       </c>
     </row>
     <row r="199">
@@ -8600,7 +8600,7 @@
         <v>12</v>
       </c>
       <c r="K199" t="n">
-        <v>8.825164679350966</v>
+        <v>8.822007691565409</v>
       </c>
     </row>
     <row r="200">
@@ -8641,7 +8641,7 @@
         <v>12</v>
       </c>
       <c r="K200" t="n">
-        <v>8.825164679350966</v>
+        <v>8.822007691565409</v>
       </c>
     </row>
     <row r="201">
@@ -8682,7 +8682,7 @@
         <v>12</v>
       </c>
       <c r="K201" t="n">
-        <v>8.717469319399115</v>
+        <v>8.717851250039388</v>
       </c>
     </row>
     <row r="202">
@@ -8723,7 +8723,7 @@
         <v>12</v>
       </c>
       <c r="K202" t="n">
-        <v>8.717469319399115</v>
+        <v>8.717851250039388</v>
       </c>
     </row>
     <row r="203">
@@ -8764,7 +8764,7 @@
         <v>12</v>
       </c>
       <c r="K203" t="n">
-        <v>11.41624358709508</v>
+        <v>11.41611211951067</v>
       </c>
     </row>
     <row r="204">
@@ -8805,7 +8805,7 @@
         <v>12</v>
       </c>
       <c r="K204" t="n">
-        <v>11.23747045773712</v>
+        <v>11.23727604870171</v>
       </c>
     </row>
     <row r="205">
@@ -8846,7 +8846,7 @@
         <v>12</v>
       </c>
       <c r="K205" t="n">
-        <v>11.03780504665424</v>
+        <v>11.01913393415817</v>
       </c>
     </row>
     <row r="206">
@@ -8887,7 +8887,7 @@
         <v>12</v>
       </c>
       <c r="K206" t="n">
-        <v>11.03780504665424</v>
+        <v>11.01913393415817</v>
       </c>
     </row>
     <row r="207">
@@ -8928,7 +8928,7 @@
         <v>12</v>
       </c>
       <c r="K207" t="n">
-        <v>7.983917610806308</v>
+        <v>7.983995745846131</v>
       </c>
     </row>
     <row r="208">
@@ -8969,7 +8969,7 @@
         <v>12</v>
       </c>
       <c r="K208" t="n">
-        <v>7.874938159898531</v>
+        <v>7.875027866395453</v>
       </c>
     </row>
     <row r="209">
@@ -9010,7 +9010,7 @@
         <v>12</v>
       </c>
       <c r="K209" t="n">
-        <v>7.833592039957618</v>
+        <v>7.833623445901845</v>
       </c>
     </row>
     <row r="210">
@@ -9051,7 +9051,7 @@
         <v>12</v>
       </c>
       <c r="K210" t="n">
-        <v>7.839185909153782</v>
+        <v>7.839149775900285</v>
       </c>
     </row>
     <row r="211">
@@ -9092,7 +9092,7 @@
         <v>12</v>
       </c>
       <c r="K211" t="n">
-        <v>7.908825418622827</v>
+        <v>7.908784749943867</v>
       </c>
     </row>
     <row r="212">
@@ -9133,7 +9133,7 @@
         <v>12</v>
       </c>
       <c r="K212" t="n">
-        <v>7.989403931656994</v>
+        <v>7.989257775401603</v>
       </c>
     </row>
     <row r="213">
@@ -9174,7 +9174,7 @@
         <v>12</v>
       </c>
       <c r="K213" t="n">
-        <v>8.087241879725132</v>
+        <v>8.087092816359368</v>
       </c>
     </row>
     <row r="214">
@@ -9215,7 +9215,7 @@
         <v>12</v>
       </c>
       <c r="K214" t="n">
-        <v>8.087241879725132</v>
+        <v>8.087092816359368</v>
       </c>
     </row>
     <row r="215">
@@ -9256,7 +9256,7 @@
         <v>12</v>
       </c>
       <c r="K215" t="n">
-        <v>8.071607434598153</v>
+        <v>8.071863161920197</v>
       </c>
     </row>
     <row r="216">
@@ -9297,7 +9297,7 @@
         <v>12</v>
       </c>
       <c r="K216" t="n">
-        <v>7.999783453159843</v>
+        <v>8.000129990585387</v>
       </c>
     </row>
     <row r="217">
@@ -9338,7 +9338,7 @@
         <v>12</v>
       </c>
       <c r="K217" t="n">
-        <v>7.922922754105595</v>
+        <v>7.923386838107357</v>
       </c>
     </row>
     <row r="218">
@@ -9379,7 +9379,7 @@
         <v>12</v>
       </c>
       <c r="K218" t="n">
-        <v>7.627780513808081</v>
+        <v>7.628525131031996</v>
       </c>
     </row>
     <row r="219">
@@ -9420,7 +9420,7 @@
         <v>12</v>
       </c>
       <c r="K219" t="n">
-        <v>7.627780513808081</v>
+        <v>7.628525131031996</v>
       </c>
     </row>
     <row r="220">
@@ -9461,7 +9461,7 @@
         <v>12</v>
       </c>
       <c r="K220" t="n">
-        <v>7.361633963936813</v>
+        <v>7.362088126232826</v>
       </c>
     </row>
     <row r="221">
@@ -9502,7 +9502,7 @@
         <v>12</v>
       </c>
       <c r="K221" t="n">
-        <v>7.283758612994068</v>
+        <v>7.284067449737954</v>
       </c>
     </row>
     <row r="222">
@@ -9543,7 +9543,7 @@
         <v>12</v>
       </c>
       <c r="K222" t="n">
-        <v>7.010906989830274</v>
+        <v>7.011785186775693</v>
       </c>
     </row>
     <row r="223">
@@ -9584,7 +9584,7 @@
         <v>12</v>
       </c>
       <c r="K223" t="n">
-        <v>6.900876621016146</v>
+        <v>6.901673709574657</v>
       </c>
     </row>
     <row r="224">
@@ -9625,7 +9625,7 @@
         <v>12</v>
       </c>
       <c r="K224" t="n">
-        <v>6.900876621016146</v>
+        <v>6.901673709574657</v>
       </c>
     </row>
     <row r="225">
@@ -9666,7 +9666,7 @@
         <v>12</v>
       </c>
       <c r="K225" t="n">
-        <v>6.737143887697933</v>
+        <v>6.737585590073397</v>
       </c>
     </row>
     <row r="226">
@@ -9707,7 +9707,7 @@
         <v>12</v>
       </c>
       <c r="K226" t="n">
-        <v>6.615940055742713</v>
+        <v>6.616353686227867</v>
       </c>
     </row>
     <row r="227">
@@ -9748,7 +9748,7 @@
         <v>12</v>
       </c>
       <c r="K227" t="n">
-        <v>6.509331198307068</v>
+        <v>6.509603999156059</v>
       </c>
     </row>
     <row r="228">
@@ -9789,7 +9789,7 @@
         <v>12</v>
       </c>
       <c r="K228" t="n">
-        <v>6.545151995917883</v>
+        <v>6.544951367918011</v>
       </c>
     </row>
     <row r="229">
@@ -9830,7 +9830,7 @@
         <v>12</v>
       </c>
       <c r="K229" t="n">
-        <v>6.545151995917883</v>
+        <v>6.544951367918011</v>
       </c>
     </row>
     <row r="230">
@@ -9871,7 +9871,7 @@
         <v>12</v>
       </c>
       <c r="K230" t="n">
-        <v>6.556691142523668</v>
+        <v>6.556608464557366</v>
       </c>
     </row>
     <row r="231">
@@ -9912,7 +9912,7 @@
         <v>12</v>
       </c>
       <c r="K231" t="n">
-        <v>6.567497043644606</v>
+        <v>6.567441138671162</v>
       </c>
     </row>
     <row r="232">
@@ -9953,7 +9953,7 @@
         <v>12</v>
       </c>
       <c r="K232" t="n">
-        <v>6.565789487972189</v>
+        <v>6.565736142326753</v>
       </c>
     </row>
     <row r="233">
@@ -9994,7 +9994,7 @@
         <v>12</v>
       </c>
       <c r="K233" t="n">
-        <v>6.565789487972189</v>
+        <v>6.565736142326753</v>
       </c>
     </row>
     <row r="234">
@@ -10035,7 +10035,7 @@
         <v>12</v>
       </c>
       <c r="K234" t="n">
-        <v>6.621840364929129</v>
+        <v>6.620839307929293</v>
       </c>
     </row>
     <row r="235">
@@ -10076,7 +10076,7 @@
         <v>12</v>
       </c>
       <c r="K235" t="n">
-        <v>6.696952617143972</v>
+        <v>6.696154112166785</v>
       </c>
     </row>
     <row r="236">
@@ -10117,7 +10117,7 @@
         <v>12</v>
       </c>
       <c r="K236" t="n">
-        <v>7.170545442462363</v>
+        <v>7.169770796623403</v>
       </c>
     </row>
     <row r="237">
@@ -10158,7 +10158,7 @@
         <v>12</v>
       </c>
       <c r="K237" t="n">
-        <v>7.212529624014738</v>
+        <v>7.21199557986813</v>
       </c>
     </row>
     <row r="238">
@@ -10199,7 +10199,7 @@
         <v>12</v>
       </c>
       <c r="K238" t="n">
-        <v>7.0694042275373</v>
+        <v>7.069098570461216</v>
       </c>
     </row>
     <row r="239">
@@ -10240,7 +10240,7 @@
         <v>12</v>
       </c>
       <c r="K239" t="n">
-        <v>6.967208070103951</v>
+        <v>6.966786456741964</v>
       </c>
     </row>
     <row r="240">
@@ -10281,7 +10281,7 @@
         <v>12</v>
       </c>
       <c r="K240" t="n">
-        <v>6.764525628379063</v>
+        <v>6.765583084489589</v>
       </c>
     </row>
     <row r="241">
@@ -10322,7 +10322,7 @@
         <v>12</v>
       </c>
       <c r="K241" t="n">
-        <v>6.764525628379063</v>
+        <v>6.765583084489589</v>
       </c>
     </row>
     <row r="242">
@@ -10363,7 +10363,7 @@
         <v>12</v>
       </c>
       <c r="K242" t="n">
-        <v>6.764525628379063</v>
+        <v>6.765583084489589</v>
       </c>
     </row>
     <row r="243">
@@ -10404,7 +10404,7 @@
         <v>12</v>
       </c>
       <c r="K243" t="n">
-        <v>6.564601479006817</v>
+        <v>6.564481422122091</v>
       </c>
     </row>
     <row r="244">
@@ -10445,7 +10445,7 @@
         <v>12</v>
       </c>
       <c r="K244" t="n">
-        <v>6.463719905980114</v>
+        <v>6.460691657296105</v>
       </c>
     </row>
     <row r="245">
@@ -10486,7 +10486,7 @@
         <v>12</v>
       </c>
       <c r="K245" t="n">
-        <v>6.389770198074604</v>
+        <v>6.387610797021559</v>
       </c>
     </row>
     <row r="246">
@@ -10527,7 +10527,7 @@
         <v>12</v>
       </c>
       <c r="K246" t="n">
-        <v>6.389770198074604</v>
+        <v>6.387610797021559</v>
       </c>
     </row>
     <row r="247">
@@ -10568,7 +10568,7 @@
         <v>12</v>
       </c>
       <c r="K247" t="n">
-        <v>6.35355459678128</v>
+        <v>6.352424811731574</v>
       </c>
     </row>
     <row r="248">
@@ -10609,7 +10609,7 @@
         <v>12</v>
       </c>
       <c r="K248" t="n">
-        <v>6.35355459678128</v>
+        <v>6.352424811731574</v>
       </c>
     </row>
     <row r="249">
@@ -10650,7 +10650,7 @@
         <v>12</v>
       </c>
       <c r="K249" t="n">
-        <v>6.395779791869125</v>
+        <v>6.395557085711514</v>
       </c>
     </row>
     <row r="250">
@@ -10691,7 +10691,7 @@
         <v>12</v>
       </c>
       <c r="K250" t="n">
-        <v>6.406404875695161</v>
+        <v>6.407299258384022</v>
       </c>
     </row>
     <row r="251">
@@ -10732,7 +10732,7 @@
         <v>12</v>
       </c>
       <c r="K251" t="n">
-        <v>6.441383269673444</v>
+        <v>6.44111503026377</v>
       </c>
     </row>
     <row r="252">
@@ -10773,7 +10773,7 @@
         <v>12</v>
       </c>
       <c r="K252" t="n">
-        <v>6.507154901965544</v>
+        <v>6.506592364551546</v>
       </c>
     </row>
     <row r="253">
@@ -10814,7 +10814,7 @@
         <v>12</v>
       </c>
       <c r="K253" t="n">
-        <v>6.507154901965544</v>
+        <v>6.506592364551546</v>
       </c>
     </row>
     <row r="254">
@@ -10855,7 +10855,7 @@
         <v>12</v>
       </c>
       <c r="K254" t="n">
-        <v>6.624889237190102</v>
+        <v>6.623757385727202</v>
       </c>
     </row>
     <row r="255">
@@ -10896,7 +10896,7 @@
         <v>12</v>
       </c>
       <c r="K255" t="n">
-        <v>6.694697108167018</v>
+        <v>6.694243669101866</v>
       </c>
     </row>
     <row r="256">
@@ -10937,7 +10937,7 @@
         <v>12</v>
       </c>
       <c r="K256" t="n">
-        <v>6.689351826243123</v>
+        <v>6.688697451995003</v>
       </c>
     </row>
     <row r="257">
@@ -10978,7 +10978,7 @@
         <v>12</v>
       </c>
       <c r="K257" t="n">
-        <v>6.645961708125747</v>
+        <v>6.64624174400871</v>
       </c>
     </row>
     <row r="258">
@@ -11019,7 +11019,7 @@
         <v>12</v>
       </c>
       <c r="K258" t="n">
-        <v>6.645961708125747</v>
+        <v>6.64624174400871</v>
       </c>
     </row>
     <row r="259">
@@ -11060,7 +11060,7 @@
         <v>12</v>
       </c>
       <c r="K259" t="n">
-        <v>6.595609736742639</v>
+        <v>6.595406718790527</v>
       </c>
     </row>
     <row r="260">
@@ -11101,7 +11101,7 @@
         <v>12</v>
       </c>
       <c r="K260" t="n">
-        <v>6.519483198421881</v>
+        <v>6.528848370669333</v>
       </c>
     </row>
     <row r="261">
@@ -11142,7 +11142,7 @@
         <v>12</v>
       </c>
       <c r="K261" t="n">
-        <v>6.519483198421881</v>
+        <v>6.528848370669333</v>
       </c>
     </row>
     <row r="262">
@@ -11183,7 +11183,7 @@
         <v>12</v>
       </c>
       <c r="K262" t="n">
-        <v>6.519483198421881</v>
+        <v>6.528848370669333</v>
       </c>
     </row>
     <row r="263">
@@ -11224,7 +11224,7 @@
         <v>12</v>
       </c>
       <c r="K263" t="n">
-        <v>6.443409971077021</v>
+        <v>6.462286106364076</v>
       </c>
     </row>
     <row r="264">
@@ -11265,7 +11265,7 @@
         <v>12</v>
       </c>
       <c r="K264" t="n">
-        <v>6.349420864135906</v>
+        <v>6.351279560507039</v>
       </c>
     </row>
     <row r="265">
@@ -11306,7 +11306,7 @@
         <v>12</v>
       </c>
       <c r="K265" t="n">
-        <v>6.349420864135906</v>
+        <v>6.351279560507039</v>
       </c>
     </row>
     <row r="266">
@@ -11347,7 +11347,7 @@
         <v>12</v>
       </c>
       <c r="K266" t="n">
-        <v>6.225251898711105</v>
+        <v>6.214616331045852</v>
       </c>
     </row>
     <row r="267">
@@ -11388,7 +11388,7 @@
         <v>12</v>
       </c>
       <c r="K267" t="n">
-        <v>6.225251898711105</v>
+        <v>6.214616331045852</v>
       </c>
     </row>
     <row r="268">
@@ -11429,7 +11429,7 @@
         <v>12</v>
       </c>
       <c r="K268" t="n">
-        <v>5.927076537069531</v>
+        <v>5.928248127220702</v>
       </c>
     </row>
     <row r="269">
@@ -11470,7 +11470,7 @@
         <v>12</v>
       </c>
       <c r="K269" t="n">
-        <v>5.927076537069531</v>
+        <v>5.928248127220702</v>
       </c>
     </row>
     <row r="270">
@@ -11511,7 +11511,7 @@
         <v>12</v>
       </c>
       <c r="K270" t="n">
-        <v>5.927076537069531</v>
+        <v>5.928248127220702</v>
       </c>
     </row>
     <row r="271">
@@ -11552,7 +11552,7 @@
         <v>12</v>
       </c>
       <c r="K271" t="n">
-        <v>5.68721867829009</v>
+        <v>5.689296761881216</v>
       </c>
     </row>
     <row r="272">
@@ -11593,7 +11593,7 @@
         <v>12</v>
       </c>
       <c r="K272" t="n">
-        <v>5.68721867829009</v>
+        <v>5.689296761881216</v>
       </c>
     </row>
     <row r="273">
@@ -11634,7 +11634,7 @@
         <v>12</v>
       </c>
       <c r="K273" t="n">
-        <v>5.556439618384283</v>
+        <v>5.556799578236054</v>
       </c>
     </row>
     <row r="274">
@@ -11675,7 +11675,7 @@
         <v>12</v>
       </c>
       <c r="K274" t="n">
-        <v>5.556439618384283</v>
+        <v>5.556799578236054</v>
       </c>
     </row>
     <row r="275">
@@ -11716,7 +11716,7 @@
         <v>12</v>
       </c>
       <c r="K275" t="n">
-        <v>5.523015648608387</v>
+        <v>5.523895774643843</v>
       </c>
     </row>
     <row r="276">
@@ -11757,7 +11757,7 @@
         <v>12</v>
       </c>
       <c r="K276" t="n">
-        <v>5.484651274469442</v>
+        <v>5.485329705990236</v>
       </c>
     </row>
     <row r="277">
@@ -11798,7 +11798,7 @@
         <v>12</v>
       </c>
       <c r="K277" t="n">
-        <v>5.403615753763492</v>
+        <v>5.403974208050389</v>
       </c>
     </row>
     <row r="278">
@@ -11839,7 +11839,7 @@
         <v>12</v>
       </c>
       <c r="K278" t="n">
-        <v>5.400035531057761</v>
+        <v>5.40007072716348</v>
       </c>
     </row>
     <row r="279">
@@ -11880,7 +11880,7 @@
         <v>12</v>
       </c>
       <c r="K279" t="n">
-        <v>5.430625940103638</v>
+        <v>5.430342883901861</v>
       </c>
     </row>
     <row r="280">
@@ -11921,7 +11921,7 @@
         <v>12</v>
       </c>
       <c r="K280" t="n">
-        <v>5.439540654494466</v>
+        <v>5.439341917973376</v>
       </c>
     </row>
     <row r="281">
@@ -11962,7 +11962,7 @@
         <v>12</v>
       </c>
       <c r="K281" t="n">
-        <v>5.43045252735542</v>
+        <v>5.43118581034982</v>
       </c>
     </row>
     <row r="282">
@@ -12003,7 +12003,7 @@
         <v>12</v>
       </c>
       <c r="K282" t="n">
-        <v>5.43045252735542</v>
+        <v>5.43118581034982</v>
       </c>
     </row>
     <row r="283">
@@ -12044,7 +12044,7 @@
         <v>12</v>
       </c>
       <c r="K283" t="n">
-        <v>5.425405849969438</v>
+        <v>5.425090139633459</v>
       </c>
     </row>
     <row r="284">
@@ -12085,7 +12085,7 @@
         <v>12</v>
       </c>
       <c r="K284" t="n">
-        <v>5.488011913313641</v>
+        <v>5.487695788561829</v>
       </c>
     </row>
     <row r="285">
@@ -12126,7 +12126,7 @@
         <v>12</v>
       </c>
       <c r="K285" t="n">
-        <v>5.489626248972863</v>
+        <v>5.489957311124576</v>
       </c>
     </row>
     <row r="286">
@@ -12167,7 +12167,7 @@
         <v>12</v>
       </c>
       <c r="K286" t="n">
-        <v>5.467548055619861</v>
+        <v>5.468647105119354</v>
       </c>
     </row>
     <row r="287">
@@ -12208,7 +12208,7 @@
         <v>12</v>
       </c>
       <c r="K287" t="n">
-        <v>5.416349643311261</v>
+        <v>5.418272606712617</v>
       </c>
     </row>
     <row r="288">
@@ -12249,7 +12249,7 @@
         <v>12</v>
       </c>
       <c r="K288" t="n">
-        <v>5.137232169365259</v>
+        <v>5.140582964517041</v>
       </c>
     </row>
     <row r="289">
@@ -12290,7 +12290,7 @@
         <v>12</v>
       </c>
       <c r="K289" t="n">
-        <v>5.137232169365259</v>
+        <v>5.140582964517041</v>
       </c>
     </row>
     <row r="290">
@@ -12331,7 +12331,7 @@
         <v>12</v>
       </c>
       <c r="K290" t="n">
-        <v>4.987184047266204</v>
+        <v>4.989178211561953</v>
       </c>
     </row>
     <row r="291">
@@ -12372,7 +12372,7 @@
         <v>12</v>
       </c>
       <c r="K291" t="n">
-        <v>4.917981624850995</v>
+        <v>4.920335288686768</v>
       </c>
     </row>
     <row r="292">
@@ -12413,7 +12413,7 @@
         <v>12</v>
       </c>
       <c r="K292" t="n">
-        <v>4.768398390704161</v>
+        <v>4.769679624206597</v>
       </c>
     </row>
     <row r="293">
@@ -12454,7 +12454,7 @@
         <v>12</v>
       </c>
       <c r="K293" t="n">
-        <v>4.768398390704161</v>
+        <v>4.769679624206597</v>
       </c>
     </row>
     <row r="294">
@@ -12495,7 +12495,7 @@
         <v>12</v>
       </c>
       <c r="K294" t="n">
-        <v>4.671140657024297</v>
+        <v>4.673231044762256</v>
       </c>
     </row>
     <row r="295">
@@ -12536,7 +12536,7 @@
         <v>12</v>
       </c>
       <c r="K295" t="n">
-        <v>4.497705336003175</v>
+        <v>4.499579867445633</v>
       </c>
     </row>
     <row r="296">
@@ -12577,7 +12577,7 @@
         <v>12</v>
       </c>
       <c r="K296" t="n">
-        <v>4.497705336003175</v>
+        <v>4.499579867445633</v>
       </c>
     </row>
     <row r="297">
@@ -12618,7 +12618,7 @@
         <v>12</v>
       </c>
       <c r="K297" t="n">
-        <v>4.446491173816532</v>
+        <v>4.447845161272626</v>
       </c>
     </row>
     <row r="298">
@@ -12659,7 +12659,7 @@
         <v>12</v>
       </c>
       <c r="K298" t="n">
-        <v>4.462156526447973</v>
+        <v>4.46145799430716</v>
       </c>
     </row>
     <row r="299">
@@ -12700,7 +12700,7 @@
         <v>12</v>
       </c>
       <c r="K299" t="n">
-        <v>4.462156526447973</v>
+        <v>4.46145799430716</v>
       </c>
     </row>
     <row r="300">
@@ -12741,7 +12741,7 @@
         <v>12</v>
       </c>
       <c r="K300" t="n">
-        <v>4.572961837477169</v>
+        <v>4.571919844476795</v>
       </c>
     </row>
     <row r="301">
@@ -12782,7 +12782,7 @@
         <v>12</v>
       </c>
       <c r="K301" t="n">
-        <v>4.72510881093438</v>
+        <v>4.723144131357025</v>
       </c>
     </row>
     <row r="302">
@@ -12823,7 +12823,7 @@
         <v>12</v>
       </c>
       <c r="K302" t="n">
-        <v>4.781057602797377</v>
+        <v>4.781276143439488</v>
       </c>
     </row>
     <row r="303">
@@ -12864,7 +12864,7 @@
         <v>12</v>
       </c>
       <c r="K303" t="n">
-        <v>4.772145484469391</v>
+        <v>4.77253103057885</v>
       </c>
     </row>
     <row r="304">
@@ -12905,7 +12905,7 @@
         <v>12</v>
       </c>
       <c r="K304" t="n">
-        <v>4.766457804572893</v>
+        <v>4.767006514885614</v>
       </c>
     </row>
     <row r="305">
@@ -12946,7 +12946,7 @@
         <v>12</v>
       </c>
       <c r="K305" t="n">
-        <v>4.675680197889633</v>
+        <v>4.67701522779378</v>
       </c>
     </row>
     <row r="306">
@@ -12987,7 +12987,7 @@
         <v>12</v>
       </c>
       <c r="K306" t="n">
-        <v>4.675680197889633</v>
+        <v>4.67701522779378</v>
       </c>
     </row>
     <row r="307">
@@ -13028,7 +13028,7 @@
         <v>12</v>
       </c>
       <c r="K307" t="n">
-        <v>4.635708280844956</v>
+        <v>4.637625171012686</v>
       </c>
     </row>
     <row r="308">
@@ -13069,7 +13069,7 @@
         <v>12</v>
       </c>
       <c r="K308" t="n">
-        <v>4.584732320464307</v>
+        <v>4.586945869950754</v>
       </c>
     </row>
     <row r="309">
@@ -13110,7 +13110,7 @@
         <v>12</v>
       </c>
       <c r="K309" t="n">
-        <v>4.471231750790213</v>
+        <v>4.473708670131539</v>
       </c>
     </row>
     <row r="310">
@@ -13151,7 +13151,7 @@
         <v>12</v>
       </c>
       <c r="K310" t="n">
-        <v>4.341696963043866</v>
+        <v>4.266404607658068</v>
       </c>
     </row>
     <row r="311">
@@ -13192,7 +13192,7 @@
         <v>12</v>
       </c>
       <c r="K311" t="n">
-        <v>4.341696963043866</v>
+        <v>4.266404607658068</v>
       </c>
     </row>
     <row r="312">
@@ -13233,7 +13233,7 @@
         <v>12</v>
       </c>
       <c r="K312" t="n">
-        <v>4.029491631604353</v>
+        <v>4.033050340001221</v>
       </c>
     </row>
     <row r="313">
@@ -13274,7 +13274,7 @@
         <v>12</v>
       </c>
       <c r="K313" t="n">
-        <v>3.953661586598497</v>
+        <v>3.956774425684551</v>
       </c>
     </row>
     <row r="314">
@@ -13315,7 +13315,7 @@
         <v>12</v>
       </c>
       <c r="K314" t="n">
-        <v>3.894104479925181</v>
+        <v>3.896216360082089</v>
       </c>
     </row>
     <row r="315">
@@ -13356,7 +13356,7 @@
         <v>12</v>
       </c>
       <c r="K315" t="n">
-        <v>3.86504784315993</v>
+        <v>3.864575224665685</v>
       </c>
     </row>
     <row r="316">
@@ -13397,7 +13397,7 @@
         <v>12</v>
       </c>
       <c r="K316" t="n">
-        <v>3.865919170884787</v>
+        <v>3.866109702661176</v>
       </c>
     </row>
     <row r="317">
@@ -13438,7 +13438,7 @@
         <v>12</v>
       </c>
       <c r="K317" t="n">
-        <v>3.89903790537417</v>
+        <v>3.897534997581773</v>
       </c>
     </row>
     <row r="318">
@@ -13479,7 +13479,7 @@
         <v>12</v>
       </c>
       <c r="K318" t="n">
-        <v>3.89903790537417</v>
+        <v>3.897534997581773</v>
       </c>
     </row>
     <row r="319">
@@ -13520,7 +13520,7 @@
         <v>12</v>
       </c>
       <c r="K319" t="n">
-        <v>3.998180962922512</v>
+        <v>3.994968682353648</v>
       </c>
     </row>
     <row r="320">
@@ -13561,7 +13561,7 @@
         <v>12</v>
       </c>
       <c r="K320" t="n">
-        <v>3.998180962922512</v>
+        <v>3.994968682353648</v>
       </c>
     </row>
     <row r="321">
@@ -13602,7 +13602,7 @@
         <v>12</v>
       </c>
       <c r="K321" t="n">
-        <v>4.155107285102944</v>
+        <v>4.205507087431931</v>
       </c>
     </row>
     <row r="322">
@@ -13643,7 +13643,7 @@
         <v>12</v>
       </c>
       <c r="K322" t="n">
-        <v>4.208420499246</v>
+        <v>4.205507087431931</v>
       </c>
     </row>
     <row r="323">
@@ -13684,7 +13684,7 @@
         <v>12</v>
       </c>
       <c r="K323" t="n">
-        <v>4.208420499246</v>
+        <v>4.205507087431931</v>
       </c>
     </row>
     <row r="324">
@@ -13725,7 +13725,7 @@
         <v>12</v>
       </c>
       <c r="K324" t="n">
-        <v>4.253280651244157</v>
+        <v>4.253764319255618</v>
       </c>
     </row>
     <row r="325">
@@ -13766,7 +13766,7 @@
         <v>12</v>
       </c>
       <c r="K325" t="n">
-        <v>4.253280651244157</v>
+        <v>4.253764319255618</v>
       </c>
     </row>
     <row r="326">
@@ -13807,7 +13807,7 @@
         <v>12</v>
       </c>
       <c r="K326" t="n">
-        <v>4.204984097251353</v>
+        <v>4.206205314899307</v>
       </c>
     </row>
     <row r="327">
@@ -13848,7 +13848,7 @@
         <v>12</v>
       </c>
       <c r="K327" t="n">
-        <v>4.11856228728011</v>
+        <v>4.120393016532408</v>
       </c>
     </row>
     <row r="328">
@@ -13889,7 +13889,7 @@
         <v>12</v>
       </c>
       <c r="K328" t="n">
-        <v>4.11856228728011</v>
+        <v>4.120393016532408</v>
       </c>
     </row>
     <row r="329">
@@ -13930,7 +13930,7 @@
         <v>12</v>
       </c>
       <c r="K329" t="n">
-        <v>4.016052122628828</v>
+        <v>4.017863996406219</v>
       </c>
     </row>
     <row r="330">
@@ -13971,7 +13971,7 @@
         <v>12</v>
       </c>
       <c r="K330" t="n">
-        <v>4.016052122628828</v>
+        <v>4.017863996406219</v>
       </c>
     </row>
     <row r="331">
@@ -14012,7 +14012,7 @@
         <v>12</v>
       </c>
       <c r="K331" t="n">
-        <v>4.016052122628828</v>
+        <v>4.017863996406219</v>
       </c>
     </row>
     <row r="332">
@@ -14053,7 +14053,7 @@
         <v>12</v>
       </c>
       <c r="K332" t="n">
-        <v>3.976864467947827</v>
+        <v>3.979080383830661</v>
       </c>
     </row>
     <row r="333">
@@ -14094,7 +14094,7 @@
         <v>12</v>
       </c>
       <c r="K333" t="n">
-        <v>3.829368804988613</v>
+        <v>3.832146387277031</v>
       </c>
     </row>
     <row r="334">
@@ -14135,7 +14135,7 @@
         <v>12</v>
       </c>
       <c r="K334" t="n">
-        <v>3.717309882233985</v>
+        <v>3.720287054272315</v>
       </c>
     </row>
     <row r="335">
@@ -14176,7 +14176,7 @@
         <v>12</v>
       </c>
       <c r="K335" t="n">
-        <v>3.717309882233985</v>
+        <v>3.720287054272315</v>
       </c>
     </row>
     <row r="336">
@@ -14217,7 +14217,7 @@
         <v>12</v>
       </c>
       <c r="K336" t="n">
-        <v>3.601248552599805</v>
+        <v>3.601353824696562</v>
       </c>
     </row>
     <row r="337">
@@ -14258,7 +14258,7 @@
         <v>12</v>
       </c>
       <c r="K337" t="n">
-        <v>3.614569184025537</v>
+        <v>3.614336555486712</v>
       </c>
     </row>
     <row r="338">
@@ -14299,7 +14299,7 @@
         <v>12</v>
       </c>
       <c r="K338" t="n">
-        <v>3.614569184025537</v>
+        <v>3.614336555486712</v>
       </c>
     </row>
     <row r="339">
@@ -14340,7 +14340,7 @@
         <v>12</v>
       </c>
       <c r="K339" t="n">
-        <v>3.642804970467443</v>
+        <v>3.642178781181344</v>
       </c>
     </row>
     <row r="340">
@@ -14381,7 +14381,7 @@
         <v>12</v>
       </c>
       <c r="K340" t="n">
-        <v>3.651275254337981</v>
+        <v>3.650865924300978</v>
       </c>
     </row>
     <row r="341">
@@ -14422,7 +14422,7 @@
         <v>12</v>
       </c>
       <c r="K341" t="n">
-        <v>3.726089902536564</v>
+        <v>3.726333974967388</v>
       </c>
     </row>
     <row r="342">
@@ -14463,7 +14463,7 @@
         <v>12</v>
       </c>
       <c r="K342" t="n">
-        <v>3.716238914904418</v>
+        <v>3.717629801278993</v>
       </c>
     </row>
     <row r="343">
@@ -14504,7 +14504,7 @@
         <v>12</v>
       </c>
       <c r="K343" t="n">
-        <v>3.647636927009276</v>
+        <v>3.618911867889351</v>
       </c>
     </row>
     <row r="344">
@@ -14545,7 +14545,7 @@
         <v>12</v>
       </c>
       <c r="K344" t="n">
-        <v>3.616428472844463</v>
+        <v>3.618911867889351</v>
       </c>
     </row>
     <row r="345">
@@ -14586,7 +14586,7 @@
         <v>12</v>
       </c>
       <c r="K345" t="n">
-        <v>3.544939488492044</v>
+        <v>3.550414254584332</v>
       </c>
     </row>
     <row r="346">
@@ -14627,7 +14627,7 @@
         <v>12</v>
       </c>
       <c r="K346" t="n">
-        <v>3.442828928590163</v>
+        <v>3.449035259654301</v>
       </c>
     </row>
     <row r="347">
@@ -14668,7 +14668,7 @@
         <v>12</v>
       </c>
       <c r="K347" t="n">
-        <v>3.442828928590163</v>
+        <v>3.449035259654301</v>
       </c>
     </row>
     <row r="348">
@@ -14709,7 +14709,7 @@
         <v>12</v>
       </c>
       <c r="K348" t="n">
-        <v>3.224479238105011</v>
+        <v>3.228962970021692</v>
       </c>
     </row>
     <row r="349">
@@ -14750,7 +14750,7 @@
         <v>12</v>
       </c>
       <c r="K349" t="n">
-        <v>3.179660949132971</v>
+        <v>3.181519313750041</v>
       </c>
     </row>
     <row r="350">
@@ -14791,7 +14791,7 @@
         <v>12</v>
       </c>
       <c r="K350" t="n">
-        <v>3.141739571348284</v>
+        <v>3.144146679643293</v>
       </c>
     </row>
     <row r="351">
@@ -14832,7 +14832,7 @@
         <v>12</v>
       </c>
       <c r="K351" t="n">
-        <v>3.103576179581915</v>
+        <v>3.103263114451305</v>
       </c>
     </row>
     <row r="352">
@@ -14873,7 +14873,7 @@
         <v>12</v>
       </c>
       <c r="K352" t="n">
-        <v>3.271625035111303</v>
+        <v>3.267479236188045</v>
       </c>
     </row>
     <row r="353">
@@ -14914,7 +14914,7 @@
         <v>12</v>
       </c>
       <c r="K353" t="n">
-        <v>3.332028071578465</v>
+        <v>3.328523579060723</v>
       </c>
     </row>
     <row r="354">
@@ -14955,7 +14955,7 @@
         <v>12</v>
       </c>
       <c r="K354" t="n">
-        <v>3.39264960925539</v>
+        <v>3.389147682296211</v>
       </c>
     </row>
     <row r="355">
@@ -14996,7 +14996,7 @@
         <v>12</v>
       </c>
       <c r="K355" t="n">
-        <v>3.39264960925539</v>
+        <v>3.44934136731067</v>
       </c>
     </row>
     <row r="356">
@@ -15037,7 +15037,7 @@
         <v>12</v>
       </c>
       <c r="K356" t="n">
-        <v>3.681023701356659</v>
+        <v>3.67350818086054</v>
       </c>
     </row>
     <row r="357">
@@ -15078,7 +15078,7 @@
         <v>12</v>
       </c>
       <c r="K357" t="n">
-        <v>3.681023701356659</v>
+        <v>3.67350818086054</v>
       </c>
     </row>
     <row r="358">
@@ -15119,7 +15119,7 @@
         <v>12</v>
       </c>
       <c r="K358" t="n">
-        <v>3.681023701356659</v>
+        <v>3.67350818086054</v>
       </c>
     </row>
     <row r="359">
@@ -15160,7 +15160,7 @@
         <v>12</v>
       </c>
       <c r="K359" t="n">
-        <v>3.681023701356659</v>
+        <v>3.759034608781058</v>
       </c>
     </row>
     <row r="360">
@@ -15201,7 +15201,7 @@
         <v>12</v>
       </c>
       <c r="K360" t="n">
-        <v>3.93497382716593</v>
+        <v>3.93113198146775</v>
       </c>
     </row>
     <row r="361">
@@ -15242,7 +15242,7 @@
         <v>12</v>
       </c>
       <c r="K361" t="n">
-        <v>3.93497382716593</v>
+        <v>3.93113198146775</v>
       </c>
     </row>
     <row r="362">
@@ -15283,7 +15283,7 @@
         <v>12</v>
       </c>
       <c r="K362" t="n">
-        <v>3.93497382716593</v>
+        <v>3.93113198146775</v>
       </c>
     </row>
     <row r="363">
@@ -15324,7 +15324,7 @@
         <v>12</v>
       </c>
       <c r="K363" t="n">
-        <v>4.046355328597745</v>
+        <v>4.044516485933277</v>
       </c>
     </row>
     <row r="364">
@@ -15365,7 +15365,7 @@
         <v>12</v>
       </c>
       <c r="K364" t="n">
-        <v>4.094965680458862</v>
+        <v>4.095401095018065</v>
       </c>
     </row>
     <row r="365">
@@ -15406,7 +15406,7 @@
         <v>12</v>
       </c>
       <c r="K365" t="n">
-        <v>4.090511017821964</v>
+        <v>4.088845480748617</v>
       </c>
     </row>
     <row r="366">
@@ -15447,7 +15447,7 @@
         <v>12</v>
       </c>
       <c r="K366" t="n">
-        <v>4.079853526575469</v>
+        <v>4.079163307946108</v>
       </c>
     </row>
     <row r="367">
@@ -15488,7 +15488,7 @@
         <v>12</v>
       </c>
       <c r="K367" t="n">
-        <v>4.064424058259151</v>
+        <v>4.064283545607989</v>
       </c>
     </row>
     <row r="368">
@@ -15529,7 +15529,7 @@
         <v>12</v>
       </c>
       <c r="K368" t="n">
-        <v>4.064424058259151</v>
+        <v>4.064283545607989</v>
       </c>
     </row>
     <row r="369">
@@ -15570,7 +15570,7 @@
         <v>12</v>
       </c>
       <c r="K369" t="n">
-        <v>4.051274663213008</v>
+        <v>4.048294391918364</v>
       </c>
     </row>
     <row r="370">
@@ -15611,7 +15611,7 @@
         <v>12</v>
       </c>
       <c r="K370" t="n">
-        <v>4.032416532855316</v>
+        <v>4.031530346455333</v>
       </c>
     </row>
     <row r="371">
@@ -15652,7 +15652,7 @@
         <v>12</v>
       </c>
       <c r="K371" t="n">
-        <v>3.995798035708694</v>
+        <v>3.99425252423884</v>
       </c>
     </row>
     <row r="372">
@@ -15693,7 +15693,7 @@
         <v>12</v>
       </c>
       <c r="K372" t="n">
-        <v>3.904937929069707</v>
+        <v>3.903201248648701</v>
       </c>
     </row>
     <row r="373">
@@ -15734,7 +15734,7 @@
         <v>12</v>
       </c>
       <c r="K373" t="n">
-        <v>3.904937929069707</v>
+        <v>3.903201248648701</v>
       </c>
     </row>
     <row r="374">
@@ -15775,7 +15775,7 @@
         <v>12</v>
       </c>
       <c r="K374" t="n">
-        <v>3.902325182219681</v>
+        <v>3.901897355672217</v>
       </c>
     </row>
     <row r="375">
@@ -15816,7 +15816,7 @@
         <v>12</v>
       </c>
       <c r="K375" t="n">
-        <v>3.902325182219681</v>
+        <v>3.901897355672217</v>
       </c>
     </row>
     <row r="376">
@@ -15857,7 +15857,7 @@
         <v>12</v>
       </c>
       <c r="K376" t="n">
-        <v>3.89954908275964</v>
+        <v>3.90023721237383</v>
       </c>
     </row>
     <row r="377">
@@ -15898,7 +15898,7 @@
         <v>12</v>
       </c>
       <c r="K377" t="n">
-        <v>3.81604229559243</v>
+        <v>3.821236181227583</v>
       </c>
     </row>
     <row r="378">
@@ -15939,7 +15939,7 @@
         <v>12</v>
       </c>
       <c r="K378" t="n">
-        <v>3.81604229559243</v>
+        <v>3.821236181227583</v>
       </c>
     </row>
     <row r="379">
@@ -15980,7 +15980,7 @@
         <v>12</v>
       </c>
       <c r="K379" t="n">
-        <v>3.81604229559243</v>
+        <v>3.821236181227583</v>
       </c>
     </row>
     <row r="380">
@@ -16021,7 +16021,7 @@
         <v>12</v>
       </c>
       <c r="K380" t="n">
-        <v>3.747192771849555</v>
+        <v>3.746904755526147</v>
       </c>
     </row>
     <row r="381">
@@ -16062,7 +16062,7 @@
         <v>12</v>
       </c>
       <c r="K381" t="n">
-        <v>3.747192771849555</v>
+        <v>3.746904755526147</v>
       </c>
     </row>
     <row r="382">
@@ -16103,7 +16103,7 @@
         <v>12</v>
       </c>
       <c r="K382" t="n">
-        <v>3.716400996354732</v>
+        <v>3.712889284962927</v>
       </c>
     </row>
     <row r="383">
@@ -16144,7 +16144,7 @@
         <v>12</v>
       </c>
       <c r="K383" t="n">
-        <v>3.716400996354732</v>
+        <v>3.712889284962927</v>
       </c>
     </row>
     <row r="384">
@@ -16185,7 +16185,7 @@
         <v>12</v>
       </c>
       <c r="K384" t="n">
-        <v>3.695657682922242</v>
+        <v>3.692307599093144</v>
       </c>
     </row>
     <row r="385">
@@ -16226,7 +16226,7 @@
         <v>12</v>
       </c>
       <c r="K385" t="n">
-        <v>3.7069232042469</v>
+        <v>3.706403208606019</v>
       </c>
     </row>
     <row r="386">
@@ -16267,7 +16267,7 @@
         <v>12</v>
       </c>
       <c r="K386" t="n">
-        <v>3.7069232042469</v>
+        <v>3.706403208606019</v>
       </c>
     </row>
     <row r="387">
@@ -16308,7 +16308,7 @@
         <v>12</v>
       </c>
       <c r="K387" t="n">
-        <v>3.727054906519708</v>
+        <v>3.727032916289831</v>
       </c>
     </row>
     <row r="388">
@@ -16349,7 +16349,7 @@
         <v>12</v>
       </c>
       <c r="K388" t="n">
-        <v>3.727485012341275</v>
+        <v>3.727459282286585</v>
       </c>
     </row>
     <row r="389">
@@ -16390,7 +16390,7 @@
         <v>12</v>
       </c>
       <c r="K389" t="n">
-        <v>3.777891374981178</v>
+        <v>3.775304394078796</v>
       </c>
     </row>
     <row r="390">
@@ -16431,7 +16431,7 @@
         <v>12</v>
       </c>
       <c r="K390" t="n">
-        <v>3.777891374981178</v>
+        <v>3.775304394078796</v>
       </c>
     </row>
     <row r="391">
@@ -16472,7 +16472,7 @@
         <v>12</v>
       </c>
       <c r="K391" t="n">
-        <v>3.927068517355079</v>
+        <v>3.925769888190252</v>
       </c>
     </row>
     <row r="392">
@@ -16513,7 +16513,7 @@
         <v>12</v>
       </c>
       <c r="K392" t="n">
-        <v>3.942216011569942</v>
+        <v>3.942381651102122</v>
       </c>
     </row>
     <row r="393">
@@ -16554,7 +16554,7 @@
         <v>12</v>
       </c>
       <c r="K393" t="n">
-        <v>3.910924677918464</v>
+        <v>3.914487246633875</v>
       </c>
     </row>
     <row r="394">
@@ -16595,7 +16595,7 @@
         <v>12</v>
       </c>
       <c r="K394" t="n">
-        <v>3.646452506582347</v>
+        <v>3.651659517196708</v>
       </c>
     </row>
     <row r="395">
@@ -16636,7 +16636,7 @@
         <v>12</v>
       </c>
       <c r="K395" t="n">
-        <v>3.646452506582347</v>
+        <v>3.651659517196708</v>
       </c>
     </row>
     <row r="396">
@@ -16677,7 +16677,7 @@
         <v>12</v>
       </c>
       <c r="K396" t="n">
-        <v>3.330273535484118</v>
+        <v>3.333852501808082</v>
       </c>
     </row>
     <row r="397">
@@ -16718,7 +16718,7 @@
         <v>12</v>
       </c>
       <c r="K397" t="n">
-        <v>3.371835260867346</v>
+        <v>3.369222620190798</v>
       </c>
     </row>
     <row r="398">
@@ -16759,7 +16759,7 @@
         <v>12</v>
       </c>
       <c r="K398" t="n">
-        <v>3.371835260867346</v>
+        <v>3.369222620190798</v>
       </c>
     </row>
     <row r="399">
@@ -16800,7 +16800,7 @@
         <v>12</v>
       </c>
       <c r="K399" t="n">
-        <v>4.181236727920914</v>
+        <v>4.173171414218996</v>
       </c>
     </row>
     <row r="400">
@@ -16841,7 +16841,7 @@
         <v>12</v>
       </c>
       <c r="K400" t="n">
-        <v>4.534175874821312</v>
+        <v>4.531995397790884</v>
       </c>
     </row>
     <row r="401">
@@ -16882,7 +16882,7 @@
         <v>12</v>
       </c>
       <c r="K401" t="n">
-        <v>4.556854453507473</v>
+        <v>4.556645274704496</v>
       </c>
     </row>
     <row r="402">
@@ -16923,7 +16923,7 @@
         <v>12</v>
       </c>
       <c r="K402" t="n">
-        <v>4.539443432680001</v>
+        <v>4.541220156884497</v>
       </c>
     </row>
     <row r="403">
@@ -16964,7 +16964,7 @@
         <v>12</v>
       </c>
       <c r="K403" t="n">
-        <v>4.539443432680001</v>
+        <v>4.541220156884497</v>
       </c>
     </row>
     <row r="404">
@@ -17005,7 +17005,7 @@
         <v>12</v>
       </c>
       <c r="K404" t="n">
-        <v>4.280797347338424</v>
+        <v>4.282031688945008</v>
       </c>
     </row>
     <row r="405">
@@ -17046,7 +17046,7 @@
         <v>12</v>
       </c>
       <c r="K405" t="n">
-        <v>4.269384811731056</v>
+        <v>4.26969932611971</v>
       </c>
     </row>
     <row r="406">
@@ -17087,7 +17087,7 @@
         <v>12</v>
       </c>
       <c r="K406" t="n">
-        <v>4.264735244902993</v>
+        <v>4.264944363723891</v>
       </c>
     </row>
     <row r="407">
@@ -17128,7 +17128,7 @@
         <v>12</v>
       </c>
       <c r="K407" t="n">
-        <v>4.262292726504922</v>
+        <v>4.262102435879059</v>
       </c>
     </row>
     <row r="408">
@@ -17169,7 +17169,7 @@
         <v>12</v>
       </c>
       <c r="K408" t="n">
-        <v>4.262292726504922</v>
+        <v>4.263673270723966</v>
       </c>
     </row>
     <row r="409">
@@ -17210,7 +17210,7 @@
         <v>12</v>
       </c>
       <c r="K409" t="n">
-        <v>4.26986651340288</v>
+        <v>4.270283539746327</v>
       </c>
     </row>
     <row r="410">
@@ -17251,7 +17251,7 @@
         <v>12</v>
       </c>
       <c r="K410" t="n">
-        <v>4.300321810001186</v>
+        <v>4.299036677417796</v>
       </c>
     </row>
     <row r="411">
@@ -17292,7 +17292,7 @@
         <v>12</v>
       </c>
       <c r="K411" t="n">
-        <v>4.300321810001186</v>
+        <v>4.299036677417796</v>
       </c>
     </row>
     <row r="412">
@@ -17333,7 +17333,7 @@
         <v>12</v>
       </c>
       <c r="K412" t="n">
-        <v>4.300321810001186</v>
+        <v>4.299036677417796</v>
       </c>
     </row>
     <row r="413">
@@ -17374,7 +17374,7 @@
         <v>12</v>
       </c>
       <c r="K413" t="n">
-        <v>4.31852538377336</v>
+        <v>4.316445953548087</v>
       </c>
     </row>
     <row r="414">
@@ -17415,7 +17415,7 @@
         <v>12</v>
       </c>
       <c r="K414" t="n">
-        <v>4.356460355585511</v>
+        <v>4.355128513544964</v>
       </c>
     </row>
     <row r="415">
@@ -17456,7 +17456,7 @@
         <v>12</v>
       </c>
       <c r="K415" t="n">
-        <v>4.356460355585511</v>
+        <v>4.355128513544964</v>
       </c>
     </row>
     <row r="416">
@@ -17497,7 +17497,7 @@
         <v>12</v>
       </c>
       <c r="K416" t="n">
-        <v>4.361701931419487</v>
+        <v>4.361205780674502</v>
       </c>
     </row>
     <row r="417">
@@ -17538,7 +17538,7 @@
         <v>12</v>
       </c>
       <c r="K417" t="n">
-        <v>4.301398698094448</v>
+        <v>4.255823026826337</v>
       </c>
     </row>
     <row r="418">
@@ -17579,7 +17579,7 @@
         <v>12</v>
       </c>
       <c r="K418" t="n">
-        <v>4.209401645323718</v>
+        <v>4.215851223284368</v>
       </c>
     </row>
     <row r="419">
@@ -17620,7 +17620,7 @@
         <v>12</v>
       </c>
       <c r="K419" t="n">
-        <v>4.209401645323718</v>
+        <v>4.215851223284368</v>
       </c>
     </row>
     <row r="420">
@@ -17661,7 +17661,7 @@
         <v>12</v>
       </c>
       <c r="K420" t="n">
-        <v>4.191447476468136</v>
+        <v>4.192484471970281</v>
       </c>
     </row>
     <row r="421">
@@ -17702,7 +17702,7 @@
         <v>12</v>
       </c>
       <c r="K421" t="n">
-        <v>4.191447476468136</v>
+        <v>4.192484471970281</v>
       </c>
     </row>
     <row r="422">
@@ -17743,7 +17743,7 @@
         <v>12</v>
       </c>
       <c r="K422" t="n">
-        <v>4.056703917921547</v>
+        <v>4.05553688099446</v>
       </c>
     </row>
     <row r="423">
@@ -17784,7 +17784,7 @@
         <v>12</v>
       </c>
       <c r="K423" t="n">
-        <v>3.840503814125141</v>
+        <v>3.840885039468298</v>
       </c>
     </row>
     <row r="424">
@@ -17825,7 +17825,7 @@
         <v>12</v>
       </c>
       <c r="K424" t="n">
-        <v>3.661907100190235</v>
+        <v>3.661727785260274</v>
       </c>
     </row>
     <row r="425">
@@ -17866,7 +17866,7 @@
         <v>12</v>
       </c>
       <c r="K425" t="n">
-        <v>3.681006404116291</v>
+        <v>3.679567603161367</v>
       </c>
     </row>
     <row r="426">
@@ -17907,7 +17907,7 @@
         <v>12</v>
       </c>
       <c r="K426" t="n">
-        <v>3.718439743789945</v>
+        <v>3.716817498938134</v>
       </c>
     </row>
     <row r="427">
@@ -17948,7 +17948,7 @@
         <v>12</v>
       </c>
       <c r="K427" t="n">
-        <v>3.835209738029023</v>
+        <v>3.833471091102376</v>
       </c>
     </row>
     <row r="428">
@@ -17989,7 +17989,7 @@
         <v>12</v>
       </c>
       <c r="K428" t="n">
-        <v>3.900174829512212</v>
+        <v>3.899363477684588</v>
       </c>
     </row>
     <row r="429">
@@ -18030,7 +18030,7 @@
         <v>12</v>
       </c>
       <c r="K429" t="n">
-        <v>3.908977539916504</v>
+        <v>3.909087402296648</v>
       </c>
     </row>
     <row r="430">
@@ -18071,7 +18071,7 @@
         <v>12</v>
       </c>
       <c r="K430" t="n">
-        <v>3.906161595795428</v>
+        <v>3.860772499745086</v>
       </c>
     </row>
     <row r="431">
@@ -18112,7 +18112,7 @@
         <v>12</v>
       </c>
       <c r="K431" t="n">
-        <v>3.584134533687182</v>
+        <v>3.586298624191295</v>
       </c>
     </row>
     <row r="432">
@@ -18153,7 +18153,7 @@
         <v>12</v>
       </c>
       <c r="K432" t="n">
-        <v>3.533546784800124</v>
+        <v>3.536217576955942</v>
       </c>
     </row>
     <row r="433">
@@ -18194,7 +18194,7 @@
         <v>12</v>
       </c>
       <c r="K433" t="n">
-        <v>3.533546784800124</v>
+        <v>3.536217576955942</v>
       </c>
     </row>
     <row r="434">
@@ -18235,7 +18235,7 @@
         <v>12</v>
       </c>
       <c r="K434" t="n">
-        <v>3.327066270127058</v>
+        <v>3.329355897533051</v>
       </c>
     </row>
     <row r="435">
@@ -18276,7 +18276,7 @@
         <v>12</v>
       </c>
       <c r="K435" t="n">
-        <v>3.327066270127058</v>
+        <v>3.329355897533051</v>
       </c>
     </row>
     <row r="436">
@@ -18317,7 +18317,7 @@
         <v>12</v>
       </c>
       <c r="K436" t="n">
-        <v>3.327066270127058</v>
+        <v>3.329355897533051</v>
       </c>
     </row>
     <row r="437">
@@ -18358,7 +18358,7 @@
         <v>12</v>
       </c>
       <c r="K437" t="n">
-        <v>3.095225708236811</v>
+        <v>3.095714786128676</v>
       </c>
     </row>
     <row r="438">
@@ -18399,7 +18399,7 @@
         <v>12</v>
       </c>
       <c r="K438" t="n">
-        <v>3.095225708236811</v>
+        <v>3.095714786128676</v>
       </c>
     </row>
     <row r="439">
@@ -18440,7 +18440,7 @@
         <v>12</v>
       </c>
       <c r="K439" t="n">
-        <v>3.095225708236811</v>
+        <v>3.095714786128676</v>
       </c>
     </row>
     <row r="440">
@@ -18481,7 +18481,7 @@
         <v>12</v>
       </c>
       <c r="K440" t="n">
-        <v>3.085222887440137</v>
+        <v>3.085548811526693</v>
       </c>
     </row>
     <row r="441">
@@ -18522,7 +18522,7 @@
         <v>12</v>
       </c>
       <c r="K441" t="n">
-        <v>3.070451231867775</v>
+        <v>3.070877541875436</v>
       </c>
     </row>
     <row r="442">
@@ -18563,7 +18563,7 @@
         <v>12</v>
       </c>
       <c r="K442" t="n">
-        <v>3.070451231867775</v>
+        <v>3.070877541875436</v>
       </c>
     </row>
     <row r="443">
@@ -18604,7 +18604,7 @@
         <v>12</v>
       </c>
       <c r="K443" t="n">
-        <v>3.054657340524292</v>
+        <v>3.05571429155445</v>
       </c>
     </row>
     <row r="444">
@@ -18645,7 +18645,7 @@
         <v>12</v>
       </c>
       <c r="K444" t="n">
-        <v>2.994197312714582</v>
+        <v>2.993596989495173</v>
       </c>
     </row>
     <row r="445">
@@ -18686,7 +18686,7 @@
         <v>12</v>
       </c>
       <c r="K445" t="n">
-        <v>2.994197312714582</v>
+        <v>2.993596989495173</v>
       </c>
     </row>
     <row r="446">
@@ -18727,7 +18727,7 @@
         <v>12</v>
       </c>
       <c r="K446" t="n">
-        <v>3.035501156476267</v>
+        <v>3.035839709419287</v>
       </c>
     </row>
     <row r="447">
@@ -18768,7 +18768,7 @@
         <v>12</v>
       </c>
       <c r="K447" t="n">
-        <v>3.120447987653189</v>
+        <v>3.12039422973989</v>
       </c>
     </row>
     <row r="448">
@@ -18809,7 +18809,7 @@
         <v>12</v>
       </c>
       <c r="K448" t="n">
-        <v>3.120447987653189</v>
+        <v>3.12039422973989</v>
       </c>
     </row>
     <row r="449">
@@ -18850,7 +18850,7 @@
         <v>12</v>
       </c>
       <c r="K449" t="n">
-        <v>4.017516597766641</v>
+        <v>4.062588214254307</v>
       </c>
     </row>
     <row r="450">
@@ -18891,7 +18891,7 @@
         <v>12</v>
       </c>
       <c r="K450" t="n">
-        <v>4.017516597766641</v>
+        <v>4.062588214254307</v>
       </c>
     </row>
     <row r="451">
@@ -18932,7 +18932,7 @@
         <v>12</v>
       </c>
       <c r="K451" t="n">
-        <v>4.017516597766641</v>
+        <v>4.062588214254307</v>
       </c>
     </row>
     <row r="452">
@@ -18973,7 +18973,7 @@
         <v>12</v>
       </c>
       <c r="K452" t="n">
-        <v>3.740667489898562</v>
+        <v>3.772752409801588</v>
       </c>
     </row>
     <row r="453">
@@ -19014,7 +19014,7 @@
         <v>12</v>
       </c>
       <c r="K453" t="n">
-        <v>3.740667489898562</v>
+        <v>3.772752409801588</v>
       </c>
     </row>
     <row r="454">
@@ -19055,7 +19055,7 @@
         <v>12</v>
       </c>
       <c r="K454" t="n">
-        <v>3.64663006678194</v>
+        <v>3.644289706221624</v>
       </c>
     </row>
     <row r="455">
@@ -19096,7 +19096,7 @@
         <v>12</v>
       </c>
       <c r="K455" t="n">
-        <v>3.463980192763072</v>
+        <v>3.464283946993778</v>
       </c>
     </row>
     <row r="456">
@@ -19137,7 +19137,7 @@
         <v>12</v>
       </c>
       <c r="K456" t="n">
-        <v>3.367743287209818</v>
+        <v>3.367843542595411</v>
       </c>
     </row>
     <row r="457">
@@ -19178,7 +19178,7 @@
         <v>12</v>
       </c>
       <c r="K457" t="n">
-        <v>3.178041040309818</v>
+        <v>3.178089038488973</v>
       </c>
     </row>
     <row r="458">
@@ -19219,7 +19219,7 @@
         <v>12</v>
       </c>
       <c r="K458" t="n">
-        <v>2.654812161131455</v>
+        <v>2.655044711054448</v>
       </c>
     </row>
     <row r="459">
@@ -19260,7 +19260,7 @@
         <v>12</v>
       </c>
       <c r="K459" t="n">
-        <v>2.385789925665169</v>
+        <v>2.385921147503803</v>
       </c>
     </row>
     <row r="460">
@@ -19301,7 +19301,7 @@
         <v>12</v>
       </c>
       <c r="K460" t="n">
-        <v>2.344520445367832</v>
+        <v>2.344608426322002</v>
       </c>
     </row>
     <row r="461">
@@ -19342,7 +19342,7 @@
         <v>12</v>
       </c>
       <c r="K461" t="n">
-        <v>2.309188151326286</v>
+        <v>2.309313535439912</v>
       </c>
     </row>
     <row r="462">
@@ -19383,7 +19383,7 @@
         <v>12</v>
       </c>
       <c r="K462" t="n">
-        <v>2.309188151326286</v>
+        <v>2.309313535439912</v>
       </c>
     </row>
     <row r="463">
@@ -19424,7 +19424,7 @@
         <v>12</v>
       </c>
       <c r="K463" t="n">
-        <v>2.358530936970293</v>
+        <v>2.358236476560578</v>
       </c>
     </row>
     <row r="464">
@@ -19465,7 +19465,7 @@
         <v>12</v>
       </c>
       <c r="K464" t="n">
-        <v>2.443440184160005</v>
+        <v>2.442955148582622</v>
       </c>
     </row>
     <row r="465">
@@ -19506,7 +19506,7 @@
         <v>12</v>
       </c>
       <c r="K465" t="n">
-        <v>2.833815609846221</v>
+        <v>2.83285176691518</v>
       </c>
     </row>
     <row r="466">
@@ -19547,7 +19547,7 @@
         <v>12</v>
       </c>
       <c r="K466" t="n">
-        <v>3.319334674415779</v>
+        <v>3.318516998520946</v>
       </c>
     </row>
     <row r="467">
@@ -19588,7 +19588,7 @@
         <v>12</v>
       </c>
       <c r="K467" t="n">
-        <v>3.424620809557982</v>
+        <v>3.424017353546439</v>
       </c>
     </row>
     <row r="468">
@@ -19629,7 +19629,7 @@
         <v>12</v>
       </c>
       <c r="K468" t="n">
-        <v>3.509789395642378</v>
+        <v>3.509673783673281</v>
       </c>
     </row>
     <row r="469">
@@ -19670,7 +19670,7 @@
         <v>12</v>
       </c>
       <c r="K469" t="n">
-        <v>3.52600150151872</v>
+        <v>3.526074134259101</v>
       </c>
     </row>
     <row r="470">
@@ -19711,7 +19711,7 @@
         <v>12</v>
       </c>
       <c r="K470" t="n">
-        <v>3.520404145499782</v>
+        <v>3.520407936703183</v>
       </c>
     </row>
     <row r="471">
@@ -19752,7 +19752,7 @@
         <v>12</v>
       </c>
       <c r="K471" t="n">
-        <v>3.520404145499782</v>
+        <v>3.520407936703183</v>
       </c>
     </row>
     <row r="472">
@@ -19793,7 +19793,7 @@
         <v>12</v>
       </c>
       <c r="K472" t="n">
-        <v>3.502669227366506</v>
+        <v>3.502571004291533</v>
       </c>
     </row>
     <row r="473">
@@ -19834,7 +19834,7 @@
         <v>12</v>
       </c>
       <c r="K473" t="n">
-        <v>3.469876409859785</v>
+        <v>3.470169665562397</v>
       </c>
     </row>
     <row r="474">
@@ -19875,7 +19875,7 @@
         <v>12</v>
       </c>
       <c r="K474" t="n">
-        <v>3.378969325078366</v>
+        <v>3.379345508742946</v>
       </c>
     </row>
     <row r="475">
@@ -19916,7 +19916,7 @@
         <v>12</v>
       </c>
       <c r="K475" t="n">
-        <v>3.378969325078366</v>
+        <v>3.379345508742946</v>
       </c>
     </row>
     <row r="476">
@@ -19957,7 +19957,7 @@
         <v>12</v>
       </c>
       <c r="K476" t="n">
-        <v>3.378969325078366</v>
+        <v>3.379345508742946</v>
       </c>
     </row>
     <row r="477">
@@ -19998,7 +19998,7 @@
         <v>12</v>
       </c>
       <c r="K477" t="n">
-        <v>3.360699052426705</v>
+        <v>3.360729219366111</v>
       </c>
     </row>
     <row r="478">
@@ -20039,7 +20039,7 @@
         <v>12</v>
       </c>
       <c r="K478" t="n">
-        <v>3.360699052426705</v>
+        <v>3.360729219366111</v>
       </c>
     </row>
     <row r="479">
@@ -20080,7 +20080,7 @@
         <v>12</v>
       </c>
       <c r="K479" t="n">
-        <v>3.264016425666739</v>
+        <v>3.264281273266731</v>
       </c>
     </row>
     <row r="480">
@@ -20121,7 +20121,7 @@
         <v>12</v>
       </c>
       <c r="K480" t="n">
-        <v>3.222467693662079</v>
+        <v>3.222593464004698</v>
       </c>
     </row>
     <row r="481">
@@ -20162,7 +20162,7 @@
         <v>12</v>
       </c>
       <c r="K481" t="n">
-        <v>3.227675240392746</v>
+        <v>3.227579468602015</v>
       </c>
     </row>
     <row r="482">
@@ -20203,7 +20203,7 @@
         <v>12</v>
       </c>
       <c r="K482" t="n">
-        <v>3.254083343790902</v>
+        <v>3.253702900968223</v>
       </c>
     </row>
     <row r="483">
@@ -20244,7 +20244,7 @@
         <v>12</v>
       </c>
       <c r="K483" t="n">
-        <v>3.277185011623322</v>
+        <v>3.276882419951266</v>
       </c>
     </row>
     <row r="484">
@@ -20285,7 +20285,7 @@
         <v>12</v>
       </c>
       <c r="K484" t="n">
-        <v>3.296364545227487</v>
+        <v>3.296194162980746</v>
       </c>
     </row>
     <row r="485">
@@ -20326,7 +20326,7 @@
         <v>12</v>
       </c>
       <c r="K485" t="n">
-        <v>3.380435284289128</v>
+        <v>3.380023115480658</v>
       </c>
     </row>
     <row r="486">
@@ -20367,7 +20367,7 @@
         <v>12</v>
       </c>
       <c r="K486" t="n">
-        <v>3.506124698668016</v>
+        <v>3.504672697406458</v>
       </c>
     </row>
     <row r="487">
@@ -20408,7 +20408,7 @@
         <v>12</v>
       </c>
       <c r="K487" t="n">
-        <v>3.506124698668016</v>
+        <v>3.504672697406458</v>
       </c>
     </row>
     <row r="488">
@@ -20449,7 +20449,7 @@
         <v>12</v>
       </c>
       <c r="K488" t="n">
-        <v>3.506124698668016</v>
+        <v>3.504672697406458</v>
       </c>
     </row>
     <row r="489">
@@ -20490,7 +20490,7 @@
         <v>12</v>
       </c>
       <c r="K489" t="n">
-        <v>3.580366731520999</v>
+        <v>3.57810934928038</v>
       </c>
     </row>
     <row r="490">
@@ -20531,7 +20531,7 @@
         <v>12</v>
       </c>
       <c r="K490" t="n">
-        <v>3.641136051269071</v>
+        <v>3.639807912940011</v>
       </c>
     </row>
     <row r="491">
@@ -20572,7 +20572,7 @@
         <v>12</v>
       </c>
       <c r="K491" t="n">
-        <v>3.817250625797078</v>
+        <v>3.816598739160073</v>
       </c>
     </row>
     <row r="492">
@@ -20613,7 +20613,7 @@
         <v>12</v>
       </c>
       <c r="K492" t="n">
-        <v>3.932050941054031</v>
+        <v>3.93167275076717</v>
       </c>
     </row>
     <row r="493">
@@ -20654,7 +20654,7 @@
         <v>12</v>
       </c>
       <c r="K493" t="n">
-        <v>3.973387840843553</v>
+        <v>3.972911096746068</v>
       </c>
     </row>
     <row r="494">
@@ -20695,7 +20695,7 @@
         <v>12</v>
       </c>
       <c r="K494" t="n">
-        <v>4.022133969641607</v>
+        <v>4.02124311766832</v>
       </c>
     </row>
     <row r="495">
@@ -20736,7 +20736,7 @@
         <v>12</v>
       </c>
       <c r="K495" t="n">
-        <v>4.200818098804361</v>
+        <v>4.199510505265802</v>
       </c>
     </row>
     <row r="496">
@@ -20777,7 +20777,7 @@
         <v>12</v>
       </c>
       <c r="K496" t="n">
-        <v>4.315126756231936</v>
+        <v>4.314458847996504</v>
       </c>
     </row>
     <row r="497">
@@ -20818,7 +20818,7 @@
         <v>12</v>
       </c>
       <c r="K497" t="n">
-        <v>4.315126756231936</v>
+        <v>4.314458847996504</v>
       </c>
     </row>
     <row r="498">
@@ -20859,7 +20859,7 @@
         <v>12</v>
       </c>
       <c r="K498" t="n">
-        <v>4.297127956467921</v>
+        <v>4.297620835428761</v>
       </c>
     </row>
     <row r="499">
@@ -20900,7 +20900,7 @@
         <v>12</v>
       </c>
       <c r="K499" t="n">
-        <v>4.297127956467921</v>
+        <v>4.297620835428761</v>
       </c>
     </row>
     <row r="500">
@@ -20941,7 +20941,7 @@
         <v>12</v>
       </c>
       <c r="K500" t="n">
-        <v>4.297127956467921</v>
+        <v>4.297620835428761</v>
       </c>
     </row>
     <row r="501">
@@ -20982,7 +20982,7 @@
         <v>12</v>
       </c>
       <c r="K501" t="n">
-        <v>4.283628632022507</v>
+        <v>4.314219822264801</v>
       </c>
     </row>
     <row r="502">
@@ -21023,7 +21023,7 @@
         <v>12</v>
       </c>
       <c r="K502" t="n">
-        <v>4.305141370084162</v>
+        <v>4.306559934914247</v>
       </c>
     </row>
     <row r="503">
@@ -21064,7 +21064,7 @@
         <v>12</v>
       </c>
       <c r="K503" t="n">
-        <v>3.973190519160861</v>
+        <v>3.976709777477144</v>
       </c>
     </row>
     <row r="504">
@@ -21105,7 +21105,7 @@
         <v>12</v>
       </c>
       <c r="K504" t="n">
-        <v>3.825682358829234</v>
+        <v>3.828676004165593</v>
       </c>
     </row>
     <row r="505">
@@ -21146,7 +21146,7 @@
         <v>12</v>
       </c>
       <c r="K505" t="n">
-        <v>3.616933261821356</v>
+        <v>3.618984907470239</v>
       </c>
     </row>
     <row r="506">
@@ -21187,7 +21187,7 @@
         <v>12</v>
       </c>
       <c r="K506" t="n">
-        <v>3.433420371344115</v>
+        <v>3.434067097574812</v>
       </c>
     </row>
     <row r="507">
@@ -21228,7 +21228,7 @@
         <v>12</v>
       </c>
       <c r="K507" t="n">
-        <v>3.409845417042359</v>
+        <v>3.409561594370477</v>
       </c>
     </row>
     <row r="508">
@@ -21269,7 +21269,7 @@
         <v>12</v>
       </c>
       <c r="K508" t="n">
-        <v>3.418430893528654</v>
+        <v>3.418295316456213</v>
       </c>
     </row>
     <row r="509">
@@ -21310,7 +21310,7 @@
         <v>12</v>
       </c>
       <c r="K509" t="n">
-        <v>3.42398838245801</v>
+        <v>3.423837880793837</v>
       </c>
     </row>
     <row r="510">
@@ -21351,7 +21351,7 @@
         <v>12</v>
       </c>
       <c r="K510" t="n">
-        <v>3.39009739675213</v>
+        <v>3.390736268572463</v>
       </c>
     </row>
     <row r="511">
@@ -21392,7 +21392,7 @@
         <v>12</v>
       </c>
       <c r="K511" t="n">
-        <v>3.346645761129527</v>
+        <v>3.348155822307562</v>
       </c>
     </row>
     <row r="512">
@@ -21433,7 +21433,7 @@
         <v>12</v>
       </c>
       <c r="K512" t="n">
-        <v>3.346645761129527</v>
+        <v>3.348155822307562</v>
       </c>
     </row>
     <row r="513">
@@ -21474,7 +21474,7 @@
         <v>12</v>
       </c>
       <c r="K513" t="n">
-        <v>3.277448409795145</v>
+        <v>3.279637295310447</v>
       </c>
     </row>
     <row r="514">
@@ -21515,7 +21515,7 @@
         <v>12</v>
       </c>
       <c r="K514" t="n">
-        <v>3.117778391676748</v>
+        <v>3.119522882691836</v>
       </c>
     </row>
     <row r="515">
@@ -21556,7 +21556,7 @@
         <v>12</v>
       </c>
       <c r="K515" t="n">
-        <v>3.037325650889228</v>
+        <v>3.038275815813988</v>
       </c>
     </row>
     <row r="516">
@@ -21597,7 +21597,7 @@
         <v>12</v>
       </c>
       <c r="K516" t="n">
-        <v>2.979135510186737</v>
+        <v>2.97979581293279</v>
       </c>
     </row>
     <row r="517">
@@ -21638,7 +21638,7 @@
         <v>12</v>
       </c>
       <c r="K517" t="n">
-        <v>2.964856408929588</v>
+        <v>2.964700877146538</v>
       </c>
     </row>
     <row r="518">
@@ -21679,7 +21679,7 @@
         <v>12</v>
       </c>
       <c r="K518" t="n">
-        <v>2.964856408929588</v>
+        <v>2.964700877146538</v>
       </c>
     </row>
     <row r="519">
@@ -21720,7 +21720,7 @@
         <v>12</v>
       </c>
       <c r="K519" t="n">
-        <v>2.953197421311996</v>
+        <v>2.953229069167224</v>
       </c>
     </row>
     <row r="520">
@@ -21761,7 +21761,7 @@
         <v>12</v>
       </c>
       <c r="K520" t="n">
-        <v>2.960118765800137</v>
+        <v>2.959801453303439</v>
       </c>
     </row>
     <row r="521">
@@ -21802,7 +21802,7 @@
         <v>12</v>
       </c>
       <c r="K521" t="n">
-        <v>2.977676564514107</v>
+        <v>2.976868034384355</v>
       </c>
     </row>
     <row r="522">
@@ -21843,7 +21843,7 @@
         <v>12</v>
       </c>
       <c r="K522" t="n">
-        <v>2.977676564514107</v>
+        <v>2.976868034384355</v>
       </c>
     </row>
     <row r="523">
@@ -21884,7 +21884,7 @@
         <v>12</v>
       </c>
       <c r="K523" t="n">
-        <v>3.049480923241088</v>
+        <v>3.048968345029999</v>
       </c>
     </row>
     <row r="524">
@@ -21925,7 +21925,7 @@
         <v>12</v>
       </c>
       <c r="K524" t="n">
-        <v>3.089282371386736</v>
+        <v>3.088357870300507</v>
       </c>
     </row>
     <row r="525">
@@ -21966,7 +21966,7 @@
         <v>12</v>
       </c>
       <c r="K525" t="n">
-        <v>3.314714429986739</v>
+        <v>3.311887980297825</v>
       </c>
     </row>
     <row r="526">
@@ -22007,7 +22007,7 @@
         <v>12</v>
       </c>
       <c r="K526" t="n">
-        <v>3.383795625959729</v>
+        <v>3.381809315629439</v>
       </c>
     </row>
     <row r="527">
@@ -22048,7 +22048,7 @@
         <v>12</v>
       </c>
       <c r="K527" t="n">
-        <v>3.394777914940569</v>
+        <v>3.396073246480741</v>
       </c>
     </row>
     <row r="528">
@@ -22089,7 +22089,7 @@
         <v>12</v>
       </c>
       <c r="K528" t="n">
-        <v>3.032040403374441</v>
+        <v>3.037500079142514</v>
       </c>
     </row>
     <row r="529">
@@ -22130,7 +22130,7 @@
         <v>12</v>
       </c>
       <c r="K529" t="n">
-        <v>2.75159478100331</v>
+        <v>2.754116259985005</v>
       </c>
     </row>
     <row r="530">
@@ -22171,7 +22171,7 @@
         <v>12</v>
       </c>
       <c r="K530" t="n">
-        <v>2.75159478100331</v>
+        <v>2.754116259985005</v>
       </c>
     </row>
     <row r="531">
@@ -22212,7 +22212,7 @@
         <v>12</v>
       </c>
       <c r="K531" t="n">
-        <v>2.635841574812391</v>
+        <v>2.637161946704848</v>
       </c>
     </row>
     <row r="532">
@@ -22253,7 +22253,7 @@
         <v>12</v>
       </c>
       <c r="K532" t="n">
-        <v>2.57590298010928</v>
+        <v>2.577272490777349</v>
       </c>
     </row>
     <row r="533">
@@ -22294,7 +22294,7 @@
         <v>12</v>
       </c>
       <c r="K533" t="n">
-        <v>2.470687257553676</v>
+        <v>2.470702124488291</v>
       </c>
     </row>
     <row r="534">
@@ -22335,7 +22335,7 @@
         <v>12</v>
       </c>
       <c r="K534" t="n">
-        <v>2.470687257553676</v>
+        <v>2.470702124488291</v>
       </c>
     </row>
     <row r="535">
@@ -22376,7 +22376,7 @@
         <v>12</v>
       </c>
       <c r="K535" t="n">
-        <v>2.470687257553676</v>
+        <v>2.470702124488291</v>
       </c>
     </row>
     <row r="536">
@@ -22417,7 +22417,7 @@
         <v>12</v>
       </c>
       <c r="K536" t="n">
-        <v>2.473572347030824</v>
+        <v>2.473395526984122</v>
       </c>
     </row>
     <row r="537">
@@ -22458,7 +22458,7 @@
         <v>12</v>
       </c>
       <c r="K537" t="n">
-        <v>2.512067072199121</v>
+        <v>2.511110099821737</v>
       </c>
     </row>
     <row r="538">
@@ -22499,7 +22499,7 @@
         <v>12</v>
       </c>
       <c r="K538" t="n">
-        <v>2.574071522284209</v>
+        <v>2.572868426235437</v>
       </c>
     </row>
     <row r="539">
@@ -22540,7 +22540,7 @@
         <v>12</v>
       </c>
       <c r="K539" t="n">
-        <v>2.574071522284209</v>
+        <v>2.572868426235437</v>
       </c>
     </row>
     <row r="540">
@@ -22581,7 +22581,7 @@
         <v>12</v>
       </c>
       <c r="K540" t="n">
-        <v>2.672693687813754</v>
+        <v>2.673358298922252</v>
       </c>
     </row>
     <row r="541">
@@ -22622,7 +22622,7 @@
         <v>12</v>
       </c>
       <c r="K541" t="n">
-        <v>2.672693687813754</v>
+        <v>2.673358298922252</v>
       </c>
     </row>
     <row r="542">
@@ -22663,7 +22663,7 @@
         <v>12</v>
       </c>
       <c r="K542" t="n">
-        <v>2.672693687813754</v>
+        <v>2.673358298922252</v>
       </c>
     </row>
     <row r="543">
@@ -22704,7 +22704,7 @@
         <v>12</v>
       </c>
       <c r="K543" t="n">
-        <v>2.672693687813754</v>
+        <v>2.673358298922252</v>
       </c>
     </row>
     <row r="544">
@@ -22745,7 +22745,7 @@
         <v>12</v>
       </c>
       <c r="K544" t="n">
-        <v>2.472705570597032</v>
+        <v>2.474900145068955</v>
       </c>
     </row>
     <row r="545">
@@ -22786,7 +22786,7 @@
         <v>12</v>
       </c>
       <c r="K545" t="n">
-        <v>2.400297296824222</v>
+        <v>2.401344645982205</v>
       </c>
     </row>
     <row r="546">
@@ -22827,7 +22827,7 @@
         <v>12</v>
       </c>
       <c r="K546" t="n">
-        <v>2.379675900625711</v>
+        <v>2.378535856927523</v>
       </c>
     </row>
     <row r="547">
@@ -22868,7 +22868,7 @@
         <v>12</v>
       </c>
       <c r="K547" t="n">
-        <v>2.379675900625711</v>
+        <v>2.378535856927523</v>
       </c>
     </row>
     <row r="548">
@@ -22909,7 +22909,7 @@
         <v>12</v>
       </c>
       <c r="K548" t="n">
-        <v>2.379675900625711</v>
+        <v>2.378535856927523</v>
       </c>
     </row>
     <row r="549">
@@ -22950,7 +22950,7 @@
         <v>12</v>
       </c>
       <c r="K549" t="n">
-        <v>2.4166260687925</v>
+        <v>2.414699233105643</v>
       </c>
     </row>
     <row r="550">
@@ -22991,7 +22991,7 @@
         <v>12</v>
       </c>
       <c r="K550" t="n">
-        <v>2.447244536282783</v>
+        <v>2.446638390335825</v>
       </c>
     </row>
     <row r="551">
@@ -23032,7 +23032,7 @@
         <v>12</v>
       </c>
       <c r="K551" t="n">
-        <v>2.175054442349441</v>
+        <v>2.181177971083748</v>
       </c>
     </row>
     <row r="552">
@@ -23073,7 +23073,7 @@
         <v>12</v>
       </c>
       <c r="K552" t="n">
-        <v>2.175054442349441</v>
+        <v>2.181177971083748</v>
       </c>
     </row>
     <row r="553">
@@ -23114,7 +23114,7 @@
         <v>12</v>
       </c>
       <c r="K553" t="n">
-        <v>1.925066695757111</v>
+        <v>1.930670036932822</v>
       </c>
     </row>
     <row r="554">
@@ -23155,7 +23155,7 @@
         <v>12</v>
       </c>
       <c r="K554" t="n">
-        <v>1.416087250369463</v>
+        <v>1.423405001103107</v>
       </c>
     </row>
     <row r="555">
@@ -23196,7 +23196,7 @@
         <v>12</v>
       </c>
       <c r="K555" t="n">
-        <v>1.123894382083565</v>
+        <v>1.12464132663886</v>
       </c>
     </row>
     <row r="556">
@@ -23237,7 +23237,7 @@
         <v>12</v>
       </c>
       <c r="K556" t="n">
-        <v>1.131080114638559</v>
+        <v>1.145634864609131</v>
       </c>
     </row>
     <row r="557">
@@ -23278,7 +23278,7 @@
         <v>12</v>
       </c>
       <c r="K557" t="n">
-        <v>1.145245298816898</v>
+        <v>1.145634864609131</v>
       </c>
     </row>
     <row r="558">
@@ -23319,7 +23319,7 @@
         <v>12</v>
       </c>
       <c r="K558" t="n">
-        <v>1.149221173839038</v>
+        <v>1.149540874391022</v>
       </c>
     </row>
     <row r="559">
@@ -23360,7 +23360,7 @@
         <v>12</v>
       </c>
       <c r="K559" t="n">
-        <v>1.159187990093719</v>
+        <v>1.160834081036322</v>
       </c>
     </row>
     <row r="560">
@@ -23401,7 +23401,7 @@
         <v>12</v>
       </c>
       <c r="K560" t="n">
-        <v>1.159187990093719</v>
+        <v>1.160834081036322</v>
       </c>
     </row>
     <row r="561">
@@ -23442,7 +23442,7 @@
         <v>12</v>
       </c>
       <c r="K561" t="n">
-        <v>1.115603605624463</v>
+        <v>1.117192343051377</v>
       </c>
     </row>
     <row r="562">
@@ -23483,7 +23483,7 @@
         <v>12</v>
       </c>
       <c r="K562" t="n">
-        <v>1.085638435459307</v>
+        <v>1.084022478320208</v>
       </c>
     </row>
     <row r="563">
@@ -23524,7 +23524,7 @@
         <v>12</v>
       </c>
       <c r="K563" t="n">
-        <v>1.085638435459307</v>
+        <v>1.084022478320208</v>
       </c>
     </row>
     <row r="564">
@@ -23565,7 +23565,7 @@
         <v>12</v>
       </c>
       <c r="K564" t="n">
-        <v>1.034396063423756</v>
+        <v>1.032694308104691</v>
       </c>
     </row>
     <row r="565">
@@ -23606,7 +23606,7 @@
         <v>12</v>
       </c>
       <c r="K565" t="n">
-        <v>1.012846939319374</v>
+        <v>1.008524525736803</v>
       </c>
     </row>
     <row r="566">
@@ -23647,7 +23647,7 @@
         <v>12</v>
       </c>
       <c r="K566" t="n">
-        <v>0.9694245790712051</v>
+        <v>0.9679336026137859</v>
       </c>
     </row>
     <row r="567">
@@ -23688,7 +23688,7 @@
         <v>12</v>
       </c>
       <c r="K567" t="n">
-        <v>0.9694245790712051</v>
+        <v>0.9679336026137859</v>
       </c>
     </row>
     <row r="568">
@@ -23729,7 +23729,7 @@
         <v>12</v>
       </c>
       <c r="K568" t="n">
-        <v>0.9743226145299796</v>
+        <v>0.9725254877836909</v>
       </c>
     </row>
     <row r="569">
@@ -23770,7 +23770,7 @@
         <v>12</v>
       </c>
       <c r="K569" t="n">
-        <v>0.9813648320274109</v>
+        <v>0.980806294554882</v>
       </c>
     </row>
     <row r="570">
@@ -23811,7 +23811,7 @@
         <v>12</v>
       </c>
       <c r="K570" t="n">
-        <v>1.004683167683627</v>
+        <v>1.004735429283389</v>
       </c>
     </row>
     <row r="571">
@@ -23852,7 +23852,7 @@
         <v>12</v>
       </c>
       <c r="K571" t="n">
-        <v>1.176159351903023</v>
+        <v>1.178568077064739</v>
       </c>
     </row>
     <row r="572">
@@ -23893,7 +23893,7 @@
         <v>12</v>
       </c>
       <c r="K572" t="n">
-        <v>1.176159351903023</v>
+        <v>1.178568077064739</v>
       </c>
     </row>
     <row r="573">
@@ -23934,7 +23934,7 @@
         <v>12</v>
       </c>
       <c r="K573" t="n">
-        <v>1.318042797516942</v>
+        <v>1.320821690152319</v>
       </c>
     </row>
     <row r="574">
@@ -23975,7 +23975,7 @@
         <v>12</v>
       </c>
       <c r="K574" t="n">
-        <v>1.565989837566988</v>
+        <v>1.568836340548849</v>
       </c>
     </row>
     <row r="575">
@@ -24016,7 +24016,7 @@
         <v>12</v>
       </c>
       <c r="K575" t="n">
-        <v>1.722219658620811</v>
+        <v>1.724376505097762</v>
       </c>
     </row>
     <row r="576">
@@ -24057,7 +24057,7 @@
         <v>12</v>
       </c>
       <c r="K576" t="n">
-        <v>1.783594776161037</v>
+        <v>1.785941315833454</v>
       </c>
     </row>
     <row r="577">
@@ -24098,7 +24098,7 @@
         <v>12</v>
       </c>
       <c r="K577" t="n">
-        <v>1.837233702001744</v>
+        <v>1.838501410786648</v>
       </c>
     </row>
     <row r="578">
@@ -24139,7 +24139,7 @@
         <v>12</v>
       </c>
       <c r="K578" t="n">
-        <v>1.860843114853313</v>
+        <v>1.860318160769866</v>
       </c>
     </row>
     <row r="579">
@@ -24180,7 +24180,7 @@
         <v>12</v>
       </c>
       <c r="K579" t="n">
-        <v>1.831540491402372</v>
+        <v>1.830023504381024</v>
       </c>
     </row>
     <row r="580">
@@ -24221,7 +24221,7 @@
         <v>12</v>
       </c>
       <c r="K580" t="n">
-        <v>1.831540491402372</v>
+        <v>1.830023504381024</v>
       </c>
     </row>
     <row r="581">
@@ -24262,7 +24262,7 @@
         <v>12</v>
       </c>
       <c r="K581" t="n">
-        <v>1.730775162375606</v>
+        <v>1.729134967725401</v>
       </c>
     </row>
     <row r="582">
@@ -24303,7 +24303,7 @@
         <v>12</v>
       </c>
       <c r="K582" t="n">
-        <v>1.626495109009087</v>
+        <v>1.624681905667168</v>
       </c>
     </row>
     <row r="583">
@@ -24344,7 +24344,7 @@
         <v>12</v>
       </c>
       <c r="K583" t="n">
-        <v>1.508042810549869</v>
+        <v>1.506470027273555</v>
       </c>
     </row>
     <row r="584">
@@ -24385,7 +24385,7 @@
         <v>12</v>
       </c>
       <c r="K584" t="n">
-        <v>1.508042810549869</v>
+        <v>1.506470027273555</v>
       </c>
     </row>
     <row r="585">
@@ -24426,7 +24426,7 @@
         <v>12</v>
       </c>
       <c r="K585" t="n">
-        <v>1.464517592491746</v>
+        <v>1.463324789690052</v>
       </c>
     </row>
     <row r="586">
@@ -24467,7 +24467,7 @@
         <v>12</v>
       </c>
       <c r="K586" t="n">
-        <v>1.358106769468824</v>
+        <v>1.357190758888041</v>
       </c>
     </row>
     <row r="587">
@@ -24508,7 +24508,7 @@
         <v>12</v>
       </c>
       <c r="K587" t="n">
-        <v>1.294085224276774</v>
+        <v>1.29330931557417</v>
       </c>
     </row>
     <row r="588">
@@ -24549,7 +24549,7 @@
         <v>12</v>
       </c>
       <c r="K588" t="n">
-        <v>1.28182156009641</v>
+        <v>1.281504298144889</v>
       </c>
     </row>
     <row r="589">
@@ -24590,7 +24590,7 @@
         <v>12</v>
       </c>
       <c r="K589" t="n">
-        <v>1.279328290163807</v>
+        <v>1.279238052299008</v>
       </c>
     </row>
     <row r="590">
@@ -24631,7 +24631,7 @@
         <v>12</v>
       </c>
       <c r="K590" t="n">
-        <v>1.279627798168528</v>
+        <v>1.279550021978489</v>
       </c>
     </row>
     <row r="591">
@@ -24672,7 +24672,7 @@
         <v>12</v>
       </c>
       <c r="K591" t="n">
-        <v>1.279627798168528</v>
+        <v>1.279550021978489</v>
       </c>
     </row>
     <row r="592">
@@ -24713,7 +24713,7 @@
         <v>12</v>
       </c>
       <c r="K592" t="n">
-        <v>1.315739881847221</v>
+        <v>1.316081978019089</v>
       </c>
     </row>
     <row r="593">
@@ -24754,7 +24754,7 @@
         <v>12</v>
       </c>
       <c r="K593" t="n">
-        <v>1.315739881847221</v>
+        <v>1.316081978019089</v>
       </c>
     </row>
     <row r="594">
@@ -24795,7 +24795,7 @@
         <v>12</v>
       </c>
       <c r="K594" t="n">
-        <v>1.310577091057348</v>
+        <v>1.310348973929904</v>
       </c>
     </row>
     <row r="595">
@@ -24836,7 +24836,7 @@
         <v>12</v>
       </c>
       <c r="K595" t="n">
-        <v>1.30326866984884</v>
+        <v>1.310348973929904</v>
       </c>
     </row>
     <row r="596">
@@ -24877,7 +24877,7 @@
         <v>12</v>
       </c>
       <c r="K596" t="n">
-        <v>1.30326866984884</v>
+        <v>1.302984685686638</v>
       </c>
     </row>
     <row r="597">
@@ -24918,7 +24918,7 @@
         <v>12</v>
       </c>
       <c r="K597" t="n">
-        <v>1.263554554362516</v>
+        <v>1.263080232672226</v>
       </c>
     </row>
     <row r="598">
@@ -24959,7 +24959,7 @@
         <v>12</v>
       </c>
       <c r="K598" t="n">
-        <v>1.227518049780225</v>
+        <v>1.22689528442262</v>
       </c>
     </row>
     <row r="599">
@@ -25000,7 +25000,7 @@
         <v>12</v>
       </c>
       <c r="K599" t="n">
-        <v>1.207156264275681</v>
+        <v>1.206464637960553</v>
       </c>
     </row>
     <row r="600">
@@ -25041,7 +25041,7 @@
         <v>12</v>
       </c>
       <c r="K600" t="n">
-        <v>1.207156264275681</v>
+        <v>1.206464637960553</v>
       </c>
     </row>
     <row r="601">
@@ -25082,7 +25082,7 @@
         <v>12</v>
       </c>
       <c r="K601" t="n">
-        <v>1.134033155534923</v>
+        <v>1.132240660988489</v>
       </c>
     </row>
     <row r="602">
@@ -25123,7 +25123,7 @@
         <v>12</v>
       </c>
       <c r="K602" t="n">
-        <v>1.134033155534923</v>
+        <v>1.132240660988489</v>
       </c>
     </row>
     <row r="603">
@@ -25164,7 +25164,7 @@
         <v>12</v>
       </c>
       <c r="K603" t="n">
-        <v>1.134033155534923</v>
+        <v>1.132240660988489</v>
       </c>
     </row>
     <row r="604">
@@ -25205,7 +25205,7 @@
         <v>12</v>
       </c>
       <c r="K604" t="n">
-        <v>0.8704435224870194</v>
+        <v>0.8688710811948952</v>
       </c>
     </row>
     <row r="605">
@@ -25246,7 +25246,7 @@
         <v>12</v>
       </c>
       <c r="K605" t="n">
-        <v>0.8704435224870194</v>
+        <v>0.8688710811948952</v>
       </c>
     </row>
     <row r="606">
@@ -25287,7 +25287,7 @@
         <v>12</v>
       </c>
       <c r="K606" t="n">
-        <v>0.8163402738983425</v>
+        <v>0.8147598714005579</v>
       </c>
     </row>
     <row r="607">
@@ -25328,7 +25328,7 @@
         <v>12</v>
       </c>
       <c r="K607" t="n">
-        <v>0.6948645988460298</v>
+        <v>0.6956443846201522</v>
       </c>
     </row>
     <row r="608">
@@ -25369,7 +25369,7 @@
         <v>12</v>
       </c>
       <c r="K608" t="n">
-        <v>0.723704314141481</v>
+        <v>0.7245333478603796</v>
       </c>
     </row>
     <row r="609">
@@ -25410,7 +25410,7 @@
         <v>12</v>
       </c>
       <c r="K609" t="n">
-        <v>0.7572489164461016</v>
+        <v>0.758264838439783</v>
       </c>
     </row>
     <row r="610">
@@ -25451,7 +25451,7 @@
         <v>12</v>
       </c>
       <c r="K610" t="n">
-        <v>0.7984816878000636</v>
+        <v>0.7997708930884277</v>
       </c>
     </row>
     <row r="611">
@@ -25492,7 +25492,7 @@
         <v>12</v>
       </c>
       <c r="K611" t="n">
-        <v>0.861434023328604</v>
+        <v>0.8642126278361183</v>
       </c>
     </row>
     <row r="612">
@@ -25533,7 +25533,7 @@
         <v>12</v>
       </c>
       <c r="K612" t="n">
-        <v>1.194708569544332</v>
+        <v>1.197438267615089</v>
       </c>
     </row>
     <row r="613">
@@ -25574,7 +25574,7 @@
         <v>12</v>
       </c>
       <c r="K613" t="n">
-        <v>1.539742672602747</v>
+        <v>1.541346732873448</v>
       </c>
     </row>
     <row r="614">
@@ -25615,7 +25615,7 @@
         <v>12</v>
       </c>
       <c r="K614" t="n">
-        <v>1.539742672602747</v>
+        <v>1.541346732873448</v>
       </c>
     </row>
     <row r="615">
@@ -25656,7 +25656,7 @@
         <v>12</v>
       </c>
       <c r="K615" t="n">
-        <v>1.745410162807558</v>
+        <v>1.746482394678834</v>
       </c>
     </row>
     <row r="616">
@@ -25697,7 +25697,7 @@
         <v>12</v>
       </c>
       <c r="K616" t="n">
-        <v>1.745410162807558</v>
+        <v>1.746482394678834</v>
       </c>
     </row>
     <row r="617">
@@ -25738,7 +25738,7 @@
         <v>12</v>
       </c>
       <c r="K617" t="n">
-        <v>1.745410162807558</v>
+        <v>1.746482394678834</v>
       </c>
     </row>
     <row r="618">
@@ -25779,7 +25779,7 @@
         <v>12</v>
       </c>
       <c r="K618" t="n">
-        <v>1.784111323469488</v>
+        <v>1.784829502860128</v>
       </c>
     </row>
     <row r="619">
@@ -25820,7 +25820,7 @@
         <v>12</v>
       </c>
       <c r="K619" t="n">
-        <v>1.784111323469488</v>
+        <v>1.784829502860128</v>
       </c>
     </row>
     <row r="620">
@@ -25861,7 +25861,7 @@
         <v>12</v>
       </c>
       <c r="K620" t="n">
-        <v>1.832790042436139</v>
+        <v>1.833266955993462</v>
       </c>
     </row>
     <row r="621">
@@ -25902,7 +25902,7 @@
         <v>12</v>
       </c>
       <c r="K621" t="n">
-        <v>1.846529331080078</v>
+        <v>1.846070882627397</v>
       </c>
     </row>
     <row r="622">
@@ -25943,7 +25943,7 @@
         <v>12</v>
       </c>
       <c r="K622" t="n">
-        <v>1.790405020241955</v>
+        <v>1.790765702313311</v>
       </c>
     </row>
     <row r="623">
@@ -25984,7 +25984,7 @@
         <v>12</v>
       </c>
       <c r="K623" t="n">
-        <v>1.790405020241955</v>
+        <v>1.790765702313311</v>
       </c>
     </row>
     <row r="624">
@@ -26025,7 +26025,7 @@
         <v>12</v>
       </c>
       <c r="K624" t="n">
-        <v>1.783828697312045</v>
+        <v>1.784268933925923</v>
       </c>
     </row>
     <row r="625">
@@ -26066,7 +26066,7 @@
         <v>12</v>
       </c>
       <c r="K625" t="n">
-        <v>1.783828697312045</v>
+        <v>1.784268933925923</v>
       </c>
     </row>
     <row r="626">
@@ -26107,7 +26107,7 @@
         <v>12</v>
       </c>
       <c r="K626" t="n">
-        <v>1.783828697312045</v>
+        <v>1.784268933925923</v>
       </c>
     </row>
     <row r="627">
@@ -26148,7 +26148,7 @@
         <v>12</v>
       </c>
       <c r="K627" t="n">
-        <v>1.789326123264181</v>
+        <v>1.789522602852701</v>
       </c>
     </row>
     <row r="628">
@@ -26189,7 +26189,7 @@
         <v>12</v>
       </c>
       <c r="K628" t="n">
-        <v>1.807139070882643</v>
+        <v>1.807813168026356</v>
       </c>
     </row>
     <row r="629">
@@ -26230,7 +26230,7 @@
         <v>12</v>
       </c>
       <c r="K629" t="n">
-        <v>1.807139070882643</v>
+        <v>1.807813168026356</v>
       </c>
     </row>
     <row r="630">
@@ -26271,7 +26271,7 @@
         <v>12</v>
       </c>
       <c r="K630" t="n">
-        <v>1.868468090956951</v>
+        <v>1.869634524467275</v>
       </c>
     </row>
     <row r="631">
@@ -26312,7 +26312,7 @@
         <v>12</v>
       </c>
       <c r="K631" t="n">
-        <v>2.001773745122148</v>
+        <v>2.00215150955919</v>
       </c>
     </row>
     <row r="632">
@@ -26353,7 +26353,7 @@
         <v>12</v>
       </c>
       <c r="K632" t="n">
-        <v>1.997460093098258</v>
+        <v>1.997060081239073</v>
       </c>
     </row>
     <row r="633">
@@ -26394,7 +26394,7 @@
         <v>12</v>
       </c>
       <c r="K633" t="n">
-        <v>1.997460093098258</v>
+        <v>1.997060081239073</v>
       </c>
     </row>
     <row r="634">
@@ -26435,7 +26435,7 @@
         <v>12</v>
       </c>
       <c r="K634" t="n">
-        <v>1.922001367796436</v>
+        <v>1.921479284662691</v>
       </c>
     </row>
     <row r="635">
@@ -26476,7 +26476,7 @@
         <v>12</v>
       </c>
       <c r="K635" t="n">
-        <v>1.85971668888828</v>
+        <v>1.858994779609939</v>
       </c>
     </row>
     <row r="636">
@@ -26517,7 +26517,7 @@
         <v>12</v>
       </c>
       <c r="K636" t="n">
-        <v>1.85971668888828</v>
+        <v>1.858994779609939</v>
       </c>
     </row>
     <row r="637">
@@ -26558,7 +26558,7 @@
         <v>12</v>
       </c>
       <c r="K637" t="n">
-        <v>1.80011545421401</v>
+        <v>1.798900388961088</v>
       </c>
     </row>
     <row r="638">
@@ -26599,7 +26599,7 @@
         <v>12</v>
       </c>
       <c r="K638" t="n">
-        <v>1.60787978877463</v>
+        <v>1.606244502493267</v>
       </c>
     </row>
     <row r="639">
@@ -26640,7 +26640,7 @@
         <v>12</v>
       </c>
       <c r="K639" t="n">
-        <v>1.523194373871843</v>
+        <v>1.52221702398882</v>
       </c>
     </row>
     <row r="640">
@@ -26681,7 +26681,7 @@
         <v>12</v>
       </c>
       <c r="K640" t="n">
-        <v>1.43457899949546</v>
+        <v>1.435226920765879</v>
       </c>
     </row>
     <row r="641">
@@ -26722,7 +26722,7 @@
         <v>12</v>
       </c>
       <c r="K641" t="n">
-        <v>1.43457899949546</v>
+        <v>1.435226920765879</v>
       </c>
     </row>
     <row r="642">
@@ -26763,7 +26763,7 @@
         <v>12</v>
       </c>
       <c r="K642" t="n">
-        <v>1.43457899949546</v>
+        <v>1.435226920765879</v>
       </c>
     </row>
     <row r="643">
@@ -26804,7 +26804,7 @@
         <v>12</v>
       </c>
       <c r="K643" t="n">
-        <v>1.43457899949546</v>
+        <v>1.435226920765879</v>
       </c>
     </row>
     <row r="644">
@@ -26845,7 +26845,7 @@
         <v>12</v>
       </c>
       <c r="K644" t="n">
-        <v>1.39055408208409</v>
+        <v>1.389359350348663</v>
       </c>
     </row>
     <row r="645">
@@ -26886,7 +26886,7 @@
         <v>12</v>
       </c>
       <c r="K645" t="n">
-        <v>1.39055408208409</v>
+        <v>1.389359350348663</v>
       </c>
     </row>
     <row r="646">
@@ -26927,7 +26927,7 @@
         <v>12</v>
       </c>
       <c r="K646" t="n">
-        <v>1.355687483893385</v>
+        <v>1.372677925654179</v>
       </c>
     </row>
     <row r="647">
@@ -26968,7 +26968,7 @@
         <v>12</v>
       </c>
       <c r="K647" t="n">
-        <v>1.355687483893385</v>
+        <v>1.355929724207424</v>
       </c>
     </row>
     <row r="648">
@@ -27009,7 +27009,7 @@
         <v>12</v>
       </c>
       <c r="K648" t="n">
-        <v>1.355687483893385</v>
+        <v>1.355929724207424</v>
       </c>
     </row>
     <row r="649">
@@ -27050,7 +27050,7 @@
         <v>12</v>
       </c>
       <c r="K649" t="n">
-        <v>1.316049262162023</v>
+        <v>1.315769865683484</v>
       </c>
     </row>
     <row r="650">
@@ -27091,7 +27091,7 @@
         <v>12</v>
       </c>
       <c r="K650" t="n">
-        <v>1.316049262162023</v>
+        <v>1.315769865683484</v>
       </c>
     </row>
     <row r="651">
@@ -27132,7 +27132,7 @@
         <v>12</v>
       </c>
       <c r="K651" t="n">
-        <v>1.308278324154629</v>
+        <v>1.308856099881447</v>
       </c>
     </row>
     <row r="652">
@@ -27173,7 +27173,7 @@
         <v>12</v>
       </c>
       <c r="K652" t="n">
-        <v>1.303477941053459</v>
+        <v>1.306651232125638</v>
       </c>
     </row>
     <row r="653">
@@ -27214,7 +27214,7 @@
         <v>12</v>
       </c>
       <c r="K653" t="n">
-        <v>1.298838943376611</v>
+        <v>1.300038557350185</v>
       </c>
     </row>
     <row r="654">
@@ -27255,7 +27255,7 @@
         <v>12</v>
       </c>
       <c r="K654" t="n">
-        <v>1.298838943376611</v>
+        <v>1.300038557350185</v>
       </c>
     </row>
     <row r="655">
@@ -27296,7 +27296,7 @@
         <v>12</v>
       </c>
       <c r="K655" t="n">
-        <v>1.298838943376611</v>
+        <v>1.300038557350185</v>
       </c>
     </row>
     <row r="656">
@@ -27337,7 +27337,7 @@
         <v>12</v>
       </c>
       <c r="K656" t="n">
-        <v>1.307751244711193</v>
+        <v>1.303680534015367</v>
       </c>
     </row>
     <row r="657">
@@ -27378,7 +27378,7 @@
         <v>12</v>
       </c>
       <c r="K657" t="n">
-        <v>1.32627407966019</v>
+        <v>1.334772402124477</v>
       </c>
     </row>
     <row r="658">
@@ -27419,7 +27419,7 @@
         <v>12</v>
       </c>
       <c r="K658" t="n">
-        <v>1.32627407966019</v>
+        <v>1.324017665756054</v>
       </c>
     </row>
     <row r="659">
@@ -27460,7 +27460,7 @@
         <v>12</v>
       </c>
       <c r="K659" t="n">
-        <v>1.445278265952763</v>
+        <v>1.447107701979886</v>
       </c>
     </row>
     <row r="660">
@@ -27501,7 +27501,7 @@
         <v>12</v>
       </c>
       <c r="K660" t="n">
-        <v>1.531232477808799</v>
+        <v>1.532105067645781</v>
       </c>
     </row>
     <row r="661">
@@ -27542,7 +27542,7 @@
         <v>12</v>
       </c>
       <c r="K661" t="n">
-        <v>1.610719542423982</v>
+        <v>1.61198440417721</v>
       </c>
     </row>
     <row r="662">
@@ -27583,7 +27583,7 @@
         <v>12</v>
       </c>
       <c r="K662" t="n">
-        <v>1.610719542423982</v>
+        <v>1.61198440417721</v>
       </c>
     </row>
     <row r="663">
@@ -27624,7 +27624,7 @@
         <v>12</v>
       </c>
       <c r="K663" t="n">
-        <v>1.677597541477979</v>
+        <v>1.67964346199181</v>
       </c>
     </row>
     <row r="664">
@@ -27665,7 +27665,7 @@
         <v>12</v>
       </c>
       <c r="K664" t="n">
-        <v>2.007281387903658</v>
+        <v>2.009090350876476</v>
       </c>
     </row>
     <row r="665">
@@ -27706,7 +27706,7 @@
         <v>12</v>
       </c>
       <c r="K665" t="n">
-        <v>2.007281387903658</v>
+        <v>2.009090350876476</v>
       </c>
     </row>
     <row r="666">
@@ -27747,7 +27747,7 @@
         <v>12</v>
       </c>
       <c r="K666" t="n">
-        <v>2.090168976303147</v>
+        <v>2.092429551075806</v>
       </c>
     </row>
     <row r="667">
@@ -27788,7 +27788,7 @@
         <v>12</v>
       </c>
       <c r="K667" t="n">
-        <v>2.090168976303147</v>
+        <v>2.092429551075806</v>
       </c>
     </row>
     <row r="668">
@@ -27829,7 +27829,7 @@
         <v>12</v>
       </c>
       <c r="K668" t="n">
-        <v>2.267254130189872</v>
+        <v>2.268723846714612</v>
       </c>
     </row>
     <row r="669">
@@ -27870,7 +27870,7 @@
         <v>12</v>
       </c>
       <c r="K669" t="n">
-        <v>2.363372231430629</v>
+        <v>2.363775733206697</v>
       </c>
     </row>
     <row r="670">
@@ -27911,7 +27911,7 @@
         <v>12</v>
       </c>
       <c r="K670" t="n">
-        <v>2.360552832004548</v>
+        <v>2.360071194468384</v>
       </c>
     </row>
     <row r="671">
@@ -27952,7 +27952,7 @@
         <v>12</v>
       </c>
       <c r="K671" t="n">
-        <v>2.360552832004548</v>
+        <v>2.360071194468384</v>
       </c>
     </row>
     <row r="672">
@@ -27993,7 +27993,7 @@
         <v>12</v>
       </c>
       <c r="K672" t="n">
-        <v>2.289717396500576</v>
+        <v>2.288563378807867</v>
       </c>
     </row>
     <row r="673">
@@ -28034,7 +28034,7 @@
         <v>12</v>
       </c>
       <c r="K673" t="n">
-        <v>2.230781576977644</v>
+        <v>2.229403528399245</v>
       </c>
     </row>
     <row r="674">
@@ -28075,7 +28075,7 @@
         <v>12</v>
       </c>
       <c r="K674" t="n">
-        <v>2.16026318861172</v>
+        <v>2.158653845416554</v>
       </c>
     </row>
     <row r="675">
@@ -28116,7 +28116,7 @@
         <v>12</v>
       </c>
       <c r="K675" t="n">
-        <v>1.944230033228157</v>
+        <v>1.943264704474658</v>
       </c>
     </row>
     <row r="676">
@@ -28157,7 +28157,7 @@
         <v>12</v>
       </c>
       <c r="K676" t="n">
-        <v>1.882953043862903</v>
+        <v>1.882037683194555</v>
       </c>
     </row>
     <row r="677">
@@ -28198,7 +28198,7 @@
         <v>12</v>
       </c>
       <c r="K677" t="n">
-        <v>1.767672420572199</v>
+        <v>1.76650290252906</v>
       </c>
     </row>
     <row r="678">
@@ -28239,7 +28239,7 @@
         <v>12</v>
       </c>
       <c r="K678" t="n">
-        <v>1.767672420572199</v>
+        <v>1.76650290252906</v>
       </c>
     </row>
     <row r="679">
@@ -28280,7 +28280,7 @@
         <v>12</v>
       </c>
       <c r="K679" t="n">
-        <v>1.680817090937332</v>
+        <v>1.680316263018162</v>
       </c>
     </row>
     <row r="680">
@@ -28321,7 +28321,7 @@
         <v>12</v>
       </c>
       <c r="K680" t="n">
-        <v>1.658627175004368</v>
+        <v>1.658323017786232</v>
       </c>
     </row>
     <row r="681">
@@ -28362,7 +28362,7 @@
         <v>12</v>
       </c>
       <c r="K681" t="n">
-        <v>1.639458829253433</v>
+        <v>1.639212943510234</v>
       </c>
     </row>
     <row r="682">
@@ -28403,7 +28403,7 @@
         <v>12</v>
       </c>
       <c r="K682" t="n">
-        <v>1.629020728744538</v>
+        <v>1.62879679676785</v>
       </c>
     </row>
     <row r="683">
@@ -28444,7 +28444,7 @@
         <v>12</v>
       </c>
       <c r="K683" t="n">
-        <v>1.629020728744538</v>
+        <v>1.62879679676785</v>
       </c>
     </row>
     <row r="684">
@@ -28485,7 +28485,7 @@
         <v>12</v>
       </c>
       <c r="K684" t="n">
-        <v>1.588054462942365</v>
+        <v>1.587587645311073</v>
       </c>
     </row>
     <row r="685">
@@ -28526,7 +28526,7 @@
         <v>12</v>
       </c>
       <c r="K685" t="n">
-        <v>1.559738234354261</v>
+        <v>1.559317997941901</v>
       </c>
     </row>
     <row r="686">
@@ -28567,7 +28567,7 @@
         <v>12</v>
       </c>
       <c r="K686" t="n">
-        <v>1.5341851165311</v>
+        <v>1.533785694400905</v>
       </c>
     </row>
     <row r="687">
@@ -28608,7 +28608,7 @@
         <v>12</v>
       </c>
       <c r="K687" t="n">
-        <v>1.397551012967835</v>
+        <v>1.397042858590406</v>
       </c>
     </row>
     <row r="688">
@@ -28649,7 +28649,7 @@
         <v>12</v>
       </c>
       <c r="K688" t="n">
-        <v>1.367327122229794</v>
+        <v>1.366961124571958</v>
       </c>
     </row>
     <row r="689">
@@ -28690,7 +28690,7 @@
         <v>12</v>
       </c>
       <c r="K689" t="n">
-        <v>1.298828102585088</v>
+        <v>1.298669958636224</v>
       </c>
     </row>
     <row r="690">
@@ -28731,7 +28731,7 @@
         <v>12</v>
       </c>
       <c r="K690" t="n">
-        <v>1.286767569665152</v>
+        <v>1.286672778510669</v>
       </c>
     </row>
     <row r="691">
@@ -28772,7 +28772,7 @@
         <v>12</v>
       </c>
       <c r="K691" t="n">
-        <v>1.307378016707403</v>
+        <v>1.307769713802554</v>
       </c>
     </row>
     <row r="692">
@@ -28813,7 +28813,7 @@
         <v>12</v>
       </c>
       <c r="K692" t="n">
-        <v>1.369275685855511</v>
+        <v>1.369506762517347</v>
       </c>
     </row>
     <row r="693">
@@ -28854,7 +28854,7 @@
         <v>12</v>
       </c>
       <c r="K693" t="n">
-        <v>1.388918172996225</v>
+        <v>1.389029040885113</v>
       </c>
     </row>
     <row r="694">
@@ -28895,7 +28895,7 @@
         <v>12</v>
       </c>
       <c r="K694" t="n">
-        <v>1.388918172996225</v>
+        <v>1.389029040885113</v>
       </c>
     </row>
     <row r="695">
@@ -28936,7 +28936,7 @@
         <v>12</v>
       </c>
       <c r="K695" t="n">
-        <v>1.393261488738817</v>
+        <v>1.393257992966911</v>
       </c>
     </row>
     <row r="696">
@@ -28977,7 +28977,7 @@
         <v>12</v>
       </c>
       <c r="K696" t="n">
-        <v>1.393261488738817</v>
+        <v>1.393257992966911</v>
       </c>
     </row>
     <row r="697">
@@ -29018,7 +29018,7 @@
         <v>12</v>
       </c>
       <c r="K697" t="n">
-        <v>1.390212443793561</v>
+        <v>1.390162145710057</v>
       </c>
     </row>
     <row r="698">
@@ -29059,7 +29059,7 @@
         <v>12</v>
       </c>
       <c r="K698" t="n">
-        <v>1.379839203880424</v>
+        <v>1.379706068093175</v>
       </c>
     </row>
     <row r="699">
@@ -29100,7 +29100,7 @@
         <v>12</v>
       </c>
       <c r="K699" t="n">
-        <v>1.357495870955582</v>
+        <v>1.35722069961142</v>
       </c>
     </row>
     <row r="700">
@@ -29141,7 +29141,7 @@
         <v>12</v>
       </c>
       <c r="K700" t="n">
-        <v>1.32667353055303</v>
+        <v>1.326367012655556</v>
       </c>
     </row>
     <row r="701">
@@ -29182,7 +29182,7 @@
         <v>12</v>
       </c>
       <c r="K701" t="n">
-        <v>1.22583659553023</v>
+        <v>1.225164070864174</v>
       </c>
     </row>
     <row r="702">
@@ -29223,7 +29223,7 @@
         <v>12</v>
       </c>
       <c r="K702" t="n">
-        <v>1.069529902851154</v>
+        <v>1.068872301826121</v>
       </c>
     </row>
     <row r="703">
@@ -29264,7 +29264,7 @@
         <v>12</v>
       </c>
       <c r="K703" t="n">
-        <v>0.8633362960477872</v>
+        <v>0.8623807552343694</v>
       </c>
     </row>
     <row r="704">
@@ -29305,7 +29305,7 @@
         <v>12</v>
       </c>
       <c r="K704" t="n">
-        <v>0.8633362960477872</v>
+        <v>0.8623807552343694</v>
       </c>
     </row>
     <row r="705">
@@ -29346,7 +29346,7 @@
         <v>12</v>
       </c>
       <c r="K705" t="n">
-        <v>0.7379015239748975</v>
+        <v>0.7371524952146997</v>
       </c>
     </row>
     <row r="706">
@@ -29387,7 +29387,7 @@
         <v>12</v>
       </c>
       <c r="K706" t="n">
-        <v>0.600382964889476</v>
+        <v>0.5999917302652901</v>
       </c>
     </row>
     <row r="707">
@@ -29428,7 +29428,7 @@
         <v>12</v>
       </c>
       <c r="K707" t="n">
-        <v>0.5415301479515319</v>
+        <v>0.5411570789756954</v>
       </c>
     </row>
     <row r="708">
@@ -29469,7 +29469,7 @@
         <v>12</v>
       </c>
       <c r="K708" t="n">
-        <v>0.5415301479515319</v>
+        <v>0.5411570789756954</v>
       </c>
     </row>
     <row r="709">
@@ -29510,7 +29510,7 @@
         <v>12</v>
       </c>
       <c r="K709" t="n">
-        <v>0.456056272287301</v>
+        <v>0.4561064301985042</v>
       </c>
     </row>
     <row r="710">
@@ -29551,7 +29551,7 @@
         <v>12</v>
       </c>
       <c r="K710" t="n">
-        <v>0.4627113003074372</v>
+        <v>0.4627640986307825</v>
       </c>
     </row>
     <row r="711">
@@ -29592,7 +29592,7 @@
         <v>12</v>
       </c>
       <c r="K711" t="n">
-        <v>0.6459922151241548</v>
+        <v>0.6463617096402818</v>
       </c>
     </row>
     <row r="712">
@@ -29633,7 +29633,7 @@
         <v>12</v>
       </c>
       <c r="K712" t="n">
-        <v>0.8054878637196621</v>
+        <v>0.8054628753986042</v>
       </c>
     </row>
     <row r="713">
@@ -29674,7 +29674,7 @@
         <v>12</v>
       </c>
       <c r="K713" t="n">
-        <v>0.8054878637196621</v>
+        <v>0.8054628753986042</v>
       </c>
     </row>
     <row r="714">
@@ -29715,7 +29715,7 @@
         <v>12</v>
       </c>
       <c r="K714" t="n">
-        <v>0.8175305434328686</v>
+        <v>0.8175785782439077</v>
       </c>
     </row>
     <row r="715">
@@ -29756,7 +29756,7 @@
         <v>12</v>
       </c>
       <c r="K715" t="n">
-        <v>0.8537506637873348</v>
+        <v>0.8538654325603435</v>
       </c>
     </row>
     <row r="716">
@@ -29797,7 +29797,7 @@
         <v>12</v>
       </c>
       <c r="K716" t="n">
-        <v>0.9410003644165074</v>
+        <v>0.9410849523926221</v>
       </c>
     </row>
     <row r="717">
@@ -29838,7 +29838,7 @@
         <v>12</v>
       </c>
       <c r="K717" t="n">
-        <v>0.9035678519035831</v>
+        <v>0.9035747726207866</v>
       </c>
     </row>
     <row r="718">
@@ -29879,7 +29879,7 @@
         <v>12</v>
       </c>
       <c r="K718" t="n">
-        <v>0.8739316917510455</v>
+        <v>0.8740440665291231</v>
       </c>
     </row>
     <row r="719">
@@ -29920,7 +29920,7 @@
         <v>12</v>
       </c>
       <c r="K719" t="n">
-        <v>0.8739316917510455</v>
+        <v>0.8740440665291231</v>
       </c>
     </row>
     <row r="720">
@@ -29961,7 +29961,7 @@
         <v>12</v>
       </c>
       <c r="K720" t="n">
-        <v>0.857571476277871</v>
+        <v>0.8584128153075468</v>
       </c>
     </row>
     <row r="721">
@@ -30002,7 +30002,7 @@
         <v>12</v>
       </c>
       <c r="K721" t="n">
-        <v>0.8336366264806322</v>
+        <v>0.8339041810366014</v>
       </c>
     </row>
     <row r="722">
@@ -30043,7 +30043,7 @@
         <v>12</v>
       </c>
       <c r="K722" t="n">
-        <v>0.8336366264806322</v>
+        <v>0.8339041810366014</v>
       </c>
     </row>
     <row r="723">
@@ -30084,7 +30084,7 @@
         <v>12</v>
       </c>
       <c r="K723" t="n">
-        <v>0.8336366264806322</v>
+        <v>0.8339041810366014</v>
       </c>
     </row>
     <row r="724">
@@ -30125,7 +30125,7 @@
         <v>12</v>
       </c>
       <c r="K724" t="n">
-        <v>0.8999185573363259</v>
+        <v>0.8989272716430202</v>
       </c>
     </row>
     <row r="725">
@@ -30166,7 +30166,7 @@
         <v>12</v>
       </c>
       <c r="K725" t="n">
-        <v>0.8999185573363259</v>
+        <v>0.8989272716430202</v>
       </c>
     </row>
     <row r="726">
@@ -30207,7 +30207,7 @@
         <v>12</v>
       </c>
       <c r="K726" t="n">
-        <v>0.9579656969267958</v>
+        <v>0.9579926927175598</v>
       </c>
     </row>
     <row r="727">
@@ -30248,7 +30248,7 @@
         <v>12</v>
       </c>
       <c r="K727" t="n">
-        <v>0.9579656969267958</v>
+        <v>0.9579926927175598</v>
       </c>
     </row>
     <row r="728">
@@ -30289,7 +30289,7 @@
         <v>12</v>
       </c>
       <c r="K728" t="n">
-        <v>0.9357829140065571</v>
+        <v>0.9358231927743621</v>
       </c>
     </row>
     <row r="729">
@@ -30330,7 +30330,7 @@
         <v>12</v>
       </c>
       <c r="K729" t="n">
-        <v>0.9357829140065571</v>
+        <v>0.9358231927743621</v>
       </c>
     </row>
     <row r="730">
@@ -30371,7 +30371,7 @@
         <v>12</v>
       </c>
       <c r="K730" t="n">
-        <v>0.9271736626573989</v>
+        <v>0.9271346180002836</v>
       </c>
     </row>
     <row r="731">
@@ -30412,7 +30412,7 @@
         <v>12</v>
       </c>
       <c r="K731" t="n">
-        <v>0.9448753482394272</v>
+        <v>0.9452001165404804</v>
       </c>
     </row>
     <row r="732">
@@ -30453,7 +30453,7 @@
         <v>12</v>
       </c>
       <c r="K732" t="n">
-        <v>1.180046920007321</v>
+        <v>1.18074013308314</v>
       </c>
     </row>
     <row r="733">
@@ -30494,7 +30494,7 @@
         <v>12</v>
       </c>
       <c r="K733" t="n">
-        <v>1.274051686376322</v>
+        <v>1.27454958835024</v>
       </c>
     </row>
     <row r="734">
@@ -30535,7 +30535,7 @@
         <v>12</v>
       </c>
       <c r="K734" t="n">
-        <v>1.404131438623516</v>
+        <v>1.404485977237237</v>
       </c>
     </row>
     <row r="735">
@@ -30576,7 +30576,7 @@
         <v>12</v>
       </c>
       <c r="K735" t="n">
-        <v>1.45289325137742</v>
+        <v>1.453105573464977</v>
       </c>
     </row>
     <row r="736">
@@ -30617,7 +30617,7 @@
         <v>12</v>
       </c>
       <c r="K736" t="n">
-        <v>1.480714902937465</v>
+        <v>1.480798188451419</v>
       </c>
     </row>
     <row r="737">
@@ -30658,7 +30658,7 @@
         <v>12</v>
       </c>
       <c r="K737" t="n">
-        <v>1.480714902937465</v>
+        <v>1.480798188451419</v>
       </c>
     </row>
     <row r="738">
@@ -30699,7 +30699,7 @@
         <v>12</v>
       </c>
       <c r="K738" t="n">
-        <v>1.426528439507999</v>
+        <v>1.426343509003666</v>
       </c>
     </row>
     <row r="739">
@@ -30740,7 +30740,7 @@
         <v>12</v>
       </c>
       <c r="K739" t="n">
-        <v>1.426528439507999</v>
+        <v>1.426343509003666</v>
       </c>
     </row>
     <row r="740">
@@ -30781,7 +30781,7 @@
         <v>12</v>
       </c>
       <c r="K740" t="n">
-        <v>1.320483388157286</v>
+        <v>1.320306572972977</v>
       </c>
     </row>
     <row r="741">
@@ -30822,7 +30822,7 @@
         <v>12</v>
       </c>
       <c r="K741" t="n">
-        <v>1.27395507353025</v>
+        <v>1.273847041107833</v>
       </c>
     </row>
     <row r="742">
@@ -30863,7 +30863,7 @@
         <v>12</v>
       </c>
       <c r="K742" t="n">
-        <v>1.27395507353025</v>
+        <v>1.273847041107833</v>
       </c>
     </row>
     <row r="743">
@@ -30904,7 +30904,7 @@
         <v>12</v>
       </c>
       <c r="K743" t="n">
-        <v>1.265384868890062</v>
+        <v>1.265451438201339</v>
       </c>
     </row>
     <row r="744">
@@ -30945,7 +30945,7 @@
         <v>12</v>
       </c>
       <c r="K744" t="n">
-        <v>1.303822642536857</v>
+        <v>1.303903775925011</v>
       </c>
     </row>
     <row r="745">
@@ -30986,7 +30986,7 @@
         <v>12</v>
       </c>
       <c r="K745" t="n">
-        <v>1.303822642536857</v>
+        <v>1.303903775925011</v>
       </c>
     </row>
     <row r="746">
@@ -31027,7 +31027,7 @@
         <v>12</v>
       </c>
       <c r="K746" t="n">
-        <v>1.363041934445349</v>
+        <v>1.363074139794368</v>
       </c>
     </row>
     <row r="747">
@@ -31068,7 +31068,7 @@
         <v>12</v>
       </c>
       <c r="K747" t="n">
-        <v>1.436695540169181</v>
+        <v>1.436716007822022</v>
       </c>
     </row>
     <row r="748">
@@ -31109,7 +31109,7 @@
         <v>12</v>
       </c>
       <c r="K748" t="n">
-        <v>1.436695540169181</v>
+        <v>1.436716007822022</v>
       </c>
     </row>
     <row r="749">
@@ -31150,7 +31150,7 @@
         <v>12</v>
       </c>
       <c r="K749" t="n">
-        <v>1.502618499091818</v>
+        <v>1.502629021323229</v>
       </c>
     </row>
     <row r="750">
@@ -31191,7 +31191,7 @@
         <v>12</v>
       </c>
       <c r="K750" t="n">
-        <v>1.502618499091818</v>
+        <v>1.502629021323229</v>
       </c>
     </row>
     <row r="751">
@@ -31232,7 +31232,7 @@
         <v>12</v>
       </c>
       <c r="K751" t="n">
-        <v>1.441810765271844</v>
+        <v>1.441870620084969</v>
       </c>
     </row>
     <row r="752">
@@ -31273,7 +31273,7 @@
         <v>12</v>
       </c>
       <c r="K752" t="n">
-        <v>1.404795770268469</v>
+        <v>1.404862196462992</v>
       </c>
     </row>
     <row r="753">
@@ -31314,7 +31314,7 @@
         <v>12</v>
       </c>
       <c r="K753" t="n">
-        <v>1.256752776860887</v>
+        <v>1.256823085575394</v>
       </c>
     </row>
     <row r="754">
@@ -31355,7 +31355,7 @@
         <v>12</v>
       </c>
       <c r="K754" t="n">
-        <v>1.256752776860887</v>
+        <v>1.256823085575394</v>
       </c>
     </row>
     <row r="755">
@@ -31396,7 +31396,7 @@
         <v>12</v>
       </c>
       <c r="K755" t="n">
-        <v>1.203118079175934</v>
+        <v>1.203222900750921</v>
       </c>
     </row>
     <row r="756">
@@ -31437,7 +31437,7 @@
         <v>12</v>
       </c>
       <c r="K756" t="n">
-        <v>1.172163889343052</v>
+        <v>1.172085373449719</v>
       </c>
     </row>
     <row r="757">
@@ -31478,7 +31478,7 @@
         <v>12</v>
       </c>
       <c r="K757" t="n">
-        <v>1.172163889343052</v>
+        <v>1.172085373449719</v>
       </c>
     </row>
     <row r="758">
@@ -31519,7 +31519,7 @@
         <v>12</v>
       </c>
       <c r="K758" t="n">
-        <v>1.196848691332015</v>
+        <v>1.196695072993834</v>
       </c>
     </row>
     <row r="759">
@@ -31560,7 +31560,7 @@
         <v>12</v>
       </c>
       <c r="K759" t="n">
-        <v>1.279988141944838</v>
+        <v>1.280024827716081</v>
       </c>
     </row>
     <row r="760">
@@ -31601,7 +31601,7 @@
         <v>12</v>
       </c>
       <c r="K760" t="n">
-        <v>1.33774645115203</v>
+        <v>1.337818658959068</v>
       </c>
     </row>
     <row r="761">
@@ -31642,7 +31642,7 @@
         <v>12</v>
       </c>
       <c r="K761" t="n">
-        <v>1.33774645115203</v>
+        <v>1.337818658959068</v>
       </c>
     </row>
     <row r="762">
@@ -31683,7 +31683,7 @@
         <v>12</v>
       </c>
       <c r="K762" t="n">
-        <v>1.339094749193525</v>
+        <v>1.339008683943403</v>
       </c>
     </row>
     <row r="763">
@@ -31724,7 +31724,7 @@
         <v>12</v>
       </c>
       <c r="K763" t="n">
-        <v>1.238409889066349</v>
+        <v>1.239239684718074</v>
       </c>
     </row>
     <row r="764">
@@ -31765,7 +31765,7 @@
         <v>12</v>
       </c>
       <c r="K764" t="n">
-        <v>1.238409889066349</v>
+        <v>1.239239684718074</v>
       </c>
     </row>
     <row r="765">
@@ -31806,7 +31806,7 @@
         <v>12</v>
       </c>
       <c r="K765" t="n">
-        <v>1.153798433927621</v>
+        <v>1.154781653041135</v>
       </c>
     </row>
     <row r="766">
@@ -31847,7 +31847,7 @@
         <v>12</v>
       </c>
       <c r="K766" t="n">
-        <v>0.9054037680415632</v>
+        <v>0.905859918563528</v>
       </c>
     </row>
     <row r="767">
@@ -31888,7 +31888,7 @@
         <v>12</v>
       </c>
       <c r="K767" t="n">
-        <v>0.9054037680415632</v>
+        <v>0.905859918563528</v>
       </c>
     </row>
     <row r="768">
@@ -31929,7 +31929,7 @@
         <v>12</v>
       </c>
       <c r="K768" t="n">
-        <v>0.7822182797546607</v>
+        <v>0.7827035441572652</v>
       </c>
     </row>
     <row r="769">
@@ -31970,7 +31970,7 @@
         <v>12</v>
       </c>
       <c r="K769" t="n">
-        <v>0.6931997822076109</v>
+        <v>0.6937357006233744</v>
       </c>
     </row>
     <row r="770">
@@ -32011,7 +32011,7 @@
         <v>12</v>
       </c>
       <c r="K770" t="n">
-        <v>0.4303462304751228</v>
+        <v>0.4308034010791127</v>
       </c>
     </row>
     <row r="771">
@@ -32052,7 +32052,7 @@
         <v>12</v>
       </c>
       <c r="K771" t="n">
-        <v>0.425736883868912</v>
+        <v>0.4258471557325104</v>
       </c>
     </row>
     <row r="772">
@@ -32093,7 +32093,7 @@
         <v>12</v>
       </c>
       <c r="K772" t="n">
-        <v>0.425736883868912</v>
+        <v>0.4258471557325104</v>
       </c>
     </row>
     <row r="773">
@@ -32134,7 +32134,7 @@
         <v>12</v>
       </c>
       <c r="K773" t="n">
-        <v>0.425736883868912</v>
+        <v>0.4258471557325104</v>
       </c>
     </row>
     <row r="774">
@@ -32175,7 +32175,7 @@
         <v>12</v>
       </c>
       <c r="K774" t="n">
-        <v>0.4741406117715971</v>
+        <v>0.4792780522319721</v>
       </c>
     </row>
     <row r="775">
@@ -32216,7 +32216,7 @@
         <v>12</v>
       </c>
       <c r="K775" t="n">
-        <v>0.6179878715603118</v>
+        <v>0.6172223432705676</v>
       </c>
     </row>
     <row r="776">
@@ -32257,7 +32257,7 @@
         <v>12</v>
       </c>
       <c r="K776" t="n">
-        <v>0.7245889203903195</v>
+        <v>0.7254256015157372</v>
       </c>
     </row>
     <row r="777">
@@ -32298,7 +32298,7 @@
         <v>12</v>
       </c>
       <c r="K777" t="n">
-        <v>0.7245889203903195</v>
+        <v>0.7254256015157372</v>
       </c>
     </row>
     <row r="778">
@@ -32339,7 +32339,7 @@
         <v>12</v>
       </c>
       <c r="K778" t="n">
-        <v>0.7483247600716969</v>
+        <v>0.7471741097607512</v>
       </c>
     </row>
     <row r="779">
@@ -32380,7 +32380,7 @@
         <v>12</v>
       </c>
       <c r="K779" t="n">
-        <v>0.8256520674606761</v>
+        <v>0.8261081367939086</v>
       </c>
     </row>
     <row r="780">
@@ -32421,7 +32421,7 @@
         <v>12</v>
       </c>
       <c r="K780" t="n">
-        <v>0.8256520674606761</v>
+        <v>0.8261081367939086</v>
       </c>
     </row>
     <row r="781">
@@ -32462,7 +32462,7 @@
         <v>12</v>
       </c>
       <c r="K781" t="n">
-        <v>0.8256520674606761</v>
+        <v>0.8261081367939086</v>
       </c>
     </row>
     <row r="782">
@@ -32503,7 +32503,7 @@
         <v>12</v>
       </c>
       <c r="K782" t="n">
-        <v>0.8312276366585113</v>
+        <v>0.8304565436518452</v>
       </c>
     </row>
     <row r="783">
@@ -32544,7 +32544,7 @@
         <v>12</v>
       </c>
       <c r="K783" t="n">
-        <v>0.8312276366585113</v>
+        <v>0.8304565436518452</v>
       </c>
     </row>
     <row r="784">
@@ -32585,7 +32585,7 @@
         <v>12</v>
       </c>
       <c r="K784" t="n">
-        <v>0.8195009571327245</v>
+        <v>0.8186780535671553</v>
       </c>
     </row>
     <row r="785">
@@ -32626,7 +32626,7 @@
         <v>12</v>
       </c>
       <c r="K785" t="n">
-        <v>0.7411302170477566</v>
+        <v>0.7411431598142287</v>
       </c>
     </row>
     <row r="786">
@@ -32667,7 +32667,7 @@
         <v>12</v>
       </c>
       <c r="K786" t="n">
-        <v>0.7489625352557558</v>
+        <v>0.7490435342364423</v>
       </c>
     </row>
     <row r="787">
@@ -32708,7 +32708,7 @@
         <v>12</v>
       </c>
       <c r="K787" t="n">
-        <v>0.7571139453758954</v>
+        <v>0.7571135273289155</v>
       </c>
     </row>
     <row r="788">
@@ -32749,7 +32749,7 @@
         <v>12</v>
       </c>
       <c r="K788" t="n">
-        <v>0.7571139453758954</v>
+        <v>0.7571135273289155</v>
       </c>
     </row>
     <row r="789">
@@ -32790,7 +32790,7 @@
         <v>12</v>
       </c>
       <c r="K789" t="n">
-        <v>0.7640387245539881</v>
+        <v>0.7640293032343267</v>
       </c>
     </row>
     <row r="790">
@@ -32831,7 +32831,7 @@
         <v>12</v>
       </c>
       <c r="K790" t="n">
-        <v>0.8931849015680801</v>
+        <v>0.8931283091564407</v>
       </c>
     </row>
     <row r="791">
@@ -32872,7 +32872,7 @@
         <v>12</v>
       </c>
       <c r="K791" t="n">
-        <v>0.9409017862981774</v>
+        <v>0.9408335003940822</v>
       </c>
     </row>
     <row r="792">
@@ -32913,7 +32913,7 @@
         <v>12</v>
       </c>
       <c r="K792" t="n">
-        <v>0.9840217771270924</v>
+        <v>0.9839439701637269</v>
       </c>
     </row>
     <row r="793">
@@ -32954,7 +32954,7 @@
         <v>12</v>
       </c>
       <c r="K793" t="n">
-        <v>1.013839090125002</v>
+        <v>1.013789178098625</v>
       </c>
     </row>
     <row r="794">
@@ -32995,7 +32995,7 @@
         <v>12</v>
       </c>
       <c r="K794" t="n">
-        <v>1.021732293330856</v>
+        <v>1.021740482231886</v>
       </c>
     </row>
     <row r="795">
@@ -33036,7 +33036,7 @@
         <v>12</v>
       </c>
       <c r="K795" t="n">
-        <v>1.021510315205498</v>
+        <v>1.021489785681747</v>
       </c>
     </row>
     <row r="796">
@@ -33077,7 +33077,7 @@
         <v>12</v>
       </c>
       <c r="K796" t="n">
-        <v>1.024611421402347</v>
+        <v>1.024616283489223</v>
       </c>
     </row>
     <row r="797">
@@ -33118,7 +33118,7 @@
         <v>12</v>
       </c>
       <c r="K797" t="n">
-        <v>1.023170799233587</v>
+        <v>1.023171790842192</v>
       </c>
     </row>
     <row r="798">
@@ -33159,7 +33159,7 @@
         <v>12</v>
       </c>
       <c r="K798" t="n">
-        <v>1.037660039716004</v>
+        <v>1.037647667559816</v>
       </c>
     </row>
     <row r="799">
@@ -33200,7 +33200,7 @@
         <v>12</v>
       </c>
       <c r="K799" t="n">
-        <v>1.037660039716004</v>
+        <v>1.037647667559816</v>
       </c>
     </row>
     <row r="800">
@@ -33241,7 +33241,7 @@
         <v>12</v>
       </c>
       <c r="K800" t="n">
-        <v>1.035876368716922</v>
+        <v>1.035908292469522</v>
       </c>
     </row>
     <row r="801">
@@ -33282,7 +33282,7 @@
         <v>12</v>
       </c>
       <c r="K801" t="n">
-        <v>1.02304057128544</v>
+        <v>1.023130306328624</v>
       </c>
     </row>
     <row r="802">
@@ -33323,7 +33323,7 @@
         <v>12</v>
       </c>
       <c r="K802" t="n">
-        <v>1.04993575399346</v>
+        <v>1.049876894917689</v>
       </c>
     </row>
     <row r="803">
@@ -33364,7 +33364,7 @@
         <v>12</v>
       </c>
       <c r="K803" t="n">
-        <v>1.045087730343041</v>
+        <v>1.045288913937081</v>
       </c>
     </row>
     <row r="804">
@@ -33405,7 +33405,7 @@
         <v>12</v>
       </c>
       <c r="K804" t="n">
-        <v>1.01356277959666</v>
+        <v>1.01368745633356</v>
       </c>
     </row>
     <row r="805">
@@ -33446,7 +33446,7 @@
         <v>12</v>
       </c>
       <c r="K805" t="n">
-        <v>0.9865866182871941</v>
+        <v>0.9868283865377088</v>
       </c>
     </row>
     <row r="806">
@@ -33487,7 +33487,7 @@
         <v>12</v>
       </c>
       <c r="K806" t="n">
-        <v>0.9430045533821274</v>
+        <v>0.9433617020432808</v>
       </c>
     </row>
     <row r="807">
@@ -33528,7 +33528,7 @@
         <v>12</v>
       </c>
       <c r="K807" t="n">
-        <v>0.8991554120777662</v>
+        <v>0.8994905605926278</v>
       </c>
     </row>
     <row r="808">
@@ -33569,7 +33569,7 @@
         <v>12</v>
       </c>
       <c r="K808" t="n">
-        <v>0.8901445688078437</v>
+        <v>0.8904036358446076</v>
       </c>
     </row>
     <row r="809">
@@ -33610,7 +33610,7 @@
         <v>12</v>
       </c>
       <c r="K809" t="n">
-        <v>0.8901445688078437</v>
+        <v>0.8904036358446076</v>
       </c>
     </row>
     <row r="810">
@@ -33651,7 +33651,7 @@
         <v>12</v>
       </c>
       <c r="K810" t="n">
-        <v>0.887951663664214</v>
+        <v>0.8889643336122491</v>
       </c>
     </row>
     <row r="811">
@@ -33692,7 +33692,7 @@
         <v>12</v>
       </c>
       <c r="K811" t="n">
-        <v>0.8334971394147027</v>
+        <v>0.8330842897219191</v>
       </c>
     </row>
     <row r="812">
@@ -33733,7 +33733,7 @@
         <v>12</v>
       </c>
       <c r="K812" t="n">
-        <v>0.6864573158648335</v>
+        <v>0.6882428093717404</v>
       </c>
     </row>
     <row r="813">
@@ -33774,7 +33774,7 @@
         <v>12</v>
       </c>
       <c r="K813" t="n">
-        <v>0.6864573158648335</v>
+        <v>0.6882428093717404</v>
       </c>
     </row>
     <row r="814">
@@ -33815,7 +33815,7 @@
         <v>12</v>
       </c>
       <c r="K814" t="n">
-        <v>0.5737825821688167</v>
+        <v>0.5711806186536532</v>
       </c>
     </row>
     <row r="815">
@@ -33856,7 +33856,7 @@
         <v>12</v>
       </c>
       <c r="K815" t="n">
-        <v>0.5737825821688167</v>
+        <v>0.5711806186536532</v>
       </c>
     </row>
     <row r="816">
@@ -33897,7 +33897,7 @@
         <v>12</v>
       </c>
       <c r="K816" t="n">
-        <v>0.4717068837457349</v>
+        <v>0.4712106652049183</v>
       </c>
     </row>
     <row r="817">
@@ -33938,7 +33938,7 @@
         <v>12</v>
       </c>
       <c r="K817" t="n">
-        <v>0.4717068837457349</v>
+        <v>0.4712106652049183</v>
       </c>
     </row>
     <row r="818">
@@ -33979,7 +33979,7 @@
         <v>12</v>
       </c>
       <c r="K818" t="n">
-        <v>0.2742043165589557</v>
+        <v>0.2741498253870284</v>
       </c>
     </row>
     <row r="819">
@@ -34020,7 +34020,7 @@
         <v>12</v>
       </c>
       <c r="K819" t="n">
-        <v>0.2742043165589557</v>
+        <v>0.2741498253870284</v>
       </c>
     </row>
     <row r="820">
@@ -34061,7 +34061,7 @@
         <v>12</v>
       </c>
       <c r="K820" t="n">
-        <v>0.1860603252607773</v>
+        <v>0.1859618558602376</v>
       </c>
     </row>
     <row r="821">
@@ -34102,7 +34102,7 @@
         <v>12</v>
       </c>
       <c r="K821" t="n">
-        <v>0.149548527462926</v>
+        <v>0.1495465771193803</v>
       </c>
     </row>
     <row r="822">
@@ -34143,7 +34143,7 @@
         <v>12</v>
       </c>
       <c r="K822" t="n">
-        <v>0.08941611297199926</v>
+        <v>0.08939671765915708</v>
       </c>
     </row>
     <row r="823">
@@ -34184,7 +34184,7 @@
         <v>12</v>
       </c>
       <c r="K823" t="n">
-        <v>0.08941611297199926</v>
+        <v>0.08939671765915708</v>
       </c>
     </row>
   </sheetData>
